--- a/NN/reports/feature_importance_white_apparent_color.xlsx
+++ b/NN/reports/feature_importance_white_apparent_color.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,25 +501,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4786348643532474</v>
+        <v>0.4065729105196067</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3762015255356469</v>
+        <v>0.3291493018522236</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6232002183142639</v>
+        <v>0.4644109321358291</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.346260559415132</v>
+        <v>1.438671876188928</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -538,25 +538,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.3098513501376765</v>
+        <v>0.2992099333553406</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2624451226637246</v>
+        <v>0.2291797279328061</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4047814927752794</v>
+        <v>0.2967604346712479</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1.315657187137866</v>
+        <v>1.423770799533282</v>
       </c>
       <c r="J3" t="n">
         <v>3</v>
@@ -575,25 +575,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.06980168567350829</v>
+        <v>0.07043117580663896</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08470205394166801</v>
+        <v>0.07192762145117108</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07276763467443288</v>
+        <v>0.024694422256211</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8451519580197258</v>
+        <v>0.947515211524121</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
@@ -612,31 +612,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03392125819245912</v>
+        <v>0.04282009912729453</v>
       </c>
       <c r="D5" t="n">
         <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1439102514616759</v>
+        <v>0.1558290110023217</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008169226868447944</v>
+        <v>0.005706524045798944</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8103699164537534</v>
+        <v>0.8392709336065023</v>
       </c>
       <c r="J5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" t="n">
         <v>5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.25</v>
       </c>
     </row>
     <row r="6">
@@ -649,31 +649,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01242469539784901</v>
+        <v>0.007345090478667085</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07230265917906245</v>
+        <v>0.050508469336305</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.005106458936631621</v>
+        <v>0.001290483164256017</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>1.371659402701831</v>
+        <v>1.516185073214777</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>4.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="7">
@@ -686,31 +686,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03503447106524671</v>
+        <v>0.06347889196297038</v>
       </c>
       <c r="D7" t="n">
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01178356171528505</v>
+        <v>0.01086974528925099</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007549312702406741</v>
+        <v>0.012058307620746</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>0.659958613808139</v>
+        <v>0.7102381910625768</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
@@ -719,35 +719,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.005348600779763525</v>
+        <v>0.01424827950268244</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01099374852031951</v>
+        <v>0.0388937622385257</v>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003880400052873412</v>
+        <v>0.01167431989016168</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1482735288640082</v>
+        <v>0.2864599872107711</v>
       </c>
       <c r="J8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="9">
@@ -756,35 +756,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.00463989376297619</v>
+        <v>0.005953696622513246</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>0.008554197203700507</v>
+        <v>0.0110282599486145</v>
       </c>
       <c r="F9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.002388489583926789</v>
+      </c>
+      <c r="H9" t="n">
         <v>8</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.003883780624181632</v>
-      </c>
-      <c r="H9" t="n">
-        <v>7</v>
-      </c>
       <c r="I9" t="n">
-        <v>0.1322699898506867</v>
+        <v>0.2408345741623004</v>
       </c>
       <c r="J9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>8.75</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="10">
@@ -793,35 +793,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.006141089234745527</v>
+        <v>0.0058600638538843</v>
       </c>
       <c r="D10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.0120158828156668</v>
+      </c>
+      <c r="F10" t="n">
         <v>7</v>
       </c>
-      <c r="E10" t="n">
-        <v>0.003407463086655959</v>
-      </c>
-      <c r="F10" t="n">
-        <v>10</v>
-      </c>
       <c r="G10" t="n">
-        <v>0.0009873511723142102</v>
+        <v>0.002259821391015104</v>
       </c>
       <c r="H10" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1374615805992225</v>
+        <v>0.2066749365948048</v>
       </c>
       <c r="J10" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
-        <v>9.5</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="11">
@@ -830,35 +830,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.004989664380578769</v>
+        <v>0.003732832738122984</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>0.002159270160746743</v>
+        <v>0.00371639329167186</v>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G11" t="n">
-        <v>0.003578368583356606</v>
+        <v>0.002466793375889997</v>
       </c>
       <c r="H11" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.6266420055755306</v>
+      </c>
+      <c r="J11" t="n">
         <v>9</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.1112783347692781</v>
-      </c>
-      <c r="J11" t="n">
-        <v>11</v>
-      </c>
       <c r="K11" t="n">
-        <v>11</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="12">
@@ -867,35 +867,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.005532454955602316</v>
+        <v>0.005718097971075684</v>
       </c>
       <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.01114242239312433</v>
+      </c>
+      <c r="F12" t="n">
         <v>8</v>
       </c>
-      <c r="E12" t="n">
-        <v>0.003198662685508405</v>
-      </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
+        <v>0.001872568715010792</v>
+      </c>
+      <c r="H12" t="n">
         <v>11</v>
       </c>
-      <c r="G12" t="n">
-        <v>0.0007333918858249078</v>
-      </c>
-      <c r="H12" t="n">
-        <v>14</v>
-      </c>
       <c r="I12" t="n">
-        <v>0.07213303796757264</v>
+        <v>0.1927333513280312</v>
       </c>
       <c r="J12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K12" t="n">
-        <v>12.25</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="13">
@@ -904,35 +904,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.002734043432042849</v>
+        <v>0.003447581827407039</v>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E13" t="n">
-        <v>0.003869405558171784</v>
+        <v>0.005242163931629659</v>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>0.000721451771677295</v>
+        <v>0.0007476917004784811</v>
       </c>
       <c r="H13" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1167555227631789</v>
+        <v>0.8867983829986508</v>
       </c>
       <c r="J13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>13</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="14">
@@ -941,35 +941,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.004166440980821164</v>
+        <v>0.002388679605767266</v>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001692518774872319</v>
+        <v>0.004392508987762973</v>
       </c>
       <c r="F14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001854515844907234</v>
+        <v>0.001013569475495801</v>
       </c>
       <c r="H14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I14" t="n">
-        <v>0.07859573331795744</v>
+        <v>0.672769671377254</v>
       </c>
       <c r="J14" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K14" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="15">
@@ -978,35 +978,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.004065886073554982</v>
+        <v>0.003852124005685164</v>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
-        <v>0.001616983925291124</v>
+        <v>0.002072561167334866</v>
       </c>
       <c r="F15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001233759210154783</v>
+        <v>0.001972247393986859</v>
       </c>
       <c r="H15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1021684507793905</v>
+        <v>0.1482583563546349</v>
       </c>
       <c r="J15" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K15" t="n">
-        <v>14</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="16">
@@ -1015,35 +1015,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.004323760808917921</v>
+        <v>0.001933603185737217</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E16" t="n">
-        <v>0.00193933852238919</v>
+        <v>0.009198273584937154</v>
       </c>
       <c r="F16" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001929100053758637</v>
+        <v>0.0002671008442111988</v>
       </c>
       <c r="H16" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01218160236218147</v>
+        <v>0.2678695621723715</v>
       </c>
       <c r="J16" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="K16" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -1052,35 +1052,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.003810996429117441</v>
+        <v>0.001590935227078281</v>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0024396892818847</v>
+        <v>0.002694814176495566</v>
       </c>
       <c r="F17" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.167182530903421e-06</v>
+        <v>0.0004935313015578035</v>
       </c>
       <c r="H17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I17" t="n">
-        <v>0.09634405678887825</v>
+        <v>0.2025258905133143</v>
       </c>
       <c r="J17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>15.25</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="18">
@@ -1089,35 +1089,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.00329161335759338</v>
+        <v>0.005213653768950966</v>
       </c>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>0.002069153113653987</v>
+        <v>0.001723245257052869</v>
       </c>
       <c r="F18" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G18" t="n">
-        <v>0.000568981263335111</v>
+        <v>0.001207182745202107</v>
       </c>
       <c r="H18" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I18" t="n">
-        <v>0.09752444756001344</v>
+        <v>0.09164550956329354</v>
       </c>
       <c r="J18" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="K18" t="n">
-        <v>15.25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1126,35 +1126,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.003882389082831054</v>
+        <v>0.002141043114578652</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E19" t="n">
-        <v>0.002200132824558406</v>
+        <v>0.003472869175817386</v>
       </c>
       <c r="F19" t="n">
+        <v>16</v>
+      </c>
+      <c r="G19" t="n">
+        <v>7.578620613383214e-05</v>
+      </c>
+      <c r="H19" t="n">
+        <v>34</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2165485625793266</v>
+      </c>
+      <c r="J19" t="n">
         <v>13</v>
       </c>
-      <c r="G19" t="n">
-        <v>-0.0003473508515325241</v>
-      </c>
-      <c r="H19" t="n">
-        <v>23</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.04975117740217749</v>
-      </c>
-      <c r="J19" t="n">
-        <v>18</v>
-      </c>
       <c r="K19" t="n">
-        <v>17.25</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="20">
@@ -1163,35 +1163,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.002393279772807551</v>
+        <v>0.002390475329932857</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E20" t="n">
-        <v>0.00106253959687849</v>
+        <v>0.002589998571600898</v>
       </c>
       <c r="F20" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0003282113358627048</v>
+        <v>0.0008620481737081521</v>
       </c>
       <c r="H20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03899607561514129</v>
+        <v>0.08446606360304898</v>
       </c>
       <c r="J20" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="K20" t="n">
-        <v>19.25</v>
+        <v>23.25</v>
       </c>
     </row>
     <row r="21">
@@ -1200,35 +1200,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.002132948626544079</v>
+        <v>0.002275603295886006</v>
       </c>
       <c r="D21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E21" t="n">
-        <v>0.001251485665618902</v>
+        <v>0.001409204688916107</v>
       </c>
       <c r="F21" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.620251328233735e-05</v>
+        <v>0.000442262914799052</v>
       </c>
       <c r="H21" t="n">
         <v>20</v>
       </c>
       <c r="I21" t="n">
-        <v>0.05786450899225626</v>
+        <v>0.1295419430619873</v>
       </c>
       <c r="J21" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K21" t="n">
-        <v>19.5</v>
+        <v>24.25</v>
       </c>
     </row>
     <row r="22">
@@ -1237,35 +1237,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.002637019746055926</v>
+        <v>0.00227475211272811</v>
       </c>
       <c r="D22" t="n">
+        <v>21</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.001366326113494094</v>
+      </c>
+      <c r="F22" t="n">
+        <v>29</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.0004730488266915911</v>
+      </c>
+      <c r="H22" t="n">
         <v>19</v>
       </c>
-      <c r="E22" t="n">
-        <v>0.001544170109840377</v>
-      </c>
-      <c r="F22" t="n">
-        <v>19</v>
-      </c>
-      <c r="G22" t="n">
-        <v>-0.0001381729846377189</v>
-      </c>
-      <c r="H22" t="n">
-        <v>22</v>
-      </c>
       <c r="I22" t="n">
-        <v>0.03770165826434724</v>
+        <v>0.1430346516538337</v>
       </c>
       <c r="J22" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K22" t="n">
-        <v>20</v>
+        <v>24.25</v>
       </c>
     </row>
     <row r="23">
@@ -1274,35 +1274,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>9.59467886710826e-05</v>
+        <v>0.003162079358151949</v>
       </c>
       <c r="D23" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0004263296390325067</v>
+        <v>0.001137377474102061</v>
       </c>
       <c r="F23" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G23" t="n">
-        <v>2.229772772206484e-05</v>
+        <v>0.0001723422210909487</v>
       </c>
       <c r="H23" t="n">
+        <v>31</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.1921799270615958</v>
+      </c>
+      <c r="J23" t="n">
         <v>18</v>
       </c>
-      <c r="I23" t="n">
-        <v>0.03239086953742176</v>
-      </c>
-      <c r="J23" t="n">
-        <v>21</v>
-      </c>
       <c r="K23" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24">
@@ -1311,35 +1311,1145 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.00014564696738907</v>
+        <v>0.001395045957988709</v>
       </c>
       <c r="D24" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0002297368338141414</v>
+        <v>0.009018698114905568</v>
       </c>
       <c r="F24" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0001222522612605914</v>
+        <v>0.0004357877178527647</v>
       </c>
       <c r="H24" t="n">
         <v>21</v>
       </c>
       <c r="I24" t="n">
+        <v>0.1361843957214524</v>
+      </c>
+      <c r="J24" t="n">
+        <v>29</v>
+      </c>
+      <c r="K24" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>standard_liquor_color</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.002151715685267272</v>
+      </c>
+      <c r="D25" t="n">
+        <v>22</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.001395690074680656</v>
+      </c>
+      <c r="F25" t="n">
+        <v>28</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.0001417221139674907</v>
+      </c>
+      <c r="H25" t="n">
+        <v>32</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.1593929350952812</v>
+      </c>
+      <c r="J25" t="n">
+        <v>22</v>
+      </c>
+      <c r="K25" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>sweetwater_brix</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.00408366209339472</v>
+      </c>
+      <c r="D26" t="n">
+        <v>12</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.002037237381054784</v>
+      </c>
+      <c r="F26" t="n">
+        <v>20</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.0006843931404619585</v>
+      </c>
+      <c r="H26" t="n">
+        <v>53</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.1724460051318526</v>
+      </c>
+      <c r="J26" t="n">
+        <v>19</v>
+      </c>
+      <c r="K26" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.001921410431688985</v>
+      </c>
+      <c r="D27" t="n">
+        <v>27</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.001687484260549532</v>
+      </c>
+      <c r="F27" t="n">
+        <v>23</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.0002302416522495965</v>
+      </c>
+      <c r="H27" t="n">
+        <v>29</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.1465380298983885</v>
+      </c>
+      <c r="J27" t="n">
+        <v>27</v>
+      </c>
+      <c r="K27" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>raw_syrup_brix</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.001889097578054567</v>
+      </c>
+      <c r="D28" t="n">
+        <v>28</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.0008770449292562827</v>
+      </c>
+      <c r="F28" t="n">
+        <v>44</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.0007934977301886637</v>
+      </c>
+      <c r="H28" t="n">
+        <v>16</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.1703142646263009</v>
+      </c>
+      <c r="J28" t="n">
+        <v>20</v>
+      </c>
+      <c r="K28" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>sulphited_color</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.001669928206103682</v>
+      </c>
+      <c r="D29" t="n">
+        <v>30</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.001289182559551359</v>
+      </c>
+      <c r="F29" t="n">
+        <v>30</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.00022583206456539</v>
+      </c>
+      <c r="H29" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.1659753101927781</v>
+      </c>
+      <c r="J29" t="n">
+        <v>21</v>
+      </c>
+      <c r="K29" t="n">
+        <v>27.75</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>co2_percent</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.001875236354155498</v>
+      </c>
+      <c r="D30" t="n">
+        <v>29</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.001420542092449193</v>
+      </c>
+      <c r="F30" t="n">
+        <v>26</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-7.365142936333058e-05</v>
+      </c>
+      <c r="H30" t="n">
+        <v>47</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.194221959201021</v>
+      </c>
+      <c r="J30" t="n">
+        <v>16</v>
+      </c>
+      <c r="K30" t="n">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.001591884876387455</v>
+      </c>
+      <c r="D31" t="n">
+        <v>31</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.0008975503660924299</v>
+      </c>
+      <c r="F31" t="n">
+        <v>43</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.0003884077899509175</v>
+      </c>
+      <c r="H31" t="n">
+        <v>25</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.1487373275154553</v>
+      </c>
+      <c r="J31" t="n">
+        <v>24</v>
+      </c>
+      <c r="K31" t="n">
+        <v>30.75</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.001426620889287097</v>
+      </c>
+      <c r="D32" t="n">
+        <v>37</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.001233797996048181</v>
+      </c>
+      <c r="F32" t="n">
+        <v>32</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.0004180963464805232</v>
+      </c>
+      <c r="H32" t="n">
+        <v>22</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.1216199643191032</v>
+      </c>
+      <c r="J32" t="n">
+        <v>34</v>
+      </c>
+      <c r="K32" t="n">
+        <v>31.25</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.001444030739204453</v>
+      </c>
+      <c r="D33" t="n">
+        <v>36</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.0009588233178267449</v>
+      </c>
+      <c r="F33" t="n">
+        <v>40</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.0003107090366941456</v>
+      </c>
+      <c r="H33" t="n">
+        <v>27</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.151174213998134</v>
+      </c>
+      <c r="J33" t="n">
+        <v>23</v>
+      </c>
+      <c r="K33" t="n">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_2</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.001523330653525749</v>
+      </c>
+      <c r="D34" t="n">
+        <v>33</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.001660669792439465</v>
+      </c>
+      <c r="F34" t="n">
+        <v>24</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-6.373590530978079e-05</v>
+      </c>
+      <c r="H34" t="n">
+        <v>46</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.1469591885128838</v>
+      </c>
+      <c r="J34" t="n">
+        <v>26</v>
+      </c>
+      <c r="K34" t="n">
+        <v>32.25</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.001359182555521891</v>
+      </c>
+      <c r="D35" t="n">
+        <v>40</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.00114811963404087</v>
+      </c>
+      <c r="F35" t="n">
+        <v>33</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.0003296159210498528</v>
+      </c>
+      <c r="H35" t="n">
+        <v>26</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.1223398881841007</v>
+      </c>
+      <c r="J35" t="n">
+        <v>32</v>
+      </c>
+      <c r="K35" t="n">
+        <v>32.75</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.001977614688915244</v>
+      </c>
+      <c r="D36" t="n">
+        <v>24</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.001734285883287098</v>
+      </c>
+      <c r="F36" t="n">
+        <v>21</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-0.0002758897424568918</v>
+      </c>
+      <c r="H36" t="n">
+        <v>52</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.1001025315170314</v>
+      </c>
+      <c r="J36" t="n">
+        <v>36</v>
+      </c>
+      <c r="K36" t="n">
+        <v>33.25</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.001344698110801744</v>
+      </c>
+      <c r="D37" t="n">
+        <v>41</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.000987889877819074</v>
+      </c>
+      <c r="F37" t="n">
+        <v>39</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.0004121634172346678</v>
+      </c>
+      <c r="H37" t="n">
+        <v>23</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.1248616794782231</v>
+      </c>
+      <c r="J37" t="n">
+        <v>31</v>
+      </c>
+      <c r="K37" t="n">
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.001963595860471165</v>
+      </c>
+      <c r="D38" t="n">
+        <v>25</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.001509004654213302</v>
+      </c>
+      <c r="F38" t="n">
+        <v>25</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-0.0002712248262002226</v>
+      </c>
+      <c r="H38" t="n">
+        <v>51</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.1038703040238067</v>
+      </c>
+      <c r="J38" t="n">
+        <v>35</v>
+      </c>
+      <c r="K38" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.003560354189681795</v>
+      </c>
+      <c r="D39" t="n">
+        <v>15</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.00107041891465202</v>
+      </c>
+      <c r="F39" t="n">
+        <v>36</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-9.283608491720275e-05</v>
+      </c>
+      <c r="H39" t="n">
+        <v>48</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.06405133728471712</v>
+      </c>
+      <c r="J39" t="n">
+        <v>47</v>
+      </c>
+      <c r="K39" t="n">
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.001316667902269605</v>
+      </c>
+      <c r="D40" t="n">
+        <v>42</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.0009322712034206816</v>
+      </c>
+      <c r="F40" t="n">
+        <v>41</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.0004120665964465919</v>
+      </c>
+      <c r="H40" t="n">
+        <v>24</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.08955986934737403</v>
+      </c>
+      <c r="J40" t="n">
+        <v>40</v>
+      </c>
+      <c r="K40" t="n">
+        <v>36.75</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.001258645102917479</v>
+      </c>
+      <c r="D41" t="n">
+        <v>43</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.001109542528416572</v>
+      </c>
+      <c r="F41" t="n">
+        <v>35</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3.765699218412077e-05</v>
+      </c>
+      <c r="H41" t="n">
+        <v>36</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.09076655113070364</v>
+      </c>
+      <c r="J41" t="n">
+        <v>39</v>
+      </c>
+      <c r="K41" t="n">
+        <v>38.25</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.001496111232371845</v>
+      </c>
+      <c r="D42" t="n">
+        <v>34</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.001262299624090363</v>
+      </c>
+      <c r="F42" t="n">
+        <v>31</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-0.000101776812074128</v>
+      </c>
+      <c r="H42" t="n">
+        <v>50</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.08358444248332875</v>
+      </c>
+      <c r="J42" t="n">
+        <v>43</v>
+      </c>
+      <c r="K42" t="n">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.001359952927898525</v>
+      </c>
+      <c r="D43" t="n">
+        <v>39</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.000784844347555557</v>
+      </c>
+      <c r="F43" t="n">
+        <v>48</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-5.527578036852443e-05</v>
+      </c>
+      <c r="H43" t="n">
+        <v>43</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.1221860038175966</v>
+      </c>
+      <c r="J43" t="n">
+        <v>33</v>
+      </c>
+      <c r="K43" t="n">
+        <v>40.75</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>filtercake_moisture</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.001465618353457205</v>
+      </c>
+      <c r="D44" t="n">
+        <v>35</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.0009075890504689311</v>
+      </c>
+      <c r="F44" t="n">
+        <v>42</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-6.038959025872481e-05</v>
+      </c>
+      <c r="H44" t="n">
+        <v>44</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.07439785613225913</v>
+      </c>
+      <c r="J44" t="n">
+        <v>45</v>
+      </c>
+      <c r="K44" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.0009659162451454334</v>
+      </c>
+      <c r="D45" t="n">
+        <v>47</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.0010598954833534</v>
+      </c>
+      <c r="F45" t="n">
+        <v>37</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-3.437122920014745e-05</v>
+      </c>
+      <c r="H45" t="n">
+        <v>41</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.08619964502381627</v>
+      </c>
+      <c r="J45" t="n">
+        <v>41</v>
+      </c>
+      <c r="K45" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.001176834384073412</v>
+      </c>
+      <c r="D46" t="n">
+        <v>45</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.001040180910976187</v>
+      </c>
+      <c r="F46" t="n">
+        <v>38</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-2.648016097195338e-05</v>
+      </c>
+      <c r="H46" t="n">
+        <v>40</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.07780667667315466</v>
+      </c>
+      <c r="J46" t="n">
+        <v>44</v>
+      </c>
+      <c r="K46" t="n">
+        <v>41.75</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>filtercake_sugar</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.001188608104898267</v>
+      </c>
+      <c r="D47" t="n">
+        <v>44</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.0008679974287115135</v>
+      </c>
+      <c r="F47" t="n">
+        <v>45</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-9.551979519116794e-05</v>
+      </c>
+      <c r="H47" t="n">
+        <v>49</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.09944565930027194</v>
+      </c>
+      <c r="J47" t="n">
+        <v>37</v>
+      </c>
+      <c r="K47" t="n">
+        <v>43.75</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_2</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.0006072118167457299</v>
+      </c>
+      <c r="D48" t="n">
+        <v>48</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.0008294176686763347</v>
+      </c>
+      <c r="F48" t="n">
+        <v>46</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.0001129120157824182</v>
+      </c>
+      <c r="H48" t="n">
+        <v>33</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.03668306533699361</v>
+      </c>
+      <c r="J48" t="n">
+        <v>49</v>
+      </c>
+      <c r="K48" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_1</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.0005354569751638635</v>
+      </c>
+      <c r="D49" t="n">
+        <v>49</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.000791305892487536</v>
+      </c>
+      <c r="F49" t="n">
+        <v>47</v>
+      </c>
+      <c r="G49" t="n">
+        <v>5.64339309587325e-05</v>
+      </c>
+      <c r="H49" t="n">
+        <v>35</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.06806981505572551</v>
+      </c>
+      <c r="J49" t="n">
+        <v>46</v>
+      </c>
+      <c r="K49" t="n">
+        <v>44.25</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.001138441486449964</v>
+      </c>
+      <c r="D50" t="n">
+        <v>46</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.0006949217019225416</v>
+      </c>
+      <c r="F50" t="n">
+        <v>49</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-3.56381611746448e-05</v>
+      </c>
+      <c r="H50" t="n">
+        <v>42</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.03700780804195913</v>
+      </c>
+      <c r="J50" t="n">
+        <v>48</v>
+      </c>
+      <c r="K50" t="n">
+        <v>46.25</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>9.541043300902036e-05</v>
+      </c>
+      <c r="D51" t="n">
+        <v>50</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.0005583641966469675</v>
+      </c>
+      <c r="F51" t="n">
+        <v>50</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2.359375964066102e-05</v>
+      </c>
+      <c r="H51" t="n">
+        <v>38</v>
+      </c>
+      <c r="I51" t="n">
         <v>0</v>
       </c>
-      <c r="J24" t="n">
-        <v>23</v>
-      </c>
-      <c r="K24" t="n">
-        <v>22.25</v>
+      <c r="J51" t="n">
+        <v>52</v>
+      </c>
+      <c r="K51" t="n">
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>2.081146124410183e-05</v>
+      </c>
+      <c r="D52" t="n">
+        <v>53</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.0001398858186863133</v>
+      </c>
+      <c r="F52" t="n">
+        <v>53</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2.379094596458575e-05</v>
+      </c>
+      <c r="H52" t="n">
+        <v>37</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.02616468904652591</v>
+      </c>
+      <c r="J52" t="n">
+        <v>50</v>
+      </c>
+      <c r="K52" t="n">
+        <v>48.25</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>7.808758290207801e-05</v>
+      </c>
+      <c r="D53" t="n">
+        <v>51</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.0002184181996498549</v>
+      </c>
+      <c r="F53" t="n">
+        <v>52</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1.263266027967669e-05</v>
+      </c>
+      <c r="H53" t="n">
+        <v>39</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.01947477582113599</v>
+      </c>
+      <c r="J53" t="n">
+        <v>51</v>
+      </c>
+      <c r="K53" t="n">
+        <v>48.25</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>shift_name</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>7.721435030299638e-05</v>
+      </c>
+      <c r="D54" t="n">
+        <v>52</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.0003166854152453804</v>
+      </c>
+      <c r="F54" t="n">
+        <v>51</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-6.196392031168063e-05</v>
+      </c>
+      <c r="H54" t="n">
+        <v>45</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>52</v>
+      </c>
+      <c r="K54" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1423,25 +2533,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4786348643532474</v>
+        <v>0.4065729105196067</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3762015255356469</v>
+        <v>0.3291493018522236</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6232002183142639</v>
+        <v>0.4644109321358291</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.346260559415132</v>
+        <v>1.438671876188928</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -1460,25 +2570,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.3098513501376765</v>
+        <v>0.2992099333553406</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2624451226637246</v>
+        <v>0.2291797279328061</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4047814927752794</v>
+        <v>0.2967604346712479</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1.315657187137866</v>
+        <v>1.423770799533282</v>
       </c>
       <c r="J3" t="n">
         <v>3</v>
@@ -1497,25 +2607,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.06980168567350829</v>
+        <v>0.07043117580663896</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08470205394166801</v>
+        <v>0.07192762145117108</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07276763467443288</v>
+        <v>0.024694422256211</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8451519580197258</v>
+        <v>0.947515211524121</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
@@ -1534,31 +2644,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03392125819245912</v>
+        <v>0.04282009912729453</v>
       </c>
       <c r="D5" t="n">
         <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1439102514616759</v>
+        <v>0.1558290110023217</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008169226868447944</v>
+        <v>0.005706524045798944</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8103699164537534</v>
+        <v>0.8392709336065023</v>
       </c>
       <c r="J5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" t="n">
         <v>5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.25</v>
       </c>
     </row>
     <row r="6">
@@ -1571,31 +2681,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01242469539784901</v>
+        <v>0.007345090478667085</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07230265917906245</v>
+        <v>0.050508469336305</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.005106458936631621</v>
+        <v>0.001290483164256017</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>1.371659402701831</v>
+        <v>1.516185073214777</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>4.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="7">
@@ -1608,31 +2718,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.03503447106524671</v>
+        <v>0.06347889196297038</v>
       </c>
       <c r="D7" t="n">
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01178356171528505</v>
+        <v>0.01086974528925099</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007549312702406741</v>
+        <v>0.012058307620746</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>0.659958613808139</v>
+        <v>0.7102381910625768</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>5.25</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="8">
@@ -1641,35 +2751,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.005348600779763525</v>
+        <v>0.01424827950268244</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01099374852031951</v>
+        <v>0.0388937622385257</v>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003880400052873412</v>
+        <v>0.01167431989016168</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1482735288640082</v>
+        <v>0.2864599872107711</v>
       </c>
       <c r="J8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>7.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="9">
@@ -1678,35 +2788,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.00463989376297619</v>
+        <v>0.005953696622513246</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>0.008554197203700507</v>
+        <v>0.0110282599486145</v>
       </c>
       <c r="F9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.002388489583926789</v>
+      </c>
+      <c r="H9" t="n">
         <v>8</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.003883780624181632</v>
-      </c>
-      <c r="H9" t="n">
-        <v>7</v>
-      </c>
       <c r="I9" t="n">
-        <v>0.1322699898506867</v>
+        <v>0.2408345741623004</v>
       </c>
       <c r="J9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>8.75</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="10">
@@ -1715,35 +2825,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.006141089234745527</v>
+        <v>0.0058600638538843</v>
       </c>
       <c r="D10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.0120158828156668</v>
+      </c>
+      <c r="F10" t="n">
         <v>7</v>
       </c>
-      <c r="E10" t="n">
-        <v>0.003407463086655959</v>
-      </c>
-      <c r="F10" t="n">
-        <v>10</v>
-      </c>
       <c r="G10" t="n">
-        <v>0.0009873511723142102</v>
+        <v>0.002259821391015104</v>
       </c>
       <c r="H10" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1374615805992225</v>
+        <v>0.2066749365948048</v>
       </c>
       <c r="J10" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K10" t="n">
-        <v>9.5</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="11">
@@ -1752,35 +2862,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.004989664380578769</v>
+        <v>0.003732832738122984</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>0.002159270160746743</v>
+        <v>0.00371639329167186</v>
       </c>
       <c r="F11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G11" t="n">
-        <v>0.003578368583356606</v>
+        <v>0.002466793375889997</v>
       </c>
       <c r="H11" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.6266420055755306</v>
+      </c>
+      <c r="J11" t="n">
         <v>9</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.1112783347692781</v>
-      </c>
-      <c r="J11" t="n">
-        <v>11</v>
-      </c>
       <c r="K11" t="n">
-        <v>11</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="12">
@@ -1789,35 +2899,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.005532454955602316</v>
+        <v>0.005718097971075684</v>
       </c>
       <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.01114242239312433</v>
+      </c>
+      <c r="F12" t="n">
         <v>8</v>
       </c>
-      <c r="E12" t="n">
-        <v>0.003198662685508405</v>
-      </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
+        <v>0.001872568715010792</v>
+      </c>
+      <c r="H12" t="n">
         <v>11</v>
       </c>
-      <c r="G12" t="n">
-        <v>0.0007333918858249078</v>
-      </c>
-      <c r="H12" t="n">
-        <v>14</v>
-      </c>
       <c r="I12" t="n">
-        <v>0.07213303796757264</v>
+        <v>0.1927333513280312</v>
       </c>
       <c r="J12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K12" t="n">
-        <v>12.25</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="13">
@@ -1826,35 +2936,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.002734043432042849</v>
+        <v>0.003447581827407039</v>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E13" t="n">
-        <v>0.003869405558171784</v>
+        <v>0.005242163931629659</v>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>0.000721451771677295</v>
+        <v>0.0007476917004784811</v>
       </c>
       <c r="H13" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1167555227631789</v>
+        <v>0.8867983829986508</v>
       </c>
       <c r="J13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>13</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="14">
@@ -1863,35 +2973,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.004166440980821164</v>
+        <v>0.002388679605767266</v>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001692518774872319</v>
+        <v>0.004392508987762973</v>
       </c>
       <c r="F14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001854515844907234</v>
+        <v>0.001013569475495801</v>
       </c>
       <c r="H14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I14" t="n">
-        <v>0.07859573331795744</v>
+        <v>0.672769671377254</v>
       </c>
       <c r="J14" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K14" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="15">
@@ -1900,35 +3010,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.004065886073554982</v>
+        <v>0.003852124005685164</v>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
-        <v>0.001616983925291124</v>
+        <v>0.002072561167334866</v>
       </c>
       <c r="F15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001233759210154783</v>
+        <v>0.001972247393986859</v>
       </c>
       <c r="H15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1021684507793905</v>
+        <v>0.1482583563546349</v>
       </c>
       <c r="J15" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K15" t="n">
-        <v>14</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="16">
@@ -1937,35 +3047,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.004323760808917921</v>
+        <v>0.001933603185737217</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E16" t="n">
-        <v>0.00193933852238919</v>
+        <v>0.009198273584937154</v>
       </c>
       <c r="F16" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G16" t="n">
-        <v>0.001929100053758637</v>
+        <v>0.0002671008442111988</v>
       </c>
       <c r="H16" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01218160236218147</v>
+        <v>0.2678695621723715</v>
       </c>
       <c r="J16" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="K16" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -1974,35 +3084,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.003810996429117441</v>
+        <v>0.001590935227078281</v>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0024396892818847</v>
+        <v>0.002694814176495566</v>
       </c>
       <c r="F17" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.167182530903421e-06</v>
+        <v>0.0004935313015578035</v>
       </c>
       <c r="H17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I17" t="n">
-        <v>0.09634405678887825</v>
+        <v>0.2025258905133143</v>
       </c>
       <c r="J17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>15.25</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="18">
@@ -2011,35 +3121,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.00329161335759338</v>
+        <v>0.005213653768950966</v>
       </c>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>0.002069153113653987</v>
+        <v>0.001723245257052869</v>
       </c>
       <c r="F18" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G18" t="n">
-        <v>0.000568981263335111</v>
+        <v>0.001207182745202107</v>
       </c>
       <c r="H18" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I18" t="n">
-        <v>0.09752444756001344</v>
+        <v>0.09164550956329354</v>
       </c>
       <c r="J18" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="K18" t="n">
-        <v>15.25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -2048,35 +3158,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.003882389082831054</v>
+        <v>0.002141043114578652</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E19" t="n">
-        <v>0.002200132824558406</v>
+        <v>0.003472869175817386</v>
       </c>
       <c r="F19" t="n">
+        <v>16</v>
+      </c>
+      <c r="G19" t="n">
+        <v>7.578620613383214e-05</v>
+      </c>
+      <c r="H19" t="n">
+        <v>34</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2165485625793266</v>
+      </c>
+      <c r="J19" t="n">
         <v>13</v>
       </c>
-      <c r="G19" t="n">
-        <v>-0.0003473508515325241</v>
-      </c>
-      <c r="H19" t="n">
-        <v>23</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.04975117740217749</v>
-      </c>
-      <c r="J19" t="n">
-        <v>18</v>
-      </c>
       <c r="K19" t="n">
-        <v>17.25</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="20">
@@ -2085,35 +3195,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.002393279772807551</v>
+        <v>0.002390475329932857</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E20" t="n">
-        <v>0.00106253959687849</v>
+        <v>0.002589998571600898</v>
       </c>
       <c r="F20" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0003282113358627048</v>
+        <v>0.0008620481737081521</v>
       </c>
       <c r="H20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I20" t="n">
-        <v>0.03899607561514129</v>
+        <v>0.08446606360304898</v>
       </c>
       <c r="J20" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="K20" t="n">
-        <v>19.25</v>
+        <v>23.25</v>
       </c>
     </row>
     <row r="21">
@@ -2122,35 +3232,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.002132948626544079</v>
+        <v>0.002275603295886006</v>
       </c>
       <c r="D21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E21" t="n">
-        <v>0.001251485665618902</v>
+        <v>0.001409204688916107</v>
       </c>
       <c r="F21" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.620251328233735e-05</v>
+        <v>0.000442262914799052</v>
       </c>
       <c r="H21" t="n">
         <v>20</v>
       </c>
       <c r="I21" t="n">
-        <v>0.05786450899225626</v>
+        <v>0.1295419430619873</v>
       </c>
       <c r="J21" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K21" t="n">
-        <v>19.5</v>
+        <v>24.25</v>
       </c>
     </row>
   </sheetData>
@@ -2164,7 +3274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2194,7 +3304,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4786348643532474</v>
+        <v>0.4065729105196067</v>
       </c>
     </row>
     <row r="3">
@@ -2207,7 +3317,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.3098513501376765</v>
+        <v>0.2992099333553406</v>
       </c>
     </row>
     <row r="4">
@@ -2220,7 +3330,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.06980168567350829</v>
+        <v>0.07043117580663896</v>
       </c>
     </row>
     <row r="5">
@@ -2233,7 +3343,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.03503447106524671</v>
+        <v>0.06347889196297038</v>
       </c>
     </row>
     <row r="6">
@@ -2246,7 +3356,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.03392125819245912</v>
+        <v>0.04282009912729453</v>
       </c>
     </row>
     <row r="7">
@@ -2255,11 +3365,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01242469539784901</v>
+        <v>0.01424827950268244</v>
       </c>
     </row>
     <row r="8">
@@ -2268,11 +3378,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.006141089234745527</v>
+        <v>0.007345090478667085</v>
       </c>
     </row>
     <row r="9">
@@ -2281,11 +3391,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.005532454955602316</v>
+        <v>0.005953696622513246</v>
       </c>
     </row>
     <row r="10">
@@ -2294,11 +3404,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.005348600779763525</v>
+        <v>0.0058600638538843</v>
       </c>
     </row>
     <row r="11">
@@ -2307,11 +3417,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.004989664380578769</v>
+        <v>0.005718097971075684</v>
       </c>
     </row>
     <row r="12">
@@ -2320,11 +3430,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.00463989376297619</v>
+        <v>0.005213653768950966</v>
       </c>
     </row>
     <row r="13">
@@ -2333,11 +3443,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.004323760808917921</v>
+        <v>0.00408366209339472</v>
       </c>
     </row>
     <row r="14">
@@ -2346,11 +3456,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.004166440980821164</v>
+        <v>0.003852124005685164</v>
       </c>
     </row>
     <row r="15">
@@ -2359,11 +3469,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.004065886073554982</v>
+        <v>0.003732832738122984</v>
       </c>
     </row>
     <row r="16">
@@ -2372,11 +3482,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.003882389082831054</v>
+        <v>0.003560354189681795</v>
       </c>
     </row>
     <row r="17">
@@ -2385,11 +3495,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.003810996429117441</v>
+        <v>0.003447581827407039</v>
       </c>
     </row>
     <row r="18">
@@ -2398,11 +3508,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.00329161335759338</v>
+        <v>0.003162079358151949</v>
       </c>
     </row>
     <row r="19">
@@ -2411,11 +3521,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.002734043432042849</v>
+        <v>0.002390475329932857</v>
       </c>
     </row>
     <row r="20">
@@ -2424,11 +3534,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.002637019746055926</v>
+        <v>0.002388679605767266</v>
       </c>
     </row>
     <row r="21">
@@ -2437,11 +3547,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.002393279772807551</v>
+        <v>0.002275603295886006</v>
       </c>
     </row>
     <row r="22">
@@ -2450,11 +3560,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.002132948626544079</v>
+        <v>0.00227475211272811</v>
       </c>
     </row>
     <row r="23">
@@ -2463,11 +3573,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.00014564696738907</v>
+        <v>0.002151715685267272</v>
       </c>
     </row>
     <row r="24">
@@ -2476,11 +3586,401 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>raw_sugar_color</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.002141043114578652</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.001977614688915244</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.001963595860471165</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_1</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.001933603185737217</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.001921410431688985</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>raw_syrup_brix</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.001889097578054567</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>co2_percent</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.001875236354155498</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>sulphited_color</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.001669928206103682</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.001591884876387455</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>raw_syrup_color</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.001590935227078281</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_2</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.001523330653525749</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.001496111232371845</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>filtercake_moisture</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.001465618353457205</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.001444030739204453</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.001426620889287097</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.001395045957988709</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.001359952927898525</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.001359182555521891</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.001344698110801744</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.001316667902269605</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.001258645102917479</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>filtercake_sugar</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.001188608104898267</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.001176834384073412</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.001138441486449964</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.0009659162451454334</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.0006072118167457299</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_1</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.0005354569751638635</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>9.541043300902036e-05</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>7.808758290207801e-05</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>shift_name</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>7.721435030299638e-05</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>carbonated_alkalinity</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>9.59467886710826e-05</v>
+      <c r="C54" t="n">
+        <v>2.081146124410183e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2494,7 +3994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2524,7 +4024,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3762015255356469</v>
+        <v>0.3291493018522236</v>
       </c>
     </row>
     <row r="3">
@@ -2537,7 +4037,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2624451226637246</v>
+        <v>0.2291797279328061</v>
       </c>
     </row>
     <row r="4">
@@ -2550,7 +4050,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1439102514616759</v>
+        <v>0.1558290110023217</v>
       </c>
     </row>
     <row r="5">
@@ -2563,7 +4063,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.08470205394166801</v>
+        <v>0.07192762145117108</v>
       </c>
     </row>
     <row r="6">
@@ -2576,7 +4076,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.07230265917906245</v>
+        <v>0.050508469336305</v>
       </c>
     </row>
     <row r="7">
@@ -2585,11 +4085,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01178356171528505</v>
+        <v>0.0388937622385257</v>
       </c>
     </row>
     <row r="8">
@@ -2598,11 +4098,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01099374852031951</v>
+        <v>0.0120158828156668</v>
       </c>
     </row>
     <row r="9">
@@ -2611,11 +4111,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.008554197203700507</v>
+        <v>0.01114242239312433</v>
       </c>
     </row>
     <row r="10">
@@ -2624,11 +4124,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.003869405558171784</v>
+        <v>0.0110282599486145</v>
       </c>
     </row>
     <row r="11">
@@ -2637,11 +4137,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.003407463086655959</v>
+        <v>0.01086974528925099</v>
       </c>
     </row>
     <row r="12">
@@ -2650,11 +4150,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.003198662685508405</v>
+        <v>0.009198273584937154</v>
       </c>
     </row>
     <row r="13">
@@ -2663,11 +4163,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0024396892818847</v>
+        <v>0.009018698114905568</v>
       </c>
     </row>
     <row r="14">
@@ -2676,11 +4176,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.002200132824558406</v>
+        <v>0.005242163931629659</v>
       </c>
     </row>
     <row r="15">
@@ -2689,11 +4189,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.002159270160746743</v>
+        <v>0.004392508987762973</v>
       </c>
     </row>
     <row r="16">
@@ -2702,11 +4202,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.002069153113653987</v>
+        <v>0.00371639329167186</v>
       </c>
     </row>
     <row r="17">
@@ -2715,11 +4215,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.00193933852238919</v>
+        <v>0.003472869175817386</v>
       </c>
     </row>
     <row r="18">
@@ -2728,11 +4228,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.001692518774872319</v>
+        <v>0.002694814176495566</v>
       </c>
     </row>
     <row r="19">
@@ -2741,11 +4241,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.001616983925291124</v>
+        <v>0.002589998571600898</v>
       </c>
     </row>
     <row r="20">
@@ -2754,11 +4254,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.001544170109840377</v>
+        <v>0.002072561167334866</v>
       </c>
     </row>
     <row r="21">
@@ -2767,11 +4267,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.001251485665618902</v>
+        <v>0.002037237381054784</v>
       </c>
     </row>
     <row r="22">
@@ -2780,11 +4280,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.00106253959687849</v>
+        <v>0.001734285883287098</v>
       </c>
     </row>
     <row r="23">
@@ -2793,11 +4293,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0004263296390325067</v>
+        <v>0.001723245257052869</v>
       </c>
     </row>
     <row r="24">
@@ -2806,11 +4306,401 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.001687484260549532</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_2</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.001660669792439465</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.001509004654213302</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>co2_percent</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.001420542092449193</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>carbonated_pH</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.001409204688916107</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>standard_liquor_color</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.001395690074680656</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>lime_alkalinity</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.001366326113494094</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>sulphited_color</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.001289182559551359</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.001262299624090363</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.001233797996048181</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.00114811963404087</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.001137377474102061</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.001109542528416572</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.00107041891465202</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.0010598954833534</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.001040180910976187</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.000987889877819074</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.0009588233178267449</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.0009322712034206816</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>filtercake_moisture</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.0009075890504689311</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.0008975503660924299</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>raw_syrup_brix</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.0008770449292562827</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>filtercake_sugar</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.0008679974287115135</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_2</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.0008294176686763347</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.000791305892487536</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.000784844347555557</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.0006949217019225416</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.0005583641966469675</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>shift_name</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>0.0002297368338141414</v>
+      <c r="C52" t="n">
+        <v>0.0003166854152453804</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.0002184181996498549</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.0001398858186863133</v>
       </c>
     </row>
   </sheetData>
@@ -2824,7 +4714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2859,10 +4749,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.6232002183142639</v>
+        <v>0.4644109321358291</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05306065235424955</v>
+        <v>0.03549717864035256</v>
       </c>
     </row>
     <row r="3">
@@ -2875,10 +4765,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.4047814927752794</v>
+        <v>0.2967604346712479</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03653462564680818</v>
+        <v>0.02342329728454571</v>
       </c>
     </row>
     <row r="4">
@@ -2891,10 +4781,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.07276763467443288</v>
+        <v>0.024694422256211</v>
       </c>
       <c r="D4" t="n">
-        <v>0.009392463520798056</v>
+        <v>0.004005080789371391</v>
       </c>
     </row>
     <row r="5">
@@ -2903,14 +4793,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.008169226868447944</v>
+        <v>0.012058307620746</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002256999769260546</v>
+        <v>0.002441294292143661</v>
       </c>
     </row>
     <row r="6">
@@ -2919,14 +4809,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.007549312702406741</v>
+        <v>0.01167431989016168</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00237238301093225</v>
+        <v>0.003376003990564784</v>
       </c>
     </row>
     <row r="7">
@@ -2935,14 +4825,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.005106458936631621</v>
+        <v>0.005706524045798944</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0004352743591443926</v>
+        <v>0.001602583362467081</v>
       </c>
     </row>
     <row r="8">
@@ -2951,14 +4841,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.003883780624181632</v>
+        <v>0.002466793375889997</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0008866220814769228</v>
+        <v>0.0005446449769103998</v>
       </c>
     </row>
     <row r="9">
@@ -2967,14 +4857,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.003880400052873412</v>
+        <v>0.002388489583926789</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0009253796718779366</v>
+        <v>0.001123155441033117</v>
       </c>
     </row>
     <row r="10">
@@ -2983,14 +4873,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.003578368583356606</v>
+        <v>0.002259821391015104</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0007322498534449927</v>
+        <v>0.001307725882813622</v>
       </c>
     </row>
     <row r="11">
@@ -2999,14 +4889,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001929100053758637</v>
+        <v>0.001972247393986859</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0004504609381813358</v>
+        <v>0.000673894347961945</v>
       </c>
     </row>
     <row r="12">
@@ -3015,14 +4905,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001854515844907234</v>
+        <v>0.001872568715010792</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0004923420366203749</v>
+        <v>0.001182416370468522</v>
       </c>
     </row>
     <row r="13">
@@ -3031,14 +4921,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001233759210154783</v>
+        <v>0.001290483164256017</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0005135413578850646</v>
+        <v>0.0001487101031429475</v>
       </c>
     </row>
     <row r="14">
@@ -3047,14 +4937,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0009873511723142102</v>
+        <v>0.001207182745202107</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00142807515181357</v>
+        <v>0.0006916333620356273</v>
       </c>
     </row>
     <row r="15">
@@ -3063,14 +4953,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0007333918858249078</v>
+        <v>0.001013569475495801</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0009356936823701181</v>
+        <v>0.000219737615080493</v>
       </c>
     </row>
     <row r="16">
@@ -3079,14 +4969,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.000721451771677295</v>
+        <v>0.0008620481737081521</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0002108177305842748</v>
+        <v>0.0004658090871524526</v>
       </c>
     </row>
     <row r="17">
@@ -3095,14 +4985,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.000568981263335111</v>
+        <v>0.0007934977301886637</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0003180606030386977</v>
+        <v>0.0004461399874994551</v>
       </c>
     </row>
     <row r="18">
@@ -3111,14 +5001,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0003282113358627048</v>
+        <v>0.0007476917004784811</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0002568117037166731</v>
+        <v>0.0002500388049779063</v>
       </c>
     </row>
     <row r="19">
@@ -3127,14 +5017,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.229772772206484e-05</v>
+        <v>0.0004935313015578035</v>
       </c>
       <c r="D19" t="n">
-        <v>6.843683156359045e-05</v>
+        <v>0.0002204942295493655</v>
       </c>
     </row>
     <row r="20">
@@ -3143,14 +5033,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-1.167182530903421e-06</v>
+        <v>0.0004730488266915911</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0005568072169461274</v>
+        <v>0.0001914563339534192</v>
       </c>
     </row>
     <row r="21">
@@ -3159,14 +5049,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-1.620251328233735e-05</v>
+        <v>0.000442262914799052</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0002756945559667091</v>
+        <v>0.0004231547766509931</v>
       </c>
     </row>
     <row r="22">
@@ -3175,14 +5065,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.0001222522612605914</v>
+        <v>0.0004357877178527647</v>
       </c>
       <c r="D22" t="n">
-        <v>6.889359792420199e-05</v>
+        <v>0.0001530037576485963</v>
       </c>
     </row>
     <row r="23">
@@ -3191,14 +5081,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.0001381729846377189</v>
+        <v>0.0004180963464805232</v>
       </c>
       <c r="D23" t="n">
-        <v>0.000314219546561292</v>
+        <v>0.0002110457267646741</v>
       </c>
     </row>
     <row r="24">
@@ -3211,10 +5101,490 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.0003473508515325241</v>
+        <v>0.0004121634172346678</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0008780012764922702</v>
+        <v>6.747963274954377e-05</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.0004120665964465919</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.0001753621395826464</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.0003884077899509175</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0002822183452349483</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0003296159210498528</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.0002172008167586282</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.0003107090366941456</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.0002604431644270943</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_1</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.0002671008442111988</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.0005101564343019422</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.0002302416522495965</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.00032710890235772</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>sulphited_color</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.00022583206456539</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.0002072438723495389</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.0001723422210909487</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.0004995759723323198</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>standard_liquor_color</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.0001417221139674907</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.0005062690086954426</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_2</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.0001129120157824182</v>
+      </c>
+      <c r="D34" t="n">
+        <v>7.795468474213297e-05</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>raw_sugar_color</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>7.578620613383214e-05</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.0001969758556252328</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_1</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>5.64339309587325e-05</v>
+      </c>
+      <c r="D36" t="n">
+        <v>8.621437876058255e-05</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>3.765699218412077e-05</v>
+      </c>
+      <c r="D37" t="n">
+        <v>7.888138603156475e-05</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2.379094596458575e-05</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3.079025050250309e-06</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2.359375964066102e-05</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.000100442147474817</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1.263266027967669e-05</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.484136921243061e-05</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>-2.648016097195338e-05</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.0001247597014616041</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>-3.437122920014745e-05</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.00010374808482088</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>-3.56381611746448e-05</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.0001082722951239124</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>-5.527578036852443e-05</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.0001356301504080066</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>filtercake_moisture</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>-6.038959025872481e-05</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.0002244041977878531</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>shift_name</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>-6.196392031168063e-05</v>
+      </c>
+      <c r="D46" t="n">
+        <v>3.097646177964852e-05</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_2</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>-6.373590530978079e-05</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.0001397211470996033</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>co2_percent</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>-7.365142936333058e-05</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.0001738436671129332</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>-9.283608491720275e-05</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.0005584237535329586</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>filtercake_sugar</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>-9.551979519116794e-05</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.0001495331024290458</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.000101776812074128</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.0002136165199502884</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.0002712248262002226</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.0002342011045836815</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.0002758897424568918</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.0002922624587833737</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>sweetwater_brix</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.0006843931404619585</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.0003616293825289954</v>
       </c>
     </row>
   </sheetData>
@@ -3228,7 +5598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3258,7 +5628,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.371659402701831</v>
+        <v>1.516185073214777</v>
       </c>
     </row>
     <row r="3">
@@ -3271,7 +5641,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.346260559415132</v>
+        <v>1.438671876188928</v>
       </c>
     </row>
     <row r="4">
@@ -3284,7 +5654,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.315657187137866</v>
+        <v>1.423770799533282</v>
       </c>
     </row>
     <row r="5">
@@ -3297,7 +5667,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8451519580197258</v>
+        <v>0.947515211524121</v>
       </c>
     </row>
     <row r="6">
@@ -3306,11 +5676,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8103699164537534</v>
+        <v>0.8867983829986508</v>
       </c>
     </row>
     <row r="7">
@@ -3319,11 +5689,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.659958613808139</v>
+        <v>0.8392709336065023</v>
       </c>
     </row>
     <row r="8">
@@ -3332,11 +5702,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1482735288640082</v>
+        <v>0.7102381910625768</v>
       </c>
     </row>
     <row r="9">
@@ -3345,11 +5715,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.1374615805992225</v>
+        <v>0.672769671377254</v>
       </c>
     </row>
     <row r="10">
@@ -3358,11 +5728,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.1322699898506867</v>
+        <v>0.6266420055755306</v>
       </c>
     </row>
     <row r="11">
@@ -3371,11 +5741,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.1167555227631789</v>
+        <v>0.2864599872107711</v>
       </c>
     </row>
     <row r="12">
@@ -3384,11 +5754,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.1112783347692781</v>
+        <v>0.2678695621723715</v>
       </c>
     </row>
     <row r="13">
@@ -3397,11 +5767,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.1021684507793905</v>
+        <v>0.2408345741623004</v>
       </c>
     </row>
     <row r="14">
@@ -3410,11 +5780,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.09752444756001344</v>
+        <v>0.2165485625793266</v>
       </c>
     </row>
     <row r="15">
@@ -3423,11 +5793,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.09634405678887825</v>
+        <v>0.2066749365948048</v>
       </c>
     </row>
     <row r="16">
@@ -3436,11 +5806,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.07859573331795744</v>
+        <v>0.2025258905133143</v>
       </c>
     </row>
     <row r="17">
@@ -3449,11 +5819,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.07213303796757264</v>
+        <v>0.194221959201021</v>
       </c>
     </row>
     <row r="18">
@@ -3462,11 +5832,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.05786450899225626</v>
+        <v>0.1927333513280312</v>
       </c>
     </row>
     <row r="19">
@@ -3475,11 +5845,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.04975117740217749</v>
+        <v>0.1921799270615958</v>
       </c>
     </row>
     <row r="20">
@@ -3488,11 +5858,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.03899607561514129</v>
+        <v>0.1724460051318526</v>
       </c>
     </row>
     <row r="21">
@@ -3501,11 +5871,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.03770165826434724</v>
+        <v>0.1703142646263009</v>
       </c>
     </row>
     <row r="22">
@@ -3514,11 +5884,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.03239086953742176</v>
+        <v>0.1659753101927781</v>
       </c>
     </row>
     <row r="23">
@@ -3527,11 +5897,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.01218160236218147</v>
+        <v>0.1593929350952812</v>
       </c>
     </row>
     <row r="24">
@@ -3540,10 +5910,400 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.151174213998134</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.1487373275154553</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>white_quality_ash_1</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.1482583563546349</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>white_quality_solution_color_2</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.1469591885128838</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.1465380298983885</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>lime_alkalinity</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.1430346516538337</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>work_period</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.1361843957214524</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>carbonated_pH</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.1295419430619873</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.1248616794782231</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.1223398881841007</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.1221860038175966</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.1216199643191032</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.1038703040238067</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.1001025315170314</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>filtercake_sugar</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.09944565930027194</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>boiler_tds</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.09164550956329354</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.09076655113070364</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.08955986934737403</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.08619964502381627</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>boiler_alkalinity</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.08446606360304898</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.08358444248332875</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.07780667667315466</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>filtercake_moisture</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.07439785613225913</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_1</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.06806981505572551</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.06405133728471712</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.03700780804195913</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>white_quality_moisture_2</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.03668306533699361</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0.02616468904652591</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.01947477582113599</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>shift_name</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3595,17 +6355,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>755</v>
+        <v>788</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="D2" t="n">
-        <v>400</v>
+        <v>446</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-11 04:45:54 UTC</t>
+          <t>2026-06-11 05:05:58 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_apparent_color.xlsx
+++ b/NN/reports/feature_importance_white_apparent_color.xlsx
@@ -550,7 +550,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2967604346712479</v>
+        <v>0.2967604346712478</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -587,7 +587,7 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.024694422256211</v>
+        <v>0.02469442225621099</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -624,7 +624,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005706524045798944</v>
+        <v>0.005706524045798933</v>
       </c>
       <c r="H5" t="n">
         <v>6</v>
@@ -661,7 +661,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001290483164256017</v>
+        <v>0.001290483164255839</v>
       </c>
       <c r="H6" t="n">
         <v>12</v>
@@ -698,7 +698,7 @@
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>0.012058307620746</v>
+        <v>0.01205830762074601</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
@@ -735,7 +735,7 @@
         <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01167431989016168</v>
+        <v>0.01167431989016169</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
@@ -772,7 +772,7 @@
         <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002388489583926789</v>
+        <v>0.002388489583926767</v>
       </c>
       <c r="H9" t="n">
         <v>8</v>
@@ -846,7 +846,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002466793375889997</v>
+        <v>0.002466793375890008</v>
       </c>
       <c r="H11" t="n">
         <v>7</v>
@@ -883,7 +883,7 @@
         <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001872568715010792</v>
+        <v>0.001872568715010758</v>
       </c>
       <c r="H12" t="n">
         <v>11</v>
@@ -920,7 +920,7 @@
         <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0007476917004784811</v>
+        <v>0.0007476917004785144</v>
       </c>
       <c r="H13" t="n">
         <v>17</v>
@@ -957,7 +957,7 @@
         <v>14</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001013569475495801</v>
+        <v>0.001013569475495835</v>
       </c>
       <c r="H14" t="n">
         <v>14</v>
@@ -994,7 +994,7 @@
         <v>19</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001972247393986859</v>
+        <v>0.001972247393986837</v>
       </c>
       <c r="H15" t="n">
         <v>10</v>
@@ -1068,7 +1068,7 @@
         <v>17</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004935313015578035</v>
+        <v>0.0004935313015577925</v>
       </c>
       <c r="H17" t="n">
         <v>18</v>
@@ -1105,7 +1105,7 @@
         <v>22</v>
       </c>
       <c r="G18" t="n">
-        <v>0.001207182745202107</v>
+        <v>0.001207182745202129</v>
       </c>
       <c r="H18" t="n">
         <v>13</v>
@@ -1179,7 +1179,7 @@
         <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0008620481737081521</v>
+        <v>0.0008620481737081409</v>
       </c>
       <c r="H20" t="n">
         <v>15</v>
@@ -1253,7 +1253,7 @@
         <v>29</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0004730488266915911</v>
+        <v>0.00047304882669158</v>
       </c>
       <c r="H22" t="n">
         <v>19</v>
@@ -1290,7 +1290,7 @@
         <v>34</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0001723422210909487</v>
+        <v>0.0001723422210909709</v>
       </c>
       <c r="H23" t="n">
         <v>31</v>
@@ -1438,7 +1438,7 @@
         <v>23</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0002302416522495965</v>
+        <v>0.0002302416522496187</v>
       </c>
       <c r="H27" t="n">
         <v>29</v>
@@ -1512,7 +1512,7 @@
         <v>30</v>
       </c>
       <c r="G29" t="n">
-        <v>0.00022583206456539</v>
+        <v>0.0002258320645653788</v>
       </c>
       <c r="H29" t="n">
         <v>30</v>
@@ -1586,7 +1586,7 @@
         <v>43</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0003884077899509175</v>
+        <v>0.0003884077899509064</v>
       </c>
       <c r="H31" t="n">
         <v>25</v>
@@ -1623,7 +1623,7 @@
         <v>32</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0004180963464805232</v>
+        <v>0.0004180963464805121</v>
       </c>
       <c r="H32" t="n">
         <v>22</v>
@@ -1660,7 +1660,7 @@
         <v>40</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0003107090366941456</v>
+        <v>0.0003107090366941567</v>
       </c>
       <c r="H33" t="n">
         <v>27</v>
@@ -1771,7 +1771,7 @@
         <v>21</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.0002758897424568918</v>
+        <v>-0.0002758897424568807</v>
       </c>
       <c r="H36" t="n">
         <v>52</v>
@@ -1808,7 +1808,7 @@
         <v>39</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0004121634172346678</v>
+        <v>0.0004121634172346899</v>
       </c>
       <c r="H37" t="n">
         <v>23</v>
@@ -1845,7 +1845,7 @@
         <v>25</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.0002712248262002226</v>
+        <v>-0.0002712248262002337</v>
       </c>
       <c r="H38" t="n">
         <v>51</v>
@@ -1882,7 +1882,7 @@
         <v>36</v>
       </c>
       <c r="G39" t="n">
-        <v>-9.283608491720275e-05</v>
+        <v>-9.283608491721385e-05</v>
       </c>
       <c r="H39" t="n">
         <v>48</v>
@@ -1919,7 +1919,7 @@
         <v>41</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0004120665964465919</v>
+        <v>0.0004120665964466142</v>
       </c>
       <c r="H40" t="n">
         <v>24</v>
@@ -1956,7 +1956,7 @@
         <v>35</v>
       </c>
       <c r="G41" t="n">
-        <v>3.765699218412077e-05</v>
+        <v>3.765699218413188e-05</v>
       </c>
       <c r="H41" t="n">
         <v>36</v>
@@ -1993,7 +1993,7 @@
         <v>31</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.000101776812074128</v>
+        <v>-0.0001017768120741169</v>
       </c>
       <c r="H42" t="n">
         <v>50</v>
@@ -2030,7 +2030,7 @@
         <v>48</v>
       </c>
       <c r="G43" t="n">
-        <v>-5.527578036852443e-05</v>
+        <v>-5.527578036853553e-05</v>
       </c>
       <c r="H43" t="n">
         <v>43</v>
@@ -2067,7 +2067,7 @@
         <v>42</v>
       </c>
       <c r="G44" t="n">
-        <v>-6.038959025872481e-05</v>
+        <v>-6.038959025870261e-05</v>
       </c>
       <c r="H44" t="n">
         <v>44</v>
@@ -2104,7 +2104,7 @@
         <v>37</v>
       </c>
       <c r="G45" t="n">
-        <v>-3.437122920014745e-05</v>
+        <v>-3.437122920015856e-05</v>
       </c>
       <c r="H45" t="n">
         <v>41</v>
@@ -2141,7 +2141,7 @@
         <v>38</v>
       </c>
       <c r="G46" t="n">
-        <v>-2.648016097195338e-05</v>
+        <v>-2.648016097196448e-05</v>
       </c>
       <c r="H46" t="n">
         <v>40</v>
@@ -2178,7 +2178,7 @@
         <v>45</v>
       </c>
       <c r="G47" t="n">
-        <v>-9.551979519116794e-05</v>
+        <v>-9.551979519119014e-05</v>
       </c>
       <c r="H47" t="n">
         <v>49</v>
@@ -2215,7 +2215,7 @@
         <v>46</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0001129120157824182</v>
+        <v>0.0001129120157824515</v>
       </c>
       <c r="H48" t="n">
         <v>33</v>
@@ -2363,7 +2363,7 @@
         <v>53</v>
       </c>
       <c r="G52" t="n">
-        <v>2.379094596458575e-05</v>
+        <v>2.379094596457465e-05</v>
       </c>
       <c r="H52" t="n">
         <v>37</v>
@@ -2400,7 +2400,7 @@
         <v>52</v>
       </c>
       <c r="G53" t="n">
-        <v>1.263266027967669e-05</v>
+        <v>1.263266027968779e-05</v>
       </c>
       <c r="H53" t="n">
         <v>39</v>
@@ -2582,7 +2582,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2967604346712479</v>
+        <v>0.2967604346712478</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -2619,7 +2619,7 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.024694422256211</v>
+        <v>0.02469442225621099</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -2656,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005706524045798944</v>
+        <v>0.005706524045798933</v>
       </c>
       <c r="H5" t="n">
         <v>6</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001290483164256017</v>
+        <v>0.001290483164255839</v>
       </c>
       <c r="H6" t="n">
         <v>12</v>
@@ -2730,7 +2730,7 @@
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>0.012058307620746</v>
+        <v>0.01205830762074601</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
@@ -2767,7 +2767,7 @@
         <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01167431989016168</v>
+        <v>0.01167431989016169</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
@@ -2804,7 +2804,7 @@
         <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002388489583926789</v>
+        <v>0.002388489583926767</v>
       </c>
       <c r="H9" t="n">
         <v>8</v>
@@ -2878,7 +2878,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002466793375889997</v>
+        <v>0.002466793375890008</v>
       </c>
       <c r="H11" t="n">
         <v>7</v>
@@ -2915,7 +2915,7 @@
         <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001872568715010792</v>
+        <v>0.001872568715010758</v>
       </c>
       <c r="H12" t="n">
         <v>11</v>
@@ -2952,7 +2952,7 @@
         <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0007476917004784811</v>
+        <v>0.0007476917004785144</v>
       </c>
       <c r="H13" t="n">
         <v>17</v>
@@ -2989,7 +2989,7 @@
         <v>14</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001013569475495801</v>
+        <v>0.001013569475495835</v>
       </c>
       <c r="H14" t="n">
         <v>14</v>
@@ -3026,7 +3026,7 @@
         <v>19</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001972247393986859</v>
+        <v>0.001972247393986837</v>
       </c>
       <c r="H15" t="n">
         <v>10</v>
@@ -3100,7 +3100,7 @@
         <v>17</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004935313015578035</v>
+        <v>0.0004935313015577925</v>
       </c>
       <c r="H17" t="n">
         <v>18</v>
@@ -3137,7 +3137,7 @@
         <v>22</v>
       </c>
       <c r="G18" t="n">
-        <v>0.001207182745202107</v>
+        <v>0.001207182745202129</v>
       </c>
       <c r="H18" t="n">
         <v>13</v>
@@ -3211,7 +3211,7 @@
         <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0008620481737081521</v>
+        <v>0.0008620481737081409</v>
       </c>
       <c r="H20" t="n">
         <v>15</v>
@@ -4752,7 +4752,7 @@
         <v>0.4644109321358291</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03549717864035256</v>
+        <v>0.03549717864035253</v>
       </c>
     </row>
     <row r="3">
@@ -4765,10 +4765,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2967604346712479</v>
+        <v>0.2967604346712478</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02342329728454571</v>
+        <v>0.02342329728454565</v>
       </c>
     </row>
     <row r="4">
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.024694422256211</v>
+        <v>0.02469442225621099</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004005080789371391</v>
+        <v>0.004005080789371404</v>
       </c>
     </row>
     <row r="5">
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.012058307620746</v>
+        <v>0.01205830762074601</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002441294292143661</v>
+        <v>0.002441294292143686</v>
       </c>
     </row>
     <row r="6">
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01167431989016168</v>
+        <v>0.01167431989016169</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003376003990564784</v>
+        <v>0.003376003990564829</v>
       </c>
     </row>
     <row r="7">
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.005706524045798944</v>
+        <v>0.005706524045798933</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001602583362467081</v>
+        <v>0.001602583362467121</v>
       </c>
     </row>
     <row r="8">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.002466793375889997</v>
+        <v>0.002466793375890008</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0005446449769103998</v>
+        <v>0.0005446449769103913</v>
       </c>
     </row>
     <row r="9">
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.002388489583926789</v>
+        <v>0.002388489583926767</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001123155441033117</v>
+        <v>0.001123155441033116</v>
       </c>
     </row>
     <row r="10">
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001972247393986859</v>
+        <v>0.001972247393986837</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000673894347961945</v>
+        <v>0.0006738943479619148</v>
       </c>
     </row>
     <row r="12">
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001872568715010792</v>
+        <v>0.001872568715010758</v>
       </c>
       <c r="D12" t="n">
-        <v>0.001182416370468522</v>
+        <v>0.001182416370468517</v>
       </c>
     </row>
     <row r="13">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001290483164256017</v>
+        <v>0.001290483164255839</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0001487101031429475</v>
+        <v>0.0001487101031427858</v>
       </c>
     </row>
     <row r="14">
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.001207182745202107</v>
+        <v>0.001207182745202129</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0006916333620356273</v>
+        <v>0.0006916333620356577</v>
       </c>
     </row>
     <row r="15">
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.001013569475495801</v>
+        <v>0.001013569475495835</v>
       </c>
       <c r="D15" t="n">
-        <v>0.000219737615080493</v>
+        <v>0.0002197376150804986</v>
       </c>
     </row>
     <row r="16">
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0008620481737081521</v>
+        <v>0.0008620481737081409</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0004658090871524526</v>
+        <v>0.0004658090871524794</v>
       </c>
     </row>
     <row r="17">
@@ -4992,7 +4992,7 @@
         <v>0.0007934977301886637</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0004461399874994551</v>
+        <v>0.0004461399874994465</v>
       </c>
     </row>
     <row r="18">
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0007476917004784811</v>
+        <v>0.0007476917004785144</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0002500388049779063</v>
+        <v>0.000250038804977906</v>
       </c>
     </row>
     <row r="19">
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0004935313015578035</v>
+        <v>0.0004935313015577925</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0002204942295493655</v>
+        <v>0.0002204942295493547</v>
       </c>
     </row>
     <row r="20">
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.0004730488266915911</v>
+        <v>0.00047304882669158</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0001914563339534192</v>
+        <v>0.0001914563339534164</v>
       </c>
     </row>
     <row r="21">
@@ -5056,7 +5056,7 @@
         <v>0.000442262914799052</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0004231547766509931</v>
+        <v>0.0004231547766510074</v>
       </c>
     </row>
     <row r="22">
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0004180963464805232</v>
+        <v>0.0004180963464805121</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0002110457267646741</v>
+        <v>0.0002110457267646595</v>
       </c>
     </row>
     <row r="24">
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0004121634172346678</v>
+        <v>0.0004121634172346899</v>
       </c>
       <c r="D24" t="n">
-        <v>6.747963274954377e-05</v>
+        <v>6.747963274953249e-05</v>
       </c>
     </row>
     <row r="25">
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0004120665964465919</v>
+        <v>0.0004120665964466142</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0001753621395826464</v>
+        <v>0.0001753621395826426</v>
       </c>
     </row>
     <row r="26">
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0003884077899509175</v>
+        <v>0.0003884077899509064</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0002822183452349483</v>
+        <v>0.0002822183452349382</v>
       </c>
     </row>
     <row r="27">
@@ -5152,7 +5152,7 @@
         <v>0.0003296159210498528</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0002172008167586282</v>
+        <v>0.0002172008167585849</v>
       </c>
     </row>
     <row r="28">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0003107090366941456</v>
+        <v>0.0003107090366941567</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0002604431644270943</v>
+        <v>0.0002604431644271064</v>
       </c>
     </row>
     <row r="29">
@@ -5184,7 +5184,7 @@
         <v>0.0002671008442111988</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0005101564343019422</v>
+        <v>0.0005101564343019618</v>
       </c>
     </row>
     <row r="30">
@@ -5197,10 +5197,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0002302416522495965</v>
+        <v>0.0002302416522496187</v>
       </c>
       <c r="D30" t="n">
-        <v>0.00032710890235772</v>
+        <v>0.0003271089023577292</v>
       </c>
     </row>
     <row r="31">
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.00022583206456539</v>
+        <v>0.0002258320645653788</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0002072438723495389</v>
+        <v>0.0002072438723495021</v>
       </c>
     </row>
     <row r="32">
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0001723422210909487</v>
+        <v>0.0001723422210909709</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0004995759723323198</v>
+        <v>0.0004995759723323336</v>
       </c>
     </row>
     <row r="33">
@@ -5248,7 +5248,7 @@
         <v>0.0001417221139674907</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0005062690086954426</v>
+        <v>0.0005062690086954437</v>
       </c>
     </row>
     <row r="34">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0001129120157824182</v>
+        <v>0.0001129120157824515</v>
       </c>
       <c r="D34" t="n">
-        <v>7.795468474213297e-05</v>
+        <v>7.795468474211582e-05</v>
       </c>
     </row>
     <row r="35">
@@ -5296,7 +5296,7 @@
         <v>5.64339309587325e-05</v>
       </c>
       <c r="D36" t="n">
-        <v>8.621437876058255e-05</v>
+        <v>8.621437876059603e-05</v>
       </c>
     </row>
     <row r="37">
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3.765699218412077e-05</v>
+        <v>3.765699218413188e-05</v>
       </c>
       <c r="D37" t="n">
-        <v>7.888138603156475e-05</v>
+        <v>7.888138603156212e-05</v>
       </c>
     </row>
     <row r="38">
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2.379094596458575e-05</v>
+        <v>2.379094596457465e-05</v>
       </c>
       <c r="D38" t="n">
-        <v>3.079025050250309e-06</v>
+        <v>3.079025050264498e-06</v>
       </c>
     </row>
     <row r="39">
@@ -5344,7 +5344,7 @@
         <v>2.359375964066102e-05</v>
       </c>
       <c r="D39" t="n">
-        <v>0.000100442147474817</v>
+        <v>0.0001004421474748148</v>
       </c>
     </row>
     <row r="40">
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1.263266027967669e-05</v>
+        <v>1.263266027968779e-05</v>
       </c>
       <c r="D40" t="n">
-        <v>1.484136921243061e-05</v>
+        <v>1.484136921244717e-05</v>
       </c>
     </row>
     <row r="41">
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-2.648016097195338e-05</v>
+        <v>-2.648016097196448e-05</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0001247597014616041</v>
+        <v>0.0001247597014616126</v>
       </c>
     </row>
     <row r="42">
@@ -5389,10 +5389,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-3.437122920014745e-05</v>
+        <v>-3.437122920015856e-05</v>
       </c>
       <c r="D42" t="n">
-        <v>0.00010374808482088</v>
+        <v>0.000103748084820849</v>
       </c>
     </row>
     <row r="43">
@@ -5408,7 +5408,7 @@
         <v>-3.56381611746448e-05</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0001082722951239124</v>
+        <v>0.0001082722951239288</v>
       </c>
     </row>
     <row r="44">
@@ -5421,10 +5421,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-5.527578036852443e-05</v>
+        <v>-5.527578036853553e-05</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0001356301504080066</v>
+        <v>0.0001356301504080031</v>
       </c>
     </row>
     <row r="45">
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-6.038959025872481e-05</v>
+        <v>-6.038959025870261e-05</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0002244041977878531</v>
+        <v>0.0002244041977878227</v>
       </c>
     </row>
     <row r="46">
@@ -5456,7 +5456,7 @@
         <v>-6.196392031168063e-05</v>
       </c>
       <c r="D46" t="n">
-        <v>3.097646177964852e-05</v>
+        <v>3.097646177965357e-05</v>
       </c>
     </row>
     <row r="47">
@@ -5472,7 +5472,7 @@
         <v>-6.373590530978079e-05</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0001397211470996033</v>
+        <v>0.0001397211470996247</v>
       </c>
     </row>
     <row r="48">
@@ -5488,7 +5488,7 @@
         <v>-7.365142936333058e-05</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0001738436671129332</v>
+        <v>0.0001738436671129335</v>
       </c>
     </row>
     <row r="49">
@@ -5501,10 +5501,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-9.283608491720275e-05</v>
+        <v>-9.283608491721385e-05</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0005584237535329586</v>
+        <v>0.0005584237535329543</v>
       </c>
     </row>
     <row r="50">
@@ -5517,10 +5517,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-9.551979519116794e-05</v>
+        <v>-9.551979519119014e-05</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0001495331024290458</v>
+        <v>0.0001495331024290542</v>
       </c>
     </row>
     <row r="51">
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-0.000101776812074128</v>
+        <v>-0.0001017768120741169</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0002136165199502884</v>
+        <v>0.0002136165199503166</v>
       </c>
     </row>
     <row r="52">
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.0002712248262002226</v>
+        <v>-0.0002712248262002337</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0002342011045836815</v>
+        <v>0.0002342011045836843</v>
       </c>
     </row>
     <row r="53">
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.0002758897424568918</v>
+        <v>-0.0002758897424568807</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0002922624587833737</v>
+        <v>0.0002922624587833606</v>
       </c>
     </row>
     <row r="54">
@@ -5584,7 +5584,7 @@
         <v>-0.0006843931404619585</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0003616293825289954</v>
+        <v>0.0003616293825289796</v>
       </c>
     </row>
   </sheetData>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-11 05:05:58 UTC</t>
+          <t>2026-06-11 09:49:48 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_apparent_color.xlsx
+++ b/NN/reports/feature_importance_white_apparent_color.xlsx
@@ -501,25 +501,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4065729105196067</v>
+        <v>0.4165063630280615</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3291493018522236</v>
+        <v>0.3306041230813141</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4644109321358291</v>
+        <v>0.4761045525333641</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.438671876188928</v>
+        <v>1.198349616808716</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -538,25 +538,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2992099333553406</v>
+        <v>0.2808911641104241</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2291797279328061</v>
+        <v>0.2390766078490786</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2967604346712478</v>
+        <v>0.2791487904168628</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1.423770799533282</v>
+        <v>1.072530669500765</v>
       </c>
       <c r="J3" t="n">
         <v>3</v>
@@ -575,25 +575,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.07043117580663896</v>
+        <v>0.0704731334153732</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07192762145117108</v>
+        <v>0.07063431481632378</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02469442225621099</v>
+        <v>0.02360148039191765</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0.947515211524121</v>
+        <v>0.6822701612908508</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
@@ -612,25 +612,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.04282009912729453</v>
+        <v>0.05523915390276699</v>
       </c>
       <c r="D5" t="n">
         <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1558290110023217</v>
+        <v>0.1472118822135189</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005706524045798933</v>
+        <v>0.008552106770008039</v>
       </c>
       <c r="H5" t="n">
         <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8392709336065023</v>
+        <v>0.6178166855264426</v>
       </c>
       <c r="J5" t="n">
         <v>6</v>
@@ -649,25 +649,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.007345090478667085</v>
+        <v>0.007332764951427079</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.050508469336305</v>
+        <v>0.05099292444392457</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001290483164255839</v>
+        <v>0.001482728878322677</v>
       </c>
       <c r="H6" t="n">
         <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>1.516185073214777</v>
+        <v>1.236279030419674</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -682,35 +682,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.06347889196297038</v>
+        <v>0.01437921541051098</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01086974528925099</v>
+        <v>0.0396324080579542</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01205830762074601</v>
+        <v>0.01139062738611735</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7102381910625768</v>
+        <v>0.28650978335402</v>
       </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="8">
@@ -719,35 +719,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01424827950268244</v>
+        <v>0.05936462511312079</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0388937622385257</v>
+        <v>0.008049120596560178</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01167431989016169</v>
+        <v>0.01033062653383405</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2864599872107711</v>
+        <v>0.4739090618199784</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K8" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -760,28 +760,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.005953696622513246</v>
+        <v>0.005865493220224619</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0110282599486145</v>
+        <v>0.01171508403166955</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002388489583926767</v>
+        <v>0.002352385369849619</v>
       </c>
       <c r="H9" t="n">
         <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2408345741623004</v>
+        <v>0.229810539278942</v>
       </c>
       <c r="J9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K9" t="n">
         <v>9.25</v>
@@ -793,35 +793,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0058600638538843</v>
+        <v>0.003680338482789539</v>
       </c>
       <c r="D10" t="n">
+        <v>14</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.003549982278399404</v>
+      </c>
+      <c r="F10" t="n">
+        <v>16</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.002523136450429464</v>
+      </c>
+      <c r="H10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.3677464095429919</v>
+      </c>
+      <c r="J10" t="n">
         <v>9</v>
       </c>
-      <c r="E10" t="n">
-        <v>0.0120158828156668</v>
-      </c>
-      <c r="F10" t="n">
-        <v>7</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.002259821391015104</v>
-      </c>
-      <c r="H10" t="n">
-        <v>9</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.2066749365948048</v>
-      </c>
-      <c r="J10" t="n">
-        <v>14</v>
-      </c>
       <c r="K10" t="n">
-        <v>9.75</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="11">
@@ -830,35 +830,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.003732832738122984</v>
+        <v>0.005951551135848279</v>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00371639329167186</v>
+        <v>0.01139603876227962</v>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002466793375890008</v>
+        <v>0.002136458895167448</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6266420055755306</v>
+        <v>0.1407178423155786</v>
       </c>
       <c r="J11" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="K11" t="n">
-        <v>11.25</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="12">
@@ -867,35 +867,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.005718097971075684</v>
+        <v>0.003182975224781823</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01114242239312433</v>
+        <v>0.004671017670986557</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001872568715010758</v>
+        <v>0.001005090769901163</v>
       </c>
       <c r="H12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1927333513280312</v>
+        <v>0.6640910913673306</v>
       </c>
       <c r="J12" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>11.5</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="13">
@@ -904,35 +904,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.003447581827407039</v>
+        <v>0.002450678522644812</v>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E13" t="n">
-        <v>0.005242163931629659</v>
+        <v>0.004791652244209006</v>
       </c>
       <c r="F13" t="n">
         <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0007476917004785144</v>
+        <v>0.0009216647418518575</v>
       </c>
       <c r="H13" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8867983829986508</v>
+        <v>0.4961148960923709</v>
       </c>
       <c r="J13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K13" t="n">
-        <v>12.75</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="14">
@@ -941,35 +941,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.002388679605767266</v>
+        <v>0.005568558762841301</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.004392508987762973</v>
+        <v>0.01166209065597926</v>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001013569475495835</v>
+        <v>0.001733866369081016</v>
       </c>
       <c r="H14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I14" t="n">
-        <v>0.672769671377254</v>
+        <v>0.1198625489822751</v>
       </c>
       <c r="J14" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="K14" t="n">
-        <v>13.75</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="15">
@@ -982,31 +982,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.003852124005685164</v>
+        <v>0.003786938594379947</v>
       </c>
       <c r="D15" t="n">
         <v>13</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002072561167334866</v>
+        <v>0.002111454812359339</v>
       </c>
       <c r="F15" t="n">
         <v>19</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001972247393986837</v>
+        <v>0.001664456317987884</v>
       </c>
       <c r="H15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1482583563546349</v>
+        <v>0.1416256039247572</v>
       </c>
       <c r="J15" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K15" t="n">
-        <v>16.75</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="16">
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.001933603185737217</v>
+        <v>0.001909589683063649</v>
       </c>
       <c r="D16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E16" t="n">
-        <v>0.009198273584937154</v>
+        <v>0.007637278622181098</v>
       </c>
       <c r="F16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0002671008442111988</v>
+        <v>0.000387969342948602</v>
       </c>
       <c r="H16" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2678695621723715</v>
+        <v>0.2387552123432464</v>
       </c>
       <c r="J16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K16" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="17">
@@ -1052,35 +1052,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.001590935227078281</v>
+        <v>0.00542538573678234</v>
       </c>
       <c r="D17" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>0.002694814176495566</v>
+        <v>0.001843656198317041</v>
       </c>
       <c r="F17" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004935313015577925</v>
+        <v>0.001297587529406119</v>
       </c>
       <c r="H17" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2025258905133143</v>
+        <v>0.1150710484016844</v>
       </c>
       <c r="J17" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K17" t="n">
-        <v>20.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
@@ -1089,35 +1089,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.005213653768950966</v>
+        <v>0.002072288043532046</v>
       </c>
       <c r="D18" t="n">
+        <v>24</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.004507777600072711</v>
+      </c>
+      <c r="F18" t="n">
+        <v>15</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.000125652302639645</v>
+      </c>
+      <c r="H18" t="n">
+        <v>32</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.2398858944846856</v>
+      </c>
+      <c r="J18" t="n">
         <v>11</v>
       </c>
-      <c r="E18" t="n">
-        <v>0.001723245257052869</v>
-      </c>
-      <c r="F18" t="n">
-        <v>22</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.001207182745202129</v>
-      </c>
-      <c r="H18" t="n">
-        <v>13</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.09164550956329354</v>
-      </c>
-      <c r="J18" t="n">
-        <v>38</v>
-      </c>
       <c r="K18" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="19">
@@ -1126,35 +1126,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.002141043114578652</v>
+        <v>0.00225115840821352</v>
       </c>
       <c r="D19" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>0.003472869175817386</v>
+        <v>0.001357061971355008</v>
       </c>
       <c r="F19" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G19" t="n">
-        <v>7.578620613383214e-05</v>
+        <v>0.0004163616826270977</v>
       </c>
       <c r="H19" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2165485625793266</v>
+        <v>0.1598125154675447</v>
       </c>
       <c r="J19" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>21.5</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="20">
@@ -1167,31 +1167,31 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.002390475329932857</v>
+        <v>0.002423001199226675</v>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E20" t="n">
-        <v>0.002589998571600898</v>
+        <v>0.002412386175043696</v>
       </c>
       <c r="F20" t="n">
         <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0008620481737081409</v>
+        <v>0.0008939545123207493</v>
       </c>
       <c r="H20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I20" t="n">
-        <v>0.08446606360304898</v>
+        <v>0.1038346518305531</v>
       </c>
       <c r="J20" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="K20" t="n">
-        <v>23.25</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="21">
@@ -1200,35 +1200,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.002275603295886006</v>
+        <v>0.001615536306275759</v>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E21" t="n">
-        <v>0.001409204688916107</v>
+        <v>0.002557803826870271</v>
       </c>
       <c r="F21" t="n">
+        <v>17</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.0003160224410930001</v>
+      </c>
+      <c r="H21" t="n">
         <v>27</v>
       </c>
-      <c r="G21" t="n">
-        <v>0.000442262914799052</v>
-      </c>
-      <c r="H21" t="n">
-        <v>20</v>
-      </c>
       <c r="I21" t="n">
-        <v>0.1295419430619873</v>
+        <v>0.2062187982627752</v>
       </c>
       <c r="J21" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K21" t="n">
-        <v>24.25</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="22">
@@ -1237,35 +1237,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.00227475211272811</v>
+        <v>0.003116999146508176</v>
       </c>
       <c r="D22" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E22" t="n">
-        <v>0.001366326113494094</v>
+        <v>0.001237897278353882</v>
       </c>
       <c r="F22" t="n">
         <v>29</v>
       </c>
       <c r="G22" t="n">
-        <v>0.00047304882669158</v>
+        <v>0.0001045709538454842</v>
       </c>
       <c r="H22" t="n">
+        <v>33</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.1601129381638917</v>
+      </c>
+      <c r="J22" t="n">
         <v>19</v>
       </c>
-      <c r="I22" t="n">
-        <v>0.1430346516538337</v>
-      </c>
-      <c r="J22" t="n">
-        <v>28</v>
-      </c>
       <c r="K22" t="n">
-        <v>24.25</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="23">
@@ -1274,35 +1274,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.003162079358151949</v>
+        <v>0.002266012182974288</v>
       </c>
       <c r="D23" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E23" t="n">
-        <v>0.001137377474102061</v>
+        <v>0.001231804086661222</v>
       </c>
       <c r="F23" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0001723422210909709</v>
+        <v>0.00047072720512219</v>
       </c>
       <c r="H23" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1921799270615958</v>
+        <v>0.1148730857526199</v>
       </c>
       <c r="J23" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K23" t="n">
-        <v>25</v>
+        <v>25.25</v>
       </c>
     </row>
     <row r="24">
@@ -1311,35 +1311,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.001395045957988709</v>
+        <v>0.00220460670377708</v>
       </c>
       <c r="D24" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>0.009018698114905568</v>
+        <v>0.0013480432808974</v>
       </c>
       <c r="F24" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0004357877178527647</v>
+        <v>0.0002265491737181602</v>
       </c>
       <c r="H24" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1361843957214524</v>
+        <v>0.1374923718309686</v>
       </c>
       <c r="J24" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K24" t="n">
-        <v>25</v>
+        <v>26.25</v>
       </c>
     </row>
     <row r="25">
@@ -1348,35 +1348,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.002151715685267272</v>
+        <v>0.004053578774404341</v>
       </c>
       <c r="D25" t="n">
+        <v>12</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.001829738778094041</v>
+      </c>
+      <c r="F25" t="n">
         <v>22</v>
       </c>
-      <c r="E25" t="n">
-        <v>0.001395690074680656</v>
-      </c>
-      <c r="F25" t="n">
-        <v>28</v>
-      </c>
       <c r="G25" t="n">
-        <v>0.0001417221139674907</v>
+        <v>-0.0006547469196777067</v>
       </c>
       <c r="H25" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1593929350952812</v>
+        <v>0.1925807873599821</v>
       </c>
       <c r="J25" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K25" t="n">
-        <v>26</v>
+        <v>26.25</v>
       </c>
     </row>
     <row r="26">
@@ -1385,35 +1385,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.00408366209339472</v>
+        <v>0.001523763742701117</v>
       </c>
       <c r="D26" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="E26" t="n">
-        <v>0.002037237381054784</v>
+        <v>0.001058699724778284</v>
       </c>
       <c r="F26" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.0006843931404619585</v>
+        <v>0.0004086844772112186</v>
       </c>
       <c r="H26" t="n">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1724460051318526</v>
+        <v>0.2162787103716499</v>
       </c>
       <c r="J26" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K26" t="n">
-        <v>26</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="27">
@@ -1426,31 +1426,31 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.001921410431688985</v>
+        <v>0.001952816557958622</v>
       </c>
       <c r="D27" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>0.001687484260549532</v>
+        <v>0.001721754149235873</v>
       </c>
       <c r="F27" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0002302416522496187</v>
+        <v>0.0002886776865377749</v>
       </c>
       <c r="H27" t="n">
+        <v>28</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.1215714553125802</v>
+      </c>
+      <c r="J27" t="n">
         <v>29</v>
       </c>
-      <c r="I27" t="n">
-        <v>0.1465380298983885</v>
-      </c>
-      <c r="J27" t="n">
-        <v>27</v>
-      </c>
       <c r="K27" t="n">
-        <v>26.5</v>
+        <v>26.75</v>
       </c>
     </row>
     <row r="28">
@@ -1463,31 +1463,31 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.001889097578054567</v>
+        <v>0.001925401250557361</v>
       </c>
       <c r="D28" t="n">
+        <v>26</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.0009511806763082975</v>
+      </c>
+      <c r="F28" t="n">
+        <v>43</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.0006425803427979049</v>
+      </c>
+      <c r="H28" t="n">
+        <v>17</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.1314372965756354</v>
+      </c>
+      <c r="J28" t="n">
+        <v>26</v>
+      </c>
+      <c r="K28" t="n">
         <v>28</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.0008770449292562827</v>
-      </c>
-      <c r="F28" t="n">
-        <v>44</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.0007934977301886637</v>
-      </c>
-      <c r="H28" t="n">
-        <v>16</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.1703142646263009</v>
-      </c>
-      <c r="J28" t="n">
-        <v>20</v>
-      </c>
-      <c r="K28" t="n">
-        <v>27</v>
       </c>
     </row>
     <row r="29">
@@ -1500,31 +1500,31 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.001669928206103682</v>
+        <v>0.00168310873626361</v>
       </c>
       <c r="D29" t="n">
         <v>30</v>
       </c>
       <c r="E29" t="n">
-        <v>0.001289182559551359</v>
+        <v>0.001207563170348514</v>
       </c>
       <c r="F29" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0002258320645653788</v>
+        <v>0.000143322314579053</v>
       </c>
       <c r="H29" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1659753101927781</v>
+        <v>0.1533962047699582</v>
       </c>
       <c r="J29" t="n">
         <v>21</v>
       </c>
       <c r="K29" t="n">
-        <v>27.75</v>
+        <v>28.25</v>
       </c>
     </row>
     <row r="30">
@@ -1533,35 +1533,35 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.001875236354155498</v>
+        <v>0.001422216227604319</v>
       </c>
       <c r="D30" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E30" t="n">
-        <v>0.001420542092449193</v>
+        <v>0.008973586438909669</v>
       </c>
       <c r="F30" t="n">
+        <v>10</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.0003281996298877377</v>
+      </c>
+      <c r="H30" t="n">
         <v>26</v>
       </c>
-      <c r="G30" t="n">
-        <v>-7.365142936333058e-05</v>
-      </c>
-      <c r="H30" t="n">
-        <v>47</v>
-      </c>
       <c r="I30" t="n">
-        <v>0.194221959201021</v>
+        <v>0.08537318741232736</v>
       </c>
       <c r="J30" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="K30" t="n">
-        <v>29.5</v>
+        <v>28.25</v>
       </c>
     </row>
     <row r="31">
@@ -1570,35 +1570,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.001591884876387455</v>
+        <v>0.001876100480860019</v>
       </c>
       <c r="D31" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0008975503660924299</v>
+        <v>0.001807229545069563</v>
       </c>
       <c r="F31" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0003884077899509064</v>
+        <v>-0.0001195851064772491</v>
       </c>
       <c r="H31" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1487373275154553</v>
+        <v>0.1975684889068154</v>
       </c>
       <c r="J31" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K31" t="n">
-        <v>30.75</v>
+        <v>29.75</v>
       </c>
     </row>
     <row r="32">
@@ -1607,35 +1607,35 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.001426620889287097</v>
+        <v>0.001546442873848397</v>
       </c>
       <c r="D32" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E32" t="n">
-        <v>0.001233797996048181</v>
+        <v>0.001813175004032185</v>
       </c>
       <c r="F32" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0004180963464805121</v>
+        <v>2.762245849674549e-06</v>
       </c>
       <c r="H32" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1216199643191032</v>
+        <v>0.1399203475237156</v>
       </c>
       <c r="J32" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="K32" t="n">
-        <v>31.25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33">
@@ -1648,31 +1648,31 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.001444030739204453</v>
+        <v>0.001467879364589689</v>
       </c>
       <c r="D33" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0009588233178267449</v>
+        <v>0.0009266225191322128</v>
       </c>
       <c r="F33" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0003107090366941567</v>
+        <v>0.0002731873965256759</v>
       </c>
       <c r="H33" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I33" t="n">
-        <v>0.151174213998134</v>
+        <v>0.2045485718760616</v>
       </c>
       <c r="J33" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="K33" t="n">
-        <v>31.5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34">
@@ -1681,35 +1681,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.001523330653525749</v>
+        <v>0.001405256658231053</v>
       </c>
       <c r="D34" t="n">
+        <v>38</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.001101450565593942</v>
+      </c>
+      <c r="F34" t="n">
         <v>33</v>
       </c>
-      <c r="E34" t="n">
-        <v>0.001660669792439465</v>
-      </c>
-      <c r="F34" t="n">
-        <v>24</v>
-      </c>
       <c r="G34" t="n">
-        <v>-6.373590530978079e-05</v>
+        <v>0.0004939475910281877</v>
       </c>
       <c r="H34" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1469591885128838</v>
+        <v>0.106171265677435</v>
       </c>
       <c r="J34" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="K34" t="n">
-        <v>32.25</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="35">
@@ -1718,35 +1718,35 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.001359182555521891</v>
+        <v>0.001880153310329902</v>
       </c>
       <c r="D35" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E35" t="n">
-        <v>0.00114811963404087</v>
+        <v>0.001934360536190422</v>
       </c>
       <c r="F35" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0003296159210498528</v>
+        <v>-0.0003126019529183899</v>
       </c>
       <c r="H35" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1223398881841007</v>
+        <v>0.1294575803156772</v>
       </c>
       <c r="J35" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K35" t="n">
-        <v>32.75</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="36">
@@ -1755,35 +1755,35 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.001977614688915244</v>
+        <v>0.002181944414213</v>
       </c>
       <c r="D36" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E36" t="n">
-        <v>0.001734285883287098</v>
+        <v>0.001475508310899919</v>
       </c>
       <c r="F36" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.0002758897424568807</v>
+        <v>-0.0003389814205102981</v>
       </c>
       <c r="H36" t="n">
         <v>52</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1001025315170314</v>
+        <v>0.1282316679533264</v>
       </c>
       <c r="J36" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="K36" t="n">
-        <v>33.25</v>
+        <v>32.25</v>
       </c>
     </row>
     <row r="37">
@@ -1792,35 +1792,35 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.001344698110801744</v>
+        <v>0.001324181788718726</v>
       </c>
       <c r="D37" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E37" t="n">
-        <v>0.000987889877819074</v>
+        <v>0.001075282134623642</v>
       </c>
       <c r="F37" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0004121634172346899</v>
+        <v>0.0004189207118883931</v>
       </c>
       <c r="H37" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1248616794782231</v>
+        <v>0.11158529414972</v>
       </c>
       <c r="J37" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K37" t="n">
-        <v>33.5</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="38">
@@ -1829,35 +1829,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.001963595860471165</v>
+        <v>0.00358843655999448</v>
       </c>
       <c r="D38" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E38" t="n">
-        <v>0.001509004654213302</v>
+        <v>0.00109379240620066</v>
       </c>
       <c r="F38" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.0002712248262002337</v>
+        <v>-5.223207071624048e-05</v>
       </c>
       <c r="H38" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1038703040238067</v>
+        <v>0.07325591331459158</v>
       </c>
       <c r="J38" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="K38" t="n">
-        <v>34</v>
+        <v>34.75</v>
       </c>
     </row>
     <row r="39">
@@ -1866,35 +1866,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.003560354189681795</v>
+        <v>0.0013199485006502</v>
       </c>
       <c r="D39" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="E39" t="n">
-        <v>0.00107041891465202</v>
+        <v>0.001154547130382378</v>
       </c>
       <c r="F39" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G39" t="n">
-        <v>-9.283608491721385e-05</v>
+        <v>0.0003298602118368299</v>
       </c>
       <c r="H39" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="I39" t="n">
-        <v>0.06405133728471712</v>
+        <v>0.0524700468327115</v>
       </c>
       <c r="J39" t="n">
         <v>47</v>
       </c>
       <c r="K39" t="n">
-        <v>36.5</v>
+        <v>36.25</v>
       </c>
     </row>
     <row r="40">
@@ -1907,31 +1907,31 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.001316667902269605</v>
+        <v>0.001278372169820007</v>
       </c>
       <c r="D40" t="n">
         <v>42</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0009322712034206816</v>
+        <v>0.001002967469465903</v>
       </c>
       <c r="F40" t="n">
         <v>41</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0004120665964466142</v>
+        <v>0.0003681251614669922</v>
       </c>
       <c r="H40" t="n">
         <v>24</v>
       </c>
       <c r="I40" t="n">
-        <v>0.08955986934737403</v>
+        <v>0.08786926996012312</v>
       </c>
       <c r="J40" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K40" t="n">
-        <v>36.75</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="41">
@@ -1940,35 +1940,35 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.001258645102917479</v>
+        <v>0.001489522975204905</v>
       </c>
       <c r="D41" t="n">
+        <v>34</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.0009939507152283882</v>
+      </c>
+      <c r="F41" t="n">
+        <v>42</v>
+      </c>
+      <c r="G41" t="n">
+        <v>4.357300668264008e-05</v>
+      </c>
+      <c r="H41" t="n">
+        <v>37</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.07201304738427394</v>
+      </c>
+      <c r="J41" t="n">
         <v>43</v>
       </c>
-      <c r="E41" t="n">
-        <v>0.001109542528416572</v>
-      </c>
-      <c r="F41" t="n">
-        <v>35</v>
-      </c>
-      <c r="G41" t="n">
-        <v>3.765699218413188e-05</v>
-      </c>
-      <c r="H41" t="n">
-        <v>36</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0.09076655113070364</v>
-      </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>39</v>
-      </c>
-      <c r="K41" t="n">
-        <v>38.25</v>
       </c>
     </row>
     <row r="42">
@@ -1977,35 +1977,35 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.001496111232371845</v>
+        <v>0.001170717320282009</v>
       </c>
       <c r="D42" t="n">
+        <v>44</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.001014908604712684</v>
+      </c>
+      <c r="F42" t="n">
+        <v>40</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.0001004520136867915</v>
+      </c>
+      <c r="H42" t="n">
         <v>34</v>
       </c>
-      <c r="E42" t="n">
-        <v>0.001262299624090363</v>
-      </c>
-      <c r="F42" t="n">
-        <v>31</v>
-      </c>
-      <c r="G42" t="n">
-        <v>-0.0001017768120741169</v>
-      </c>
-      <c r="H42" t="n">
-        <v>50</v>
-      </c>
       <c r="I42" t="n">
-        <v>0.08358444248332875</v>
+        <v>0.09691135010235818</v>
       </c>
       <c r="J42" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="K42" t="n">
-        <v>39.5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43">
@@ -2014,35 +2014,35 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.001359952927898525</v>
+        <v>0.001259483624557032</v>
       </c>
       <c r="D43" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E43" t="n">
-        <v>0.000784844347555557</v>
+        <v>0.001095079940739656</v>
       </c>
       <c r="F43" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="G43" t="n">
-        <v>-5.527578036853553e-05</v>
+        <v>4.210899185662642e-05</v>
       </c>
       <c r="H43" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1221860038175966</v>
+        <v>0.06522008278876879</v>
       </c>
       <c r="J43" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="K43" t="n">
-        <v>40.75</v>
+        <v>39.75</v>
       </c>
     </row>
     <row r="44">
@@ -2051,35 +2051,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.001465618353457205</v>
+        <v>0.001377660164585235</v>
       </c>
       <c r="D44" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0009075890504689311</v>
+        <v>0.0008008771383007751</v>
       </c>
       <c r="F44" t="n">
+        <v>47</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-9.861126962218414e-07</v>
+      </c>
+      <c r="H44" t="n">
         <v>42</v>
       </c>
-      <c r="G44" t="n">
-        <v>-6.038959025870261e-05</v>
-      </c>
-      <c r="H44" t="n">
-        <v>44</v>
-      </c>
       <c r="I44" t="n">
-        <v>0.07439785613225913</v>
+        <v>0.1134854836112336</v>
       </c>
       <c r="J44" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="K44" t="n">
-        <v>41.5</v>
+        <v>40.25</v>
       </c>
     </row>
     <row r="45">
@@ -2088,35 +2088,35 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0009659162451454334</v>
+        <v>0.001459353406819576</v>
       </c>
       <c r="D45" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="E45" t="n">
-        <v>0.0010598954833534</v>
+        <v>0.001045676264699847</v>
       </c>
       <c r="F45" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G45" t="n">
-        <v>-3.437122920015856e-05</v>
+        <v>-7.407733931898974e-05</v>
       </c>
       <c r="H45" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I45" t="n">
-        <v>0.08619964502381627</v>
+        <v>0.05844033263516879</v>
       </c>
       <c r="J45" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K45" t="n">
-        <v>41.5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46">
@@ -2125,35 +2125,35 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.001176834384073412</v>
+        <v>0.001159971095830336</v>
       </c>
       <c r="D46" t="n">
         <v>45</v>
       </c>
       <c r="E46" t="n">
-        <v>0.001040180910976187</v>
+        <v>0.0009263130496737242</v>
       </c>
       <c r="F46" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G46" t="n">
-        <v>-2.648016097196448e-05</v>
+        <v>-3.494969673081272e-05</v>
       </c>
       <c r="H46" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I46" t="n">
-        <v>0.07780667667315466</v>
+        <v>0.1062600742559612</v>
       </c>
       <c r="J46" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="K46" t="n">
-        <v>41.75</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="47">
@@ -2162,35 +2162,35 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.001188608104898267</v>
+        <v>0.0005306475056556192</v>
       </c>
       <c r="D47" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E47" t="n">
-        <v>0.0008679974287115135</v>
+        <v>0.000767815827354959</v>
       </c>
       <c r="F47" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G47" t="n">
-        <v>-9.551979519119014e-05</v>
+        <v>4.996488354248596e-05</v>
       </c>
       <c r="H47" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="I47" t="n">
-        <v>0.09944565930027194</v>
+        <v>0.07723852475526449</v>
       </c>
       <c r="J47" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K47" t="n">
-        <v>43.75</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="48">
@@ -2203,31 +2203,31 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.0006072118167457299</v>
+        <v>0.0006485909228951996</v>
       </c>
       <c r="D48" t="n">
         <v>48</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0008294176686763347</v>
+        <v>0.0008914295508628588</v>
       </c>
       <c r="F48" t="n">
         <v>46</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0001129120157824515</v>
+        <v>4.448725532437692e-05</v>
       </c>
       <c r="H48" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I48" t="n">
-        <v>0.03668306533699361</v>
+        <v>0.005638754778659383</v>
       </c>
       <c r="J48" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K48" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49">
@@ -2236,35 +2236,35 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.0005354569751638635</v>
+        <v>0.001105095374194287</v>
       </c>
       <c r="D49" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E49" t="n">
-        <v>0.000791305892487536</v>
+        <v>0.00104881979376202</v>
       </c>
       <c r="F49" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="G49" t="n">
-        <v>5.64339309587325e-05</v>
+        <v>-0.0003023502629998176</v>
       </c>
       <c r="H49" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="I49" t="n">
-        <v>0.06806981505572551</v>
+        <v>0.05784603239742125</v>
       </c>
       <c r="J49" t="n">
         <v>46</v>
       </c>
       <c r="K49" t="n">
-        <v>44.25</v>
+        <v>45.25</v>
       </c>
     </row>
     <row r="50">
@@ -2277,31 +2277,31 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.001138441486449964</v>
+        <v>0.00111841178422654</v>
       </c>
       <c r="D50" t="n">
         <v>46</v>
       </c>
       <c r="E50" t="n">
-        <v>0.0006949217019225416</v>
+        <v>0.0007946482086225369</v>
       </c>
       <c r="F50" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G50" t="n">
-        <v>-3.56381611746448e-05</v>
+        <v>-1.721897560962304e-05</v>
       </c>
       <c r="H50" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I50" t="n">
-        <v>0.03700780804195913</v>
+        <v>0.04452011846688331</v>
       </c>
       <c r="J50" t="n">
         <v>48</v>
       </c>
       <c r="K50" t="n">
-        <v>46.25</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="51">
@@ -2310,35 +2310,35 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>9.541043300902036e-05</v>
+        <v>0.0001249375002640287</v>
       </c>
       <c r="D51" t="n">
         <v>50</v>
       </c>
       <c r="E51" t="n">
-        <v>0.0005583641966469675</v>
+        <v>0.0002812180453595566</v>
       </c>
       <c r="F51" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G51" t="n">
-        <v>2.359375964066102e-05</v>
+        <v>2.258744967039705e-05</v>
       </c>
       <c r="H51" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>0.0007857841193852355</v>
       </c>
       <c r="J51" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K51" t="n">
-        <v>47.5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="52">
@@ -2347,35 +2347,35 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2.081146124410183e-05</v>
+        <v>6.737916972965479e-05</v>
       </c>
       <c r="D52" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0001398858186863133</v>
+        <v>0.0005170322901136405</v>
       </c>
       <c r="F52" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G52" t="n">
-        <v>2.379094596457465e-05</v>
+        <v>6.82048063872509e-06</v>
       </c>
       <c r="H52" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I52" t="n">
-        <v>0.02616468904652591</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K52" t="n">
-        <v>48.25</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="53">
@@ -2384,35 +2384,35 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>7.808758290207801e-05</v>
+        <v>2.532199209291146e-05</v>
       </c>
       <c r="D53" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0002184181996498549</v>
+        <v>0.0001221167458791846</v>
       </c>
       <c r="F53" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G53" t="n">
-        <v>1.263266027968779e-05</v>
+        <v>-9.206848448506388e-06</v>
       </c>
       <c r="H53" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I53" t="n">
-        <v>0.01947477582113599</v>
+        <v>0.02298624135869165</v>
       </c>
       <c r="J53" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K53" t="n">
-        <v>48.25</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="54">
@@ -2425,22 +2425,22 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>7.721435030299638e-05</v>
+        <v>7.577446736926195e-05</v>
       </c>
       <c r="D54" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0003166854152453804</v>
+        <v>0.0003402447111151486</v>
       </c>
       <c r="F54" t="n">
         <v>51</v>
       </c>
       <c r="G54" t="n">
-        <v>-6.196392031168063e-05</v>
+        <v>-5.125645230295017e-05</v>
       </c>
       <c r="H54" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
@@ -2533,25 +2533,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4065729105196067</v>
+        <v>0.4165063630280615</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3291493018522236</v>
+        <v>0.3306041230813141</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4644109321358291</v>
+        <v>0.4761045525333641</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.438671876188928</v>
+        <v>1.198349616808716</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -2570,25 +2570,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2992099333553406</v>
+        <v>0.2808911641104241</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2291797279328061</v>
+        <v>0.2390766078490786</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2967604346712478</v>
+        <v>0.2791487904168628</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1.423770799533282</v>
+        <v>1.072530669500765</v>
       </c>
       <c r="J3" t="n">
         <v>3</v>
@@ -2607,25 +2607,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.07043117580663896</v>
+        <v>0.0704731334153732</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07192762145117108</v>
+        <v>0.07063431481632378</v>
       </c>
       <c r="F4" t="n">
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02469442225621099</v>
+        <v>0.02360148039191765</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>0.947515211524121</v>
+        <v>0.6822701612908508</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
@@ -2644,25 +2644,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.04282009912729453</v>
+        <v>0.05523915390276699</v>
       </c>
       <c r="D5" t="n">
         <v>5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1558290110023217</v>
+        <v>0.1472118822135189</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005706524045798933</v>
+        <v>0.008552106770008039</v>
       </c>
       <c r="H5" t="n">
         <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8392709336065023</v>
+        <v>0.6178166855264426</v>
       </c>
       <c r="J5" t="n">
         <v>6</v>
@@ -2681,25 +2681,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.007345090478667085</v>
+        <v>0.007332764951427079</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0.050508469336305</v>
+        <v>0.05099292444392457</v>
       </c>
       <c r="F6" t="n">
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001290483164255839</v>
+        <v>0.001482728878322677</v>
       </c>
       <c r="H6" t="n">
         <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>1.516185073214777</v>
+        <v>1.236279030419674</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -2714,35 +2714,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.06347889196297038</v>
+        <v>0.01437921541051098</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01086974528925099</v>
+        <v>0.0396324080579542</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01205830762074601</v>
+        <v>0.01139062738611735</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7102381910625768</v>
+        <v>0.28650978335402</v>
       </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="8">
@@ -2751,35 +2751,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01424827950268244</v>
+        <v>0.05936462511312079</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0388937622385257</v>
+        <v>0.008049120596560178</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01167431989016169</v>
+        <v>0.01033062653383405</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2864599872107711</v>
+        <v>0.4739090618199784</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K8" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -2792,28 +2792,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.005953696622513246</v>
+        <v>0.005865493220224619</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0110282599486145</v>
+        <v>0.01171508403166955</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002388489583926767</v>
+        <v>0.002352385369849619</v>
       </c>
       <c r="H9" t="n">
         <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2408345741623004</v>
+        <v>0.229810539278942</v>
       </c>
       <c r="J9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K9" t="n">
         <v>9.25</v>
@@ -2825,35 +2825,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0058600638538843</v>
+        <v>0.003680338482789539</v>
       </c>
       <c r="D10" t="n">
+        <v>14</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.003549982278399404</v>
+      </c>
+      <c r="F10" t="n">
+        <v>16</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.002523136450429464</v>
+      </c>
+      <c r="H10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.3677464095429919</v>
+      </c>
+      <c r="J10" t="n">
         <v>9</v>
       </c>
-      <c r="E10" t="n">
-        <v>0.0120158828156668</v>
-      </c>
-      <c r="F10" t="n">
-        <v>7</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.002259821391015104</v>
-      </c>
-      <c r="H10" t="n">
-        <v>9</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.2066749365948048</v>
-      </c>
-      <c r="J10" t="n">
-        <v>14</v>
-      </c>
       <c r="K10" t="n">
-        <v>9.75</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="11">
@@ -2862,35 +2862,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.003732832738122984</v>
+        <v>0.005951551135848279</v>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00371639329167186</v>
+        <v>0.01139603876227962</v>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002466793375890008</v>
+        <v>0.002136458895167448</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6266420055755306</v>
+        <v>0.1407178423155786</v>
       </c>
       <c r="J11" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="K11" t="n">
-        <v>11.25</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="12">
@@ -2899,35 +2899,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.005718097971075684</v>
+        <v>0.003182975224781823</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01114242239312433</v>
+        <v>0.004671017670986557</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001872568715010758</v>
+        <v>0.001005090769901163</v>
       </c>
       <c r="H12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1927333513280312</v>
+        <v>0.6640910913673306</v>
       </c>
       <c r="J12" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>11.5</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="13">
@@ -2936,35 +2936,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.003447581827407039</v>
+        <v>0.002450678522644812</v>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E13" t="n">
-        <v>0.005242163931629659</v>
+        <v>0.004791652244209006</v>
       </c>
       <c r="F13" t="n">
         <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0007476917004785144</v>
+        <v>0.0009216647418518575</v>
       </c>
       <c r="H13" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8867983829986508</v>
+        <v>0.4961148960923709</v>
       </c>
       <c r="J13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K13" t="n">
-        <v>12.75</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="14">
@@ -2973,35 +2973,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.002388679605767266</v>
+        <v>0.005568558762841301</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.004392508987762973</v>
+        <v>0.01166209065597926</v>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001013569475495835</v>
+        <v>0.001733866369081016</v>
       </c>
       <c r="H14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I14" t="n">
-        <v>0.672769671377254</v>
+        <v>0.1198625489822751</v>
       </c>
       <c r="J14" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="K14" t="n">
-        <v>13.75</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="15">
@@ -3014,31 +3014,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.003852124005685164</v>
+        <v>0.003786938594379947</v>
       </c>
       <c r="D15" t="n">
         <v>13</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002072561167334866</v>
+        <v>0.002111454812359339</v>
       </c>
       <c r="F15" t="n">
         <v>19</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001972247393986837</v>
+        <v>0.001664456317987884</v>
       </c>
       <c r="H15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1482583563546349</v>
+        <v>0.1416256039247572</v>
       </c>
       <c r="J15" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K15" t="n">
-        <v>16.75</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="16">
@@ -3051,31 +3051,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.001933603185737217</v>
+        <v>0.001909589683063649</v>
       </c>
       <c r="D16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E16" t="n">
-        <v>0.009198273584937154</v>
+        <v>0.007637278622181098</v>
       </c>
       <c r="F16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0002671008442111988</v>
+        <v>0.000387969342948602</v>
       </c>
       <c r="H16" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2678695621723715</v>
+        <v>0.2387552123432464</v>
       </c>
       <c r="J16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K16" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="17">
@@ -3084,35 +3084,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.001590935227078281</v>
+        <v>0.00542538573678234</v>
       </c>
       <c r="D17" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>0.002694814176495566</v>
+        <v>0.001843656198317041</v>
       </c>
       <c r="F17" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004935313015577925</v>
+        <v>0.001297587529406119</v>
       </c>
       <c r="H17" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2025258905133143</v>
+        <v>0.1150710484016844</v>
       </c>
       <c r="J17" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K17" t="n">
-        <v>20.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
@@ -3121,35 +3121,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.005213653768950966</v>
+        <v>0.002072288043532046</v>
       </c>
       <c r="D18" t="n">
+        <v>24</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.004507777600072711</v>
+      </c>
+      <c r="F18" t="n">
+        <v>15</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.000125652302639645</v>
+      </c>
+      <c r="H18" t="n">
+        <v>32</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.2398858944846856</v>
+      </c>
+      <c r="J18" t="n">
         <v>11</v>
       </c>
-      <c r="E18" t="n">
-        <v>0.001723245257052869</v>
-      </c>
-      <c r="F18" t="n">
-        <v>22</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.001207182745202129</v>
-      </c>
-      <c r="H18" t="n">
-        <v>13</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.09164550956329354</v>
-      </c>
-      <c r="J18" t="n">
-        <v>38</v>
-      </c>
       <c r="K18" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="19">
@@ -3158,35 +3158,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.002141043114578652</v>
+        <v>0.00225115840821352</v>
       </c>
       <c r="D19" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E19" t="n">
-        <v>0.003472869175817386</v>
+        <v>0.001357061971355008</v>
       </c>
       <c r="F19" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="G19" t="n">
-        <v>7.578620613383214e-05</v>
+        <v>0.0004163616826270977</v>
       </c>
       <c r="H19" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2165485625793266</v>
+        <v>0.1598125154675447</v>
       </c>
       <c r="J19" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K19" t="n">
-        <v>21.5</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="20">
@@ -3199,31 +3199,31 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.002390475329932857</v>
+        <v>0.002423001199226675</v>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E20" t="n">
-        <v>0.002589998571600898</v>
+        <v>0.002412386175043696</v>
       </c>
       <c r="F20" t="n">
         <v>18</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0008620481737081409</v>
+        <v>0.0008939545123207493</v>
       </c>
       <c r="H20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I20" t="n">
-        <v>0.08446606360304898</v>
+        <v>0.1038346518305531</v>
       </c>
       <c r="J20" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="K20" t="n">
-        <v>23.25</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="21">
@@ -3232,35 +3232,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.002275603295886006</v>
+        <v>0.001615536306275759</v>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E21" t="n">
-        <v>0.001409204688916107</v>
+        <v>0.002557803826870271</v>
       </c>
       <c r="F21" t="n">
+        <v>17</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.0003160224410930001</v>
+      </c>
+      <c r="H21" t="n">
         <v>27</v>
       </c>
-      <c r="G21" t="n">
-        <v>0.000442262914799052</v>
-      </c>
-      <c r="H21" t="n">
-        <v>20</v>
-      </c>
       <c r="I21" t="n">
-        <v>0.1295419430619873</v>
+        <v>0.2062187982627752</v>
       </c>
       <c r="J21" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K21" t="n">
-        <v>24.25</v>
+        <v>22.5</v>
       </c>
     </row>
   </sheetData>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4065729105196067</v>
+        <v>0.4165063630280615</v>
       </c>
     </row>
     <row r="3">
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2992099333553406</v>
+        <v>0.2808911641104241</v>
       </c>
     </row>
     <row r="4">
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.07043117580663896</v>
+        <v>0.0704731334153732</v>
       </c>
     </row>
     <row r="5">
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.06347889196297038</v>
+        <v>0.05936462511312079</v>
       </c>
     </row>
     <row r="6">
@@ -3356,7 +3356,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.04282009912729453</v>
+        <v>0.05523915390276699</v>
       </c>
     </row>
     <row r="7">
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01424827950268244</v>
+        <v>0.01437921541051098</v>
       </c>
     </row>
     <row r="8">
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.007345090478667085</v>
+        <v>0.007332764951427079</v>
       </c>
     </row>
     <row r="9">
@@ -3391,11 +3391,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.005953696622513246</v>
+        <v>0.005951551135848279</v>
       </c>
     </row>
     <row r="10">
@@ -3404,11 +3404,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0058600638538843</v>
+        <v>0.005865493220224619</v>
       </c>
     </row>
     <row r="11">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.005718097971075684</v>
+        <v>0.005568558762841301</v>
       </c>
     </row>
     <row r="12">
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.005213653768950966</v>
+        <v>0.00542538573678234</v>
       </c>
     </row>
     <row r="13">
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.00408366209339472</v>
+        <v>0.004053578774404341</v>
       </c>
     </row>
     <row r="14">
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.003852124005685164</v>
+        <v>0.003786938594379947</v>
       </c>
     </row>
     <row r="15">
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.003732832738122984</v>
+        <v>0.003680338482789539</v>
       </c>
     </row>
     <row r="16">
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.003560354189681795</v>
+        <v>0.00358843655999448</v>
       </c>
     </row>
     <row r="17">
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.003447581827407039</v>
+        <v>0.003182975224781823</v>
       </c>
     </row>
     <row r="18">
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.003162079358151949</v>
+        <v>0.003116999146508176</v>
       </c>
     </row>
     <row r="19">
@@ -3521,11 +3521,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.002390475329932857</v>
+        <v>0.002450678522644812</v>
       </c>
     </row>
     <row r="20">
@@ -3534,11 +3534,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.002388679605767266</v>
+        <v>0.002423001199226675</v>
       </c>
     </row>
     <row r="21">
@@ -3547,11 +3547,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.002275603295886006</v>
+        <v>0.002266012182974288</v>
       </c>
     </row>
     <row r="22">
@@ -3560,11 +3560,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.00227475211272811</v>
+        <v>0.00225115840821352</v>
       </c>
     </row>
     <row r="23">
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.002151715685267272</v>
+        <v>0.00220460670377708</v>
       </c>
     </row>
     <row r="24">
@@ -3586,11 +3586,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.002141043114578652</v>
+        <v>0.002181944414213</v>
       </c>
     </row>
     <row r="25">
@@ -3599,11 +3599,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.001977614688915244</v>
+        <v>0.002072288043532046</v>
       </c>
     </row>
     <row r="26">
@@ -3612,11 +3612,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.001963595860471165</v>
+        <v>0.001952816557958622</v>
       </c>
     </row>
     <row r="27">
@@ -3625,11 +3625,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.001933603185737217</v>
+        <v>0.001925401250557361</v>
       </c>
     </row>
     <row r="28">
@@ -3638,11 +3638,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.001921410431688985</v>
+        <v>0.001909589683063649</v>
       </c>
     </row>
     <row r="29">
@@ -3651,11 +3651,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.001889097578054567</v>
+        <v>0.001880153310329902</v>
       </c>
     </row>
     <row r="30">
@@ -3668,7 +3668,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.001875236354155498</v>
+        <v>0.001876100480860019</v>
       </c>
     </row>
     <row r="31">
@@ -3681,7 +3681,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.001669928206103682</v>
+        <v>0.00168310873626361</v>
       </c>
     </row>
     <row r="32">
@@ -3690,11 +3690,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.001591884876387455</v>
+        <v>0.001615536306275759</v>
       </c>
     </row>
     <row r="33">
@@ -3703,11 +3703,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.001590935227078281</v>
+        <v>0.001546442873848397</v>
       </c>
     </row>
     <row r="34">
@@ -3716,11 +3716,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.001523330653525749</v>
+        <v>0.001523763742701117</v>
       </c>
     </row>
     <row r="35">
@@ -3729,11 +3729,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.001496111232371845</v>
+        <v>0.001489522975204905</v>
       </c>
     </row>
     <row r="36">
@@ -3742,11 +3742,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.001465618353457205</v>
+        <v>0.001467879364589689</v>
       </c>
     </row>
     <row r="37">
@@ -3755,11 +3755,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.001444030739204453</v>
+        <v>0.001459353406819576</v>
       </c>
     </row>
     <row r="38">
@@ -3768,11 +3768,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.001426620889287097</v>
+        <v>0.001422216227604319</v>
       </c>
     </row>
     <row r="39">
@@ -3781,11 +3781,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.001395045957988709</v>
+        <v>0.001405256658231053</v>
       </c>
     </row>
     <row r="40">
@@ -3798,7 +3798,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.001359952927898525</v>
+        <v>0.001377660164585235</v>
       </c>
     </row>
     <row r="41">
@@ -3807,11 +3807,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.001359182555521891</v>
+        <v>0.001324181788718726</v>
       </c>
     </row>
     <row r="42">
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.001344698110801744</v>
+        <v>0.0013199485006502</v>
       </c>
     </row>
     <row r="43">
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.001316667902269605</v>
+        <v>0.001278372169820007</v>
       </c>
     </row>
     <row r="44">
@@ -3846,11 +3846,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.001258645102917479</v>
+        <v>0.001259483624557032</v>
       </c>
     </row>
     <row r="45">
@@ -3859,11 +3859,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.001188608104898267</v>
+        <v>0.001170717320282009</v>
       </c>
     </row>
     <row r="46">
@@ -3872,11 +3872,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.001176834384073412</v>
+        <v>0.001159971095830336</v>
       </c>
     </row>
     <row r="47">
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.001138441486449964</v>
+        <v>0.00111841178422654</v>
       </c>
     </row>
     <row r="48">
@@ -3902,7 +3902,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.0009659162451454334</v>
+        <v>0.001105095374194287</v>
       </c>
     </row>
     <row r="49">
@@ -3915,7 +3915,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.0006072118167457299</v>
+        <v>0.0006485909228951996</v>
       </c>
     </row>
     <row r="50">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.0005354569751638635</v>
+        <v>0.0005306475056556192</v>
       </c>
     </row>
     <row r="51">
@@ -3937,11 +3937,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>9.541043300902036e-05</v>
+        <v>0.0001249375002640287</v>
       </c>
     </row>
     <row r="52">
@@ -3950,11 +3950,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7.808758290207801e-05</v>
+        <v>7.577446736926195e-05</v>
       </c>
     </row>
     <row r="53">
@@ -3963,11 +3963,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>7.721435030299638e-05</v>
+        <v>6.737916972965479e-05</v>
       </c>
     </row>
     <row r="54">
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2.081146124410183e-05</v>
+        <v>2.532199209291146e-05</v>
       </c>
     </row>
   </sheetData>
@@ -4024,7 +4024,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3291493018522236</v>
+        <v>0.3306041230813141</v>
       </c>
     </row>
     <row r="3">
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2291797279328061</v>
+        <v>0.2390766078490786</v>
       </c>
     </row>
     <row r="4">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1558290110023217</v>
+        <v>0.1472118822135189</v>
       </c>
     </row>
     <row r="5">
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.07192762145117108</v>
+        <v>0.07063431481632378</v>
       </c>
     </row>
     <row r="6">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.050508469336305</v>
+        <v>0.05099292444392457</v>
       </c>
     </row>
     <row r="7">
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0388937622385257</v>
+        <v>0.0396324080579542</v>
       </c>
     </row>
     <row r="8">
@@ -4098,11 +4098,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.0120158828156668</v>
+        <v>0.01171508403166955</v>
       </c>
     </row>
     <row r="9">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.01114242239312433</v>
+        <v>0.01166209065597926</v>
       </c>
     </row>
     <row r="10">
@@ -4124,11 +4124,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.0110282599486145</v>
+        <v>0.01139603876227962</v>
       </c>
     </row>
     <row r="11">
@@ -4137,11 +4137,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.01086974528925099</v>
+        <v>0.008973586438909669</v>
       </c>
     </row>
     <row r="12">
@@ -4150,11 +4150,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.009198273584937154</v>
+        <v>0.008049120596560178</v>
       </c>
     </row>
     <row r="13">
@@ -4163,11 +4163,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.009018698114905568</v>
+        <v>0.007637278622181098</v>
       </c>
     </row>
     <row r="14">
@@ -4176,11 +4176,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.005242163931629659</v>
+        <v>0.004791652244209006</v>
       </c>
     </row>
     <row r="15">
@@ -4189,11 +4189,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.004392508987762973</v>
+        <v>0.004671017670986557</v>
       </c>
     </row>
     <row r="16">
@@ -4202,11 +4202,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.00371639329167186</v>
+        <v>0.004507777600072711</v>
       </c>
     </row>
     <row r="17">
@@ -4215,11 +4215,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.003472869175817386</v>
+        <v>0.003549982278399404</v>
       </c>
     </row>
     <row r="18">
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.002694814176495566</v>
+        <v>0.002557803826870271</v>
       </c>
     </row>
     <row r="19">
@@ -4245,7 +4245,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.002589998571600898</v>
+        <v>0.002412386175043696</v>
       </c>
     </row>
     <row r="20">
@@ -4258,7 +4258,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.002072561167334866</v>
+        <v>0.002111454812359339</v>
       </c>
     </row>
     <row r="21">
@@ -4267,11 +4267,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.002037237381054784</v>
+        <v>0.001934360536190422</v>
       </c>
     </row>
     <row r="22">
@@ -4280,11 +4280,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.001734285883287098</v>
+        <v>0.001843656198317041</v>
       </c>
     </row>
     <row r="23">
@@ -4293,11 +4293,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.001723245257052869</v>
+        <v>0.001829738778094041</v>
       </c>
     </row>
     <row r="24">
@@ -4306,11 +4306,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.001687484260549532</v>
+        <v>0.001813175004032185</v>
       </c>
     </row>
     <row r="25">
@@ -4319,11 +4319,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.001660669792439465</v>
+        <v>0.001807229545069563</v>
       </c>
     </row>
     <row r="26">
@@ -4332,11 +4332,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.001509004654213302</v>
+        <v>0.001721754149235873</v>
       </c>
     </row>
     <row r="27">
@@ -4345,11 +4345,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.001420542092449193</v>
+        <v>0.001475508310899919</v>
       </c>
     </row>
     <row r="28">
@@ -4362,7 +4362,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.001409204688916107</v>
+        <v>0.001357061971355008</v>
       </c>
     </row>
     <row r="29">
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.001395690074680656</v>
+        <v>0.0013480432808974</v>
       </c>
     </row>
     <row r="30">
@@ -4384,11 +4384,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.001366326113494094</v>
+        <v>0.001237897278353882</v>
       </c>
     </row>
     <row r="31">
@@ -4397,11 +4397,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.001289182559551359</v>
+        <v>0.001231804086661222</v>
       </c>
     </row>
     <row r="32">
@@ -4410,11 +4410,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.001262299624090363</v>
+        <v>0.001207563170348514</v>
       </c>
     </row>
     <row r="33">
@@ -4423,11 +4423,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.001233797996048181</v>
+        <v>0.001154547130382378</v>
       </c>
     </row>
     <row r="34">
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.00114811963404087</v>
+        <v>0.001101450565593942</v>
       </c>
     </row>
     <row r="35">
@@ -4449,11 +4449,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.001137377474102061</v>
+        <v>0.001095079940739656</v>
       </c>
     </row>
     <row r="36">
@@ -4462,11 +4462,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.001109542528416572</v>
+        <v>0.00109379240620066</v>
       </c>
     </row>
     <row r="37">
@@ -4475,11 +4475,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.00107041891465202</v>
+        <v>0.001075282134623642</v>
       </c>
     </row>
     <row r="38">
@@ -4488,11 +4488,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0010598954833534</v>
+        <v>0.001058699724778284</v>
       </c>
     </row>
     <row r="39">
@@ -4501,11 +4501,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.001040180910976187</v>
+        <v>0.00104881979376202</v>
       </c>
     </row>
     <row r="40">
@@ -4514,11 +4514,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.000987889877819074</v>
+        <v>0.001045676264699847</v>
       </c>
     </row>
     <row r="41">
@@ -4527,11 +4527,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0009588233178267449</v>
+        <v>0.001014908604712684</v>
       </c>
     </row>
     <row r="42">
@@ -4544,7 +4544,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0009322712034206816</v>
+        <v>0.001002967469465903</v>
       </c>
     </row>
     <row r="43">
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0009075890504689311</v>
+        <v>0.0009939507152283882</v>
       </c>
     </row>
     <row r="44">
@@ -4566,11 +4566,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0008975503660924299</v>
+        <v>0.0009511806763082975</v>
       </c>
     </row>
     <row r="45">
@@ -4579,11 +4579,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0008770449292562827</v>
+        <v>0.0009266225191322128</v>
       </c>
     </row>
     <row r="46">
@@ -4596,7 +4596,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0008679974287115135</v>
+        <v>0.0009263130496737242</v>
       </c>
     </row>
     <row r="47">
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.0008294176686763347</v>
+        <v>0.0008914295508628588</v>
       </c>
     </row>
     <row r="48">
@@ -4618,11 +4618,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.000791305892487536</v>
+        <v>0.0008008771383007751</v>
       </c>
     </row>
     <row r="49">
@@ -4631,11 +4631,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.000784844347555557</v>
+        <v>0.0007946482086225369</v>
       </c>
     </row>
     <row r="50">
@@ -4644,11 +4644,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.0006949217019225416</v>
+        <v>0.000767815827354959</v>
       </c>
     </row>
     <row r="51">
@@ -4661,7 +4661,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.0005583641966469675</v>
+        <v>0.0005170322901136405</v>
       </c>
     </row>
     <row r="52">
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.0003166854152453804</v>
+        <v>0.0003402447111151486</v>
       </c>
     </row>
     <row r="53">
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.0002184181996498549</v>
+        <v>0.0002812180453595566</v>
       </c>
     </row>
     <row r="54">
@@ -4700,7 +4700,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.0001398858186863133</v>
+        <v>0.0001221167458791846</v>
       </c>
     </row>
   </sheetData>
@@ -4749,10 +4749,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4644109321358291</v>
+        <v>0.4761045525333641</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03549717864035253</v>
+        <v>0.03515390124805566</v>
       </c>
     </row>
     <row r="3">
@@ -4765,10 +4765,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2967604346712478</v>
+        <v>0.2791487904168628</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02342329728454565</v>
+        <v>0.02224560841029055</v>
       </c>
     </row>
     <row r="4">
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.02469442225621099</v>
+        <v>0.02360148039191765</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004005080789371404</v>
+        <v>0.003959301992855861</v>
       </c>
     </row>
     <row r="5">
@@ -4793,14 +4793,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_quality_apparent_color_1</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.01205830762074601</v>
+        <v>0.01139062738611735</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002441294292143686</v>
+        <v>0.003265662775843139</v>
       </c>
     </row>
     <row r="6">
@@ -4809,14 +4809,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01167431989016169</v>
+        <v>0.01033062653383405</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003376003990564829</v>
+        <v>0.002037440960858772</v>
       </c>
     </row>
     <row r="7">
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.005706524045798933</v>
+        <v>0.008552106770008039</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001602583362467121</v>
+        <v>0.002068625637215055</v>
       </c>
     </row>
     <row r="8">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.002466793375890008</v>
+        <v>0.002523136450429464</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0005446449769103913</v>
+        <v>0.0005373922822073779</v>
       </c>
     </row>
     <row r="9">
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.002388489583926767</v>
+        <v>0.002352385369849619</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001123155441033116</v>
+        <v>0.001171440340158616</v>
       </c>
     </row>
     <row r="10">
@@ -4877,10 +4877,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.002259821391015104</v>
+        <v>0.002136458895167448</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001307725882813622</v>
+        <v>0.001249642493012471</v>
       </c>
     </row>
     <row r="11">
@@ -4889,14 +4889,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001972247393986837</v>
+        <v>0.001733866369081016</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0006738943479619148</v>
+        <v>0.001280745624214429</v>
       </c>
     </row>
     <row r="12">
@@ -4905,14 +4905,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001872568715010758</v>
+        <v>0.001664456317987884</v>
       </c>
       <c r="D12" t="n">
-        <v>0.001182416370468517</v>
+        <v>0.0006350417102082709</v>
       </c>
     </row>
     <row r="13">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001290483164255839</v>
+        <v>0.001482728878322677</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0001487101031427858</v>
+        <v>0.0001794409693939473</v>
       </c>
     </row>
     <row r="14">
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.001207182745202129</v>
+        <v>0.001297587529406119</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0006916333620356577</v>
+        <v>0.0006847882641749693</v>
       </c>
     </row>
     <row r="15">
@@ -4953,14 +4953,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.001013569475495835</v>
+        <v>0.001005090769901163</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0002197376150804986</v>
+        <v>0.0002328475787992315</v>
       </c>
     </row>
     <row r="16">
@@ -4969,14 +4969,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0008620481737081409</v>
+        <v>0.0009216647418518575</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0004658090871524794</v>
+        <v>0.0002641336677146884</v>
       </c>
     </row>
     <row r="17">
@@ -4985,14 +4985,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0007934977301886637</v>
+        <v>0.0008939545123207493</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0004461399874994465</v>
+        <v>0.0004956754370202703</v>
       </c>
     </row>
     <row r="18">
@@ -5001,14 +5001,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0007476917004785144</v>
+        <v>0.0006425803427979049</v>
       </c>
       <c r="D18" t="n">
-        <v>0.000250038804977906</v>
+        <v>0.0004416961751193929</v>
       </c>
     </row>
     <row r="19">
@@ -5017,14 +5017,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0004935313015577925</v>
+        <v>0.0004939475910281877</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0002204942295493547</v>
+        <v>0.0002284868843701049</v>
       </c>
     </row>
     <row r="20">
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.00047304882669158</v>
+        <v>0.00047072720512219</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0001914563339534164</v>
+        <v>0.0002011924938085931</v>
       </c>
     </row>
     <row r="21">
@@ -5049,14 +5049,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.000442262914799052</v>
+        <v>0.0004189207118883931</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0004231547766510074</v>
+        <v>0.0002205058215989641</v>
       </c>
     </row>
     <row r="22">
@@ -5065,14 +5065,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0004357877178527647</v>
+        <v>0.0004163616826270977</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0001530037576485963</v>
+        <v>0.0004101029283148259</v>
       </c>
     </row>
     <row r="23">
@@ -5081,14 +5081,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0004180963464805121</v>
+        <v>0.0004086844772112186</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0002110457267646595</v>
+        <v>0.0002584483202664285</v>
       </c>
     </row>
     <row r="24">
@@ -5097,14 +5097,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0004121634172346899</v>
+        <v>0.000387969342948602</v>
       </c>
       <c r="D24" t="n">
-        <v>6.747963274953249e-05</v>
+        <v>0.0004842629602930905</v>
       </c>
     </row>
     <row r="25">
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0004120665964466142</v>
+        <v>0.0003681251614669922</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0001753621395826426</v>
+        <v>0.0001901413595004222</v>
       </c>
     </row>
     <row r="26">
@@ -5129,14 +5129,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0003884077899509064</v>
+        <v>0.0003298602118368299</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0002822183452349382</v>
+        <v>7.420256107290811e-05</v>
       </c>
     </row>
     <row r="27">
@@ -5145,14 +5145,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0003296159210498528</v>
+        <v>0.0003281996298877377</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0002172008167585849</v>
+        <v>0.0001265747425788584</v>
       </c>
     </row>
     <row r="28">
@@ -5161,14 +5161,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0003107090366941567</v>
+        <v>0.0003160224410930001</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0002604431644271064</v>
+        <v>0.0001936066576621885</v>
       </c>
     </row>
     <row r="29">
@@ -5177,14 +5177,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0002671008442111988</v>
+        <v>0.0002886776865377749</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0005101564343019618</v>
+        <v>0.0002998485437186236</v>
       </c>
     </row>
     <row r="30">
@@ -5193,14 +5193,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0002302416522496187</v>
+        <v>0.0002731873965256759</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0003271089023577292</v>
+        <v>0.0002780621106458746</v>
       </c>
     </row>
     <row r="31">
@@ -5209,14 +5209,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0002258320645653788</v>
+        <v>0.0002265491737181602</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0002072438723495021</v>
+        <v>0.0004667151962868474</v>
       </c>
     </row>
     <row r="32">
@@ -5225,14 +5225,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0001723422210909709</v>
+        <v>0.000143322314579053</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0004995759723323336</v>
+        <v>0.0001606887678236269</v>
       </c>
     </row>
     <row r="33">
@@ -5241,14 +5241,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0001417221139674907</v>
+        <v>0.000125652302639645</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0005062690086954437</v>
+        <v>0.0002027547360125371</v>
       </c>
     </row>
     <row r="34">
@@ -5257,14 +5257,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0001129120157824515</v>
+        <v>0.0001045709538454842</v>
       </c>
       <c r="D34" t="n">
-        <v>7.795468474211582e-05</v>
+        <v>0.0005433195132755192</v>
       </c>
     </row>
     <row r="35">
@@ -5273,14 +5273,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7.578620613383214e-05</v>
+        <v>0.0001004520136867915</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0001969758556252328</v>
+        <v>7.699375576561803e-05</v>
       </c>
     </row>
     <row r="36">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5.64339309587325e-05</v>
+        <v>4.996488354248596e-05</v>
       </c>
       <c r="D36" t="n">
-        <v>8.621437876059603e-05</v>
+        <v>9.530251591256622e-05</v>
       </c>
     </row>
     <row r="37">
@@ -5305,14 +5305,14 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>white_quality_moisture_2</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3.765699218413188e-05</v>
+        <v>4.448725532437692e-05</v>
       </c>
       <c r="D37" t="n">
-        <v>7.888138603156212e-05</v>
+        <v>8.102294106327235e-05</v>
       </c>
     </row>
     <row r="38">
@@ -5321,14 +5321,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2.379094596457465e-05</v>
+        <v>4.357300668264008e-05</v>
       </c>
       <c r="D38" t="n">
-        <v>3.079025050264498e-06</v>
+        <v>0.0002140827525695976</v>
       </c>
     </row>
     <row r="39">
@@ -5337,14 +5337,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2.359375964066102e-05</v>
+        <v>4.210899185662642e-05</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0001004421474748148</v>
+        <v>0.0001591835438267494</v>
       </c>
     </row>
     <row r="40">
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1.263266027968779e-05</v>
+        <v>2.258744967039705e-05</v>
       </c>
       <c r="D40" t="n">
-        <v>1.484136921244717e-05</v>
+        <v>2.362033107267677e-05</v>
       </c>
     </row>
     <row r="41">
@@ -5369,14 +5369,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-2.648016097196448e-05</v>
+        <v>6.82048063872509e-06</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0001247597014616126</v>
+        <v>4.485582365181625e-05</v>
       </c>
     </row>
     <row r="42">
@@ -5385,14 +5385,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-3.437122920015856e-05</v>
+        <v>2.762245849674549e-06</v>
       </c>
       <c r="D42" t="n">
-        <v>0.000103748084820849</v>
+        <v>0.0001595544517067935</v>
       </c>
     </row>
     <row r="43">
@@ -5401,14 +5401,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-3.56381611746448e-05</v>
+        <v>-9.861126962218414e-07</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0001082722951239288</v>
+        <v>0.0001482059553467903</v>
       </c>
     </row>
     <row r="44">
@@ -5417,14 +5417,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-5.527578036853553e-05</v>
+        <v>-9.206848448506388e-06</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0001356301504080031</v>
+        <v>7.775929036751156e-06</v>
       </c>
     </row>
     <row r="45">
@@ -5433,14 +5433,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-6.038959025870261e-05</v>
+        <v>-1.721897560962304e-05</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0002244041977878227</v>
+        <v>9.490379946939309e-05</v>
       </c>
     </row>
     <row r="46">
@@ -5449,14 +5449,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>shift_name</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-6.196392031168063e-05</v>
+        <v>-3.494969673081272e-05</v>
       </c>
       <c r="D46" t="n">
-        <v>3.097646177965357e-05</v>
+        <v>0.0001287288212643009</v>
       </c>
     </row>
     <row r="47">
@@ -5465,14 +5465,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-6.373590530978079e-05</v>
+        <v>-5.125645230295017e-05</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0001397211470996247</v>
+        <v>1.941419715885385e-05</v>
       </c>
     </row>
     <row r="48">
@@ -5481,14 +5481,14 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-7.365142936333058e-05</v>
+        <v>-5.223207071624048e-05</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0001738436671129335</v>
+        <v>0.0005565570931598214</v>
       </c>
     </row>
     <row r="49">
@@ -5497,14 +5497,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-9.283608491721385e-05</v>
+        <v>-7.407733931898974e-05</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0005584237535329543</v>
+        <v>0.0002236628811538142</v>
       </c>
     </row>
     <row r="50">
@@ -5513,14 +5513,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-9.551979519119014e-05</v>
+        <v>-0.0001195851064772491</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0001495331024290542</v>
+        <v>0.0001561249239193249</v>
       </c>
     </row>
     <row r="51">
@@ -5529,14 +5529,14 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-0.0001017768120741169</v>
+        <v>-0.0003023502629998176</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0002136165199503166</v>
+        <v>0.0002050707450226975</v>
       </c>
     </row>
     <row r="52">
@@ -5545,14 +5545,14 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.0002712248262002337</v>
+        <v>-0.0003126019529183899</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0002342011045836843</v>
+        <v>0.0002626275236228015</v>
       </c>
     </row>
     <row r="53">
@@ -5561,14 +5561,14 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.0002758897424568807</v>
+        <v>-0.0003389814205102981</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0002922624587833606</v>
+        <v>0.0002626940205436082</v>
       </c>
     </row>
     <row r="54">
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.0006843931404619585</v>
+        <v>-0.0006547469196777067</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0003616293825289796</v>
+        <v>0.0003377717366934673</v>
       </c>
     </row>
   </sheetData>
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.516185073214777</v>
+        <v>1.236279030419674</v>
       </c>
     </row>
     <row r="3">
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.438671876188928</v>
+        <v>1.198349616808716</v>
       </c>
     </row>
     <row r="4">
@@ -5654,7 +5654,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.423770799533282</v>
+        <v>1.072530669500765</v>
       </c>
     </row>
     <row r="5">
@@ -5667,7 +5667,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.947515211524121</v>
+        <v>0.6822701612908508</v>
       </c>
     </row>
     <row r="6">
@@ -5680,7 +5680,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.8867983829986508</v>
+        <v>0.6640910913673306</v>
       </c>
     </row>
     <row r="7">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.8392709336065023</v>
+        <v>0.6178166855264426</v>
       </c>
     </row>
     <row r="8">
@@ -5702,11 +5702,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.7102381910625768</v>
+        <v>0.4961148960923709</v>
       </c>
     </row>
     <row r="9">
@@ -5715,11 +5715,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.672769671377254</v>
+        <v>0.4739090618199784</v>
       </c>
     </row>
     <row r="10">
@@ -5732,7 +5732,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6266420055755306</v>
+        <v>0.3677464095429919</v>
       </c>
     </row>
     <row r="11">
@@ -5745,7 +5745,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.2864599872107711</v>
+        <v>0.28650978335402</v>
       </c>
     </row>
     <row r="12">
@@ -5754,11 +5754,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.2678695621723715</v>
+        <v>0.2398858944846856</v>
       </c>
     </row>
     <row r="13">
@@ -5767,11 +5767,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>white_quality_solution_color_1</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.2408345741623004</v>
+        <v>0.2387552123432464</v>
       </c>
     </row>
     <row r="14">
@@ -5780,11 +5780,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>white_quality_apparent_color_2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.2165485625793266</v>
+        <v>0.229810539278942</v>
       </c>
     </row>
     <row r="15">
@@ -5793,11 +5793,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.2066749365948048</v>
+        <v>0.2162787103716499</v>
       </c>
     </row>
     <row r="16">
@@ -5810,7 +5810,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.2025258905133143</v>
+        <v>0.2062187982627752</v>
       </c>
     </row>
     <row r="17">
@@ -5819,11 +5819,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.194221959201021</v>
+        <v>0.2045485718760616</v>
       </c>
     </row>
     <row r="18">
@@ -5832,11 +5832,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.1927333513280312</v>
+        <v>0.1975684889068154</v>
       </c>
     </row>
     <row r="19">
@@ -5845,11 +5845,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.1921799270615958</v>
+        <v>0.1925807873599821</v>
       </c>
     </row>
     <row r="20">
@@ -5858,11 +5858,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.1724460051318526</v>
+        <v>0.1601129381638917</v>
       </c>
     </row>
     <row r="21">
@@ -5871,11 +5871,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.1703142646263009</v>
+        <v>0.1598125154675447</v>
       </c>
     </row>
     <row r="22">
@@ -5888,7 +5888,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.1659753101927781</v>
+        <v>0.1533962047699582</v>
       </c>
     </row>
     <row r="23">
@@ -5897,11 +5897,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>white_quality_ash_1</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.1593929350952812</v>
+        <v>0.1416256039247572</v>
       </c>
     </row>
     <row r="24">
@@ -5910,11 +5910,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.151174213998134</v>
+        <v>0.1407178423155786</v>
       </c>
     </row>
     <row r="25">
@@ -5923,11 +5923,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>white_quality_solution_color_2</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.1487373275154553</v>
+        <v>0.1399203475237156</v>
       </c>
     </row>
     <row r="26">
@@ -5936,11 +5936,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.1482583563546349</v>
+        <v>0.1374923718309686</v>
       </c>
     </row>
     <row r="27">
@@ -5949,11 +5949,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.1469591885128838</v>
+        <v>0.1314372965756354</v>
       </c>
     </row>
     <row r="28">
@@ -5962,11 +5962,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.1465380298983885</v>
+        <v>0.1294575803156772</v>
       </c>
     </row>
     <row r="29">
@@ -5975,11 +5975,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.1430346516538337</v>
+        <v>0.1282316679533264</v>
       </c>
     </row>
     <row r="30">
@@ -5988,11 +5988,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.1361843957214524</v>
+        <v>0.1215714553125802</v>
       </c>
     </row>
     <row r="31">
@@ -6001,11 +6001,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.1295419430619873</v>
+        <v>0.1198625489822751</v>
       </c>
     </row>
     <row r="32">
@@ -6014,11 +6014,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.1248616794782231</v>
+        <v>0.1150710484016844</v>
       </c>
     </row>
     <row r="33">
@@ -6027,11 +6027,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.1223398881841007</v>
+        <v>0.1148730857526199</v>
       </c>
     </row>
     <row r="34">
@@ -6044,7 +6044,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.1221860038175966</v>
+        <v>0.1134854836112336</v>
       </c>
     </row>
     <row r="35">
@@ -6057,7 +6057,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.1216199643191032</v>
+        <v>0.11158529414972</v>
       </c>
     </row>
     <row r="36">
@@ -6066,11 +6066,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.1038703040238067</v>
+        <v>0.1062600742559612</v>
       </c>
     </row>
     <row r="37">
@@ -6079,11 +6079,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.1001025315170314</v>
+        <v>0.106171265677435</v>
       </c>
     </row>
     <row r="38">
@@ -6092,11 +6092,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.09944565930027194</v>
+        <v>0.1038346518305531</v>
       </c>
     </row>
     <row r="39">
@@ -6105,11 +6105,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.09164550956329354</v>
+        <v>0.09691135010235818</v>
       </c>
     </row>
     <row r="40">
@@ -6118,11 +6118,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.09076655113070364</v>
+        <v>0.08786926996012312</v>
       </c>
     </row>
     <row r="41">
@@ -6131,11 +6131,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.08955986934737403</v>
+        <v>0.08537318741232736</v>
       </c>
     </row>
     <row r="42">
@@ -6144,11 +6144,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>white_quality_moisture_1</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.08619964502381627</v>
+        <v>0.07723852475526449</v>
       </c>
     </row>
     <row r="43">
@@ -6157,11 +6157,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.08446606360304898</v>
+        <v>0.07325591331459158</v>
       </c>
     </row>
     <row r="44">
@@ -6170,11 +6170,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.08358444248332875</v>
+        <v>0.07201304738427394</v>
       </c>
     </row>
     <row r="45">
@@ -6187,7 +6187,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.07780667667315466</v>
+        <v>0.06522008278876879</v>
       </c>
     </row>
     <row r="46">
@@ -6196,11 +6196,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.07439785613225913</v>
+        <v>0.05844033263516879</v>
       </c>
     </row>
     <row r="47">
@@ -6209,11 +6209,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.06806981505572551</v>
+        <v>0.05784603239742125</v>
       </c>
     </row>
     <row r="48">
@@ -6222,11 +6222,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.06405133728471712</v>
+        <v>0.0524700468327115</v>
       </c>
     </row>
     <row r="49">
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.03700780804195913</v>
+        <v>0.04452011846688331</v>
       </c>
     </row>
     <row r="50">
@@ -6248,11 +6248,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.03668306533699361</v>
+        <v>0.02298624135869165</v>
       </c>
     </row>
     <row r="51">
@@ -6261,11 +6261,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>white_quality_moisture_2</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.02616468904652591</v>
+        <v>0.005638754778659383</v>
       </c>
     </row>
     <row r="52">
@@ -6278,7 +6278,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.01947477582113599</v>
+        <v>0.0007857841193852355</v>
       </c>
     </row>
     <row r="53">
@@ -6318,7 +6318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6334,15 +6334,30 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>training_rows_used</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>permutation_rows_used</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>source_variables_ranked</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>encoded_feature_count</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>preprocessing_scope</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>created_at_utc</t>
         </is>
@@ -6358,14 +6373,25 @@
         <v>788</v>
       </c>
       <c r="C2" t="n">
+        <v>591</v>
+      </c>
+      <c r="D2" t="n">
+        <v>197</v>
+      </c>
+      <c r="E2" t="n">
         <v>53</v>
       </c>
-      <c r="D2" t="n">
-        <v>446</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-06-11 09:49:48 UTC</t>
+      <c r="F2" t="n">
+        <v>414</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>fit_on_training_split_only</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-06-14 21:58:10 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_apparent_color.xlsx
+++ b/NN/reports/feature_importance_white_apparent_color.xlsx
@@ -550,7 +550,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2791487904168628</v>
+        <v>0.2791487904168629</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -587,7 +587,7 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02360148039191765</v>
+        <v>0.02360148039191767</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -624,7 +624,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008552106770008039</v>
+        <v>0.008552106770008071</v>
       </c>
       <c r="H5" t="n">
         <v>6</v>
@@ -661,7 +661,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001482728878322677</v>
+        <v>0.0014827288783222</v>
       </c>
       <c r="H6" t="n">
         <v>12</v>
@@ -698,7 +698,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01139062738611735</v>
+        <v>0.01139062738611738</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
@@ -735,7 +735,7 @@
         <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01033062653383405</v>
+        <v>0.01033062653383406</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
@@ -772,7 +772,7 @@
         <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002352385369849619</v>
+        <v>0.002352385369849608</v>
       </c>
       <c r="H9" t="n">
         <v>8</v>
@@ -809,7 +809,7 @@
         <v>16</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002523136450429464</v>
+        <v>0.002523136450429486</v>
       </c>
       <c r="H10" t="n">
         <v>7</v>
@@ -846,7 +846,7 @@
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002136458895167448</v>
+        <v>0.002136458895167481</v>
       </c>
       <c r="H11" t="n">
         <v>9</v>
@@ -883,7 +883,7 @@
         <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001005090769901163</v>
+        <v>0.001005090769901151</v>
       </c>
       <c r="H12" t="n">
         <v>14</v>
@@ -957,7 +957,7 @@
         <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001733866369081016</v>
+        <v>0.001733866369081005</v>
       </c>
       <c r="H14" t="n">
         <v>10</v>
@@ -1068,7 +1068,7 @@
         <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>0.001297587529406119</v>
+        <v>0.00129758752940613</v>
       </c>
       <c r="H17" t="n">
         <v>13</v>
@@ -1216,7 +1216,7 @@
         <v>17</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0003160224410930001</v>
+        <v>0.0003160224410929891</v>
       </c>
       <c r="H21" t="n">
         <v>27</v>
@@ -1253,7 +1253,7 @@
         <v>29</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0001045709538454842</v>
+        <v>0.0001045709538454731</v>
       </c>
       <c r="H22" t="n">
         <v>33</v>
@@ -1327,7 +1327,7 @@
         <v>28</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0002265491737181602</v>
+        <v>0.0002265491737181713</v>
       </c>
       <c r="H24" t="n">
         <v>30</v>
@@ -1364,7 +1364,7 @@
         <v>22</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.0006547469196777067</v>
+        <v>-0.0006547469196776956</v>
       </c>
       <c r="H25" t="n">
         <v>53</v>
@@ -1475,7 +1475,7 @@
         <v>43</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0006425803427979049</v>
+        <v>0.0006425803427979271</v>
       </c>
       <c r="H28" t="n">
         <v>17</v>
@@ -1512,7 +1512,7 @@
         <v>31</v>
       </c>
       <c r="G29" t="n">
-        <v>0.000143322314579053</v>
+        <v>0.0001433223145790419</v>
       </c>
       <c r="H29" t="n">
         <v>31</v>
@@ -1586,7 +1586,7 @@
         <v>24</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.0001195851064772491</v>
+        <v>-0.0001195851064772269</v>
       </c>
       <c r="H31" t="n">
         <v>49</v>
@@ -1623,7 +1623,7 @@
         <v>23</v>
       </c>
       <c r="G32" t="n">
-        <v>2.762245849674549e-06</v>
+        <v>2.762245849663447e-06</v>
       </c>
       <c r="H32" t="n">
         <v>41</v>
@@ -1697,7 +1697,7 @@
         <v>33</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0004939475910281877</v>
+        <v>0.0004939475910281765</v>
       </c>
       <c r="H34" t="n">
         <v>18</v>
@@ -1734,7 +1734,7 @@
         <v>20</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.0003126019529183899</v>
+        <v>-0.0003126019529183788</v>
       </c>
       <c r="H35" t="n">
         <v>51</v>
@@ -1771,7 +1771,7 @@
         <v>26</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.0003389814205102981</v>
+        <v>-0.000338981420510287</v>
       </c>
       <c r="H36" t="n">
         <v>52</v>
@@ -1845,7 +1845,7 @@
         <v>35</v>
       </c>
       <c r="G38" t="n">
-        <v>-5.223207071624048e-05</v>
+        <v>-5.223207071622937e-05</v>
       </c>
       <c r="H38" t="n">
         <v>47</v>
@@ -1882,7 +1882,7 @@
         <v>32</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0003298602118368299</v>
+        <v>0.0003298602118368188</v>
       </c>
       <c r="H39" t="n">
         <v>25</v>
@@ -1919,7 +1919,7 @@
         <v>41</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0003681251614669922</v>
+        <v>0.0003681251614669811</v>
       </c>
       <c r="H40" t="n">
         <v>24</v>
@@ -1956,7 +1956,7 @@
         <v>42</v>
       </c>
       <c r="G41" t="n">
-        <v>4.357300668264008e-05</v>
+        <v>4.357300668266229e-05</v>
       </c>
       <c r="H41" t="n">
         <v>37</v>
@@ -1993,7 +1993,7 @@
         <v>40</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0001004520136867915</v>
+        <v>0.0001004520136867804</v>
       </c>
       <c r="H42" t="n">
         <v>34</v>
@@ -2030,7 +2030,7 @@
         <v>34</v>
       </c>
       <c r="G43" t="n">
-        <v>4.210899185662642e-05</v>
+        <v>4.210899185663752e-05</v>
       </c>
       <c r="H43" t="n">
         <v>38</v>
@@ -2141,7 +2141,7 @@
         <v>45</v>
       </c>
       <c r="G46" t="n">
-        <v>-3.494969673081272e-05</v>
+        <v>-3.494969673079051e-05</v>
       </c>
       <c r="H46" t="n">
         <v>45</v>
@@ -2178,7 +2178,7 @@
         <v>49</v>
       </c>
       <c r="G47" t="n">
-        <v>4.996488354248596e-05</v>
+        <v>4.996488354246376e-05</v>
       </c>
       <c r="H47" t="n">
         <v>35</v>
@@ -2215,7 +2215,7 @@
         <v>46</v>
       </c>
       <c r="G48" t="n">
-        <v>4.448725532437692e-05</v>
+        <v>4.448725532436581e-05</v>
       </c>
       <c r="H48" t="n">
         <v>36</v>
@@ -2289,7 +2289,7 @@
         <v>48</v>
       </c>
       <c r="G50" t="n">
-        <v>-1.721897560962304e-05</v>
+        <v>-1.721897560961194e-05</v>
       </c>
       <c r="H50" t="n">
         <v>44</v>
@@ -2326,7 +2326,7 @@
         <v>52</v>
       </c>
       <c r="G51" t="n">
-        <v>2.258744967039705e-05</v>
+        <v>2.258744967038595e-05</v>
       </c>
       <c r="H51" t="n">
         <v>39</v>
@@ -2363,7 +2363,7 @@
         <v>50</v>
       </c>
       <c r="G52" t="n">
-        <v>6.82048063872509e-06</v>
+        <v>6.820480638736192e-06</v>
       </c>
       <c r="H52" t="n">
         <v>40</v>
@@ -2400,7 +2400,7 @@
         <v>53</v>
       </c>
       <c r="G53" t="n">
-        <v>-9.206848448506388e-06</v>
+        <v>-9.206848448517491e-06</v>
       </c>
       <c r="H53" t="n">
         <v>43</v>
@@ -2437,7 +2437,7 @@
         <v>51</v>
       </c>
       <c r="G54" t="n">
-        <v>-5.125645230295017e-05</v>
+        <v>-5.125645230293907e-05</v>
       </c>
       <c r="H54" t="n">
         <v>46</v>
@@ -2582,7 +2582,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2791487904168628</v>
+        <v>0.2791487904168629</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -2619,7 +2619,7 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02360148039191765</v>
+        <v>0.02360148039191767</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -2656,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008552106770008039</v>
+        <v>0.008552106770008071</v>
       </c>
       <c r="H5" t="n">
         <v>6</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001482728878322677</v>
+        <v>0.0014827288783222</v>
       </c>
       <c r="H6" t="n">
         <v>12</v>
@@ -2730,7 +2730,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01139062738611735</v>
+        <v>0.01139062738611738</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
@@ -2767,7 +2767,7 @@
         <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01033062653383405</v>
+        <v>0.01033062653383406</v>
       </c>
       <c r="H8" t="n">
         <v>5</v>
@@ -2804,7 +2804,7 @@
         <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002352385369849619</v>
+        <v>0.002352385369849608</v>
       </c>
       <c r="H9" t="n">
         <v>8</v>
@@ -2841,7 +2841,7 @@
         <v>16</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002523136450429464</v>
+        <v>0.002523136450429486</v>
       </c>
       <c r="H10" t="n">
         <v>7</v>
@@ -2878,7 +2878,7 @@
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002136458895167448</v>
+        <v>0.002136458895167481</v>
       </c>
       <c r="H11" t="n">
         <v>9</v>
@@ -2915,7 +2915,7 @@
         <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001005090769901163</v>
+        <v>0.001005090769901151</v>
       </c>
       <c r="H12" t="n">
         <v>14</v>
@@ -2989,7 +2989,7 @@
         <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001733866369081016</v>
+        <v>0.001733866369081005</v>
       </c>
       <c r="H14" t="n">
         <v>10</v>
@@ -3100,7 +3100,7 @@
         <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>0.001297587529406119</v>
+        <v>0.00129758752940613</v>
       </c>
       <c r="H17" t="n">
         <v>13</v>
@@ -3248,7 +3248,7 @@
         <v>17</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0003160224410930001</v>
+        <v>0.0003160224410929891</v>
       </c>
       <c r="H21" t="n">
         <v>27</v>
@@ -4752,7 +4752,7 @@
         <v>0.4761045525333641</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03515390124805566</v>
+        <v>0.03515390124805571</v>
       </c>
     </row>
     <row r="3">
@@ -4765,10 +4765,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2791487904168628</v>
+        <v>0.2791487904168629</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02224560841029055</v>
+        <v>0.02224560841029052</v>
       </c>
     </row>
     <row r="4">
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.02360148039191765</v>
+        <v>0.02360148039191767</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003959301992855861</v>
+        <v>0.003959301992855883</v>
       </c>
     </row>
     <row r="5">
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.01139062738611735</v>
+        <v>0.01139062738611738</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003265662775843139</v>
+        <v>0.003265662775843141</v>
       </c>
     </row>
     <row r="6">
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01033062653383405</v>
+        <v>0.01033062653383406</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002037440960858772</v>
+        <v>0.002037440960858786</v>
       </c>
     </row>
     <row r="7">
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.008552106770008039</v>
+        <v>0.008552106770008071</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002068625637215055</v>
+        <v>0.002068625637215081</v>
       </c>
     </row>
     <row r="8">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.002523136450429464</v>
+        <v>0.002523136450429486</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0005373922822073779</v>
+        <v>0.0005373922822073943</v>
       </c>
     </row>
     <row r="9">
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.002352385369849619</v>
+        <v>0.002352385369849608</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001171440340158616</v>
+        <v>0.001171440340158609</v>
       </c>
     </row>
     <row r="10">
@@ -4877,10 +4877,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.002136458895167448</v>
+        <v>0.002136458895167481</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001249642493012471</v>
+        <v>0.001249642493012473</v>
       </c>
     </row>
     <row r="11">
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001733866369081016</v>
+        <v>0.001733866369081005</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001280745624214429</v>
+        <v>0.001280745624214428</v>
       </c>
     </row>
     <row r="12">
@@ -4912,7 +4912,7 @@
         <v>0.001664456317987884</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0006350417102082709</v>
+        <v>0.0006350417102082824</v>
       </c>
     </row>
     <row r="13">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001482728878322677</v>
+        <v>0.0014827288783222</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0001794409693939473</v>
+        <v>0.0001794409693926725</v>
       </c>
     </row>
     <row r="14">
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.001297587529406119</v>
+        <v>0.00129758752940613</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0006847882641749693</v>
+        <v>0.0006847882641749602</v>
       </c>
     </row>
     <row r="15">
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.001005090769901163</v>
+        <v>0.001005090769901151</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0002328475787992315</v>
+        <v>0.0002328475787992394</v>
       </c>
     </row>
     <row r="16">
@@ -4976,7 +4976,7 @@
         <v>0.0009216647418518575</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0002641336677146884</v>
+        <v>0.0002641336677146671</v>
       </c>
     </row>
     <row r="17">
@@ -4992,7 +4992,7 @@
         <v>0.0008939545123207493</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0004956754370202703</v>
+        <v>0.0004956754370202931</v>
       </c>
     </row>
     <row r="18">
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0006425803427979049</v>
+        <v>0.0006425803427979271</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0004416961751193929</v>
+        <v>0.0004416961751193849</v>
       </c>
     </row>
     <row r="19">
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0004939475910281877</v>
+        <v>0.0004939475910281765</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0002284868843701049</v>
+        <v>0.0002284868843701428</v>
       </c>
     </row>
     <row r="20">
@@ -5040,7 +5040,7 @@
         <v>0.00047072720512219</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0002011924938085931</v>
+        <v>0.0002011924938086137</v>
       </c>
     </row>
     <row r="21">
@@ -5056,7 +5056,7 @@
         <v>0.0004189207118883931</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0002205058215989641</v>
+        <v>0.0002205058215989761</v>
       </c>
     </row>
     <row r="22">
@@ -5072,7 +5072,7 @@
         <v>0.0004163616826270977</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0004101029283148259</v>
+        <v>0.0004101029283148488</v>
       </c>
     </row>
     <row r="23">
@@ -5088,7 +5088,7 @@
         <v>0.0004086844772112186</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0002584483202664285</v>
+        <v>0.0002584483202664728</v>
       </c>
     </row>
     <row r="24">
@@ -5104,7 +5104,7 @@
         <v>0.000387969342948602</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0004842629602930905</v>
+        <v>0.0004842629602930608</v>
       </c>
     </row>
     <row r="25">
@@ -5117,10 +5117,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0003681251614669922</v>
+        <v>0.0003681251614669811</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0001901413595004222</v>
+        <v>0.0001901413595004068</v>
       </c>
     </row>
     <row r="26">
@@ -5133,10 +5133,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0003298602118368299</v>
+        <v>0.0003298602118368188</v>
       </c>
       <c r="D26" t="n">
-        <v>7.420256107290811e-05</v>
+        <v>7.42025610728648e-05</v>
       </c>
     </row>
     <row r="27">
@@ -5152,7 +5152,7 @@
         <v>0.0003281996298877377</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0001265747425788584</v>
+        <v>0.0001265747425788562</v>
       </c>
     </row>
     <row r="28">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0003160224410930001</v>
+        <v>0.0003160224410929891</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0001936066576621885</v>
+        <v>0.0001936066576622069</v>
       </c>
     </row>
     <row r="29">
@@ -5184,7 +5184,7 @@
         <v>0.0002886776865377749</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0002998485437186236</v>
+        <v>0.0002998485437186469</v>
       </c>
     </row>
     <row r="30">
@@ -5200,7 +5200,7 @@
         <v>0.0002731873965256759</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0002780621106458746</v>
+        <v>0.000278062110645897</v>
       </c>
     </row>
     <row r="31">
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0002265491737181602</v>
+        <v>0.0002265491737181713</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0004667151962868474</v>
+        <v>0.0004667151962868532</v>
       </c>
     </row>
     <row r="32">
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.000143322314579053</v>
+        <v>0.0001433223145790419</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0001606887678236269</v>
+        <v>0.0001606887678236195</v>
       </c>
     </row>
     <row r="33">
@@ -5248,7 +5248,7 @@
         <v>0.000125652302639645</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0002027547360125371</v>
+        <v>0.0002027547360125282</v>
       </c>
     </row>
     <row r="34">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0001045709538454842</v>
+        <v>0.0001045709538454731</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0005433195132755192</v>
+        <v>0.0005433195132755317</v>
       </c>
     </row>
     <row r="35">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0001004520136867915</v>
+        <v>0.0001004520136867804</v>
       </c>
       <c r="D35" t="n">
-        <v>7.699375576561803e-05</v>
+        <v>7.699375576561304e-05</v>
       </c>
     </row>
     <row r="36">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4.996488354248596e-05</v>
+        <v>4.996488354246376e-05</v>
       </c>
       <c r="D36" t="n">
-        <v>9.530251591256622e-05</v>
+        <v>9.530251591256675e-05</v>
       </c>
     </row>
     <row r="37">
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4.448725532437692e-05</v>
+        <v>4.448725532436581e-05</v>
       </c>
       <c r="D37" t="n">
-        <v>8.102294106327235e-05</v>
+        <v>8.10229410632983e-05</v>
       </c>
     </row>
     <row r="38">
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4.357300668264008e-05</v>
+        <v>4.357300668266229e-05</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0002140827525695976</v>
+        <v>0.0002140827525696152</v>
       </c>
     </row>
     <row r="39">
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4.210899185662642e-05</v>
+        <v>4.210899185663752e-05</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0001591835438267494</v>
+        <v>0.0001591835438267418</v>
       </c>
     </row>
     <row r="40">
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2.258744967039705e-05</v>
+        <v>2.258744967038595e-05</v>
       </c>
       <c r="D40" t="n">
-        <v>2.362033107267677e-05</v>
+        <v>2.36203310726899e-05</v>
       </c>
     </row>
     <row r="41">
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6.82048063872509e-06</v>
+        <v>6.820480638736192e-06</v>
       </c>
       <c r="D41" t="n">
-        <v>4.485582365181625e-05</v>
+        <v>4.485582365178197e-05</v>
       </c>
     </row>
     <row r="42">
@@ -5389,10 +5389,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2.762245849674549e-06</v>
+        <v>2.762245849663447e-06</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0001595544517067935</v>
+        <v>0.0001595544517068001</v>
       </c>
     </row>
     <row r="43">
@@ -5421,10 +5421,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-9.206848448506388e-06</v>
+        <v>-9.206848448517491e-06</v>
       </c>
       <c r="D44" t="n">
-        <v>7.775929036751156e-06</v>
+        <v>7.775929036744435e-06</v>
       </c>
     </row>
     <row r="45">
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-1.721897560962304e-05</v>
+        <v>-1.721897560961194e-05</v>
       </c>
       <c r="D45" t="n">
-        <v>9.490379946939309e-05</v>
+        <v>9.490379946940288e-05</v>
       </c>
     </row>
     <row r="46">
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-3.494969673081272e-05</v>
+        <v>-3.494969673079051e-05</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0001287288212643009</v>
+        <v>0.0001287288212643273</v>
       </c>
     </row>
     <row r="47">
@@ -5469,10 +5469,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-5.125645230295017e-05</v>
+        <v>-5.125645230293907e-05</v>
       </c>
       <c r="D47" t="n">
-        <v>1.941419715885385e-05</v>
+        <v>1.941419715886425e-05</v>
       </c>
     </row>
     <row r="48">
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-5.223207071624048e-05</v>
+        <v>-5.223207071622937e-05</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0005565570931598214</v>
+        <v>0.0005565570931598128</v>
       </c>
     </row>
     <row r="49">
@@ -5517,10 +5517,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-0.0001195851064772491</v>
+        <v>-0.0001195851064772269</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0001561249239193249</v>
+        <v>0.0001561249239193307</v>
       </c>
     </row>
     <row r="51">
@@ -5536,7 +5536,7 @@
         <v>-0.0003023502629998176</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0002050707450226975</v>
+        <v>0.0002050707450227234</v>
       </c>
     </row>
     <row r="52">
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.0003126019529183899</v>
+        <v>-0.0003126019529183788</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0002626275236228015</v>
+        <v>0.000262627523622785</v>
       </c>
     </row>
     <row r="53">
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.0003389814205102981</v>
+        <v>-0.000338981420510287</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0002626940205436082</v>
+        <v>0.0002626940205436014</v>
       </c>
     </row>
     <row r="54">
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.0006547469196777067</v>
+        <v>-0.0006547469196776956</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0003377717366934673</v>
+        <v>0.0003377717366934631</v>
       </c>
     </row>
   </sheetData>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-14 21:58:10 UTC</t>
+          <t>2026-06-15 07:20:55 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_apparent_color.xlsx
+++ b/NN/reports/feature_importance_white_apparent_color.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,25 +501,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4165063630280615</v>
+        <v>0.5920742209544035</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3306041230813141</v>
+        <v>0.4679226951658499</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4761045525333641</v>
+        <v>1.031908169033023</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.198349616808716</v>
+        <v>1.208046827087069</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -534,35 +534,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2808911641104241</v>
+        <v>0.08967119999287057</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2390766078490786</v>
+        <v>0.08670767180741892</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2791487904168629</v>
+        <v>0.02395540046258777</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1.072530669500765</v>
+        <v>0.6762138378539095</v>
       </c>
       <c r="J3" t="n">
         <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -571,35 +571,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0704731334153732</v>
+        <v>0.08167065478904427</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07063431481632378</v>
+        <v>0.2154339671576504</v>
       </c>
       <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01782556110928256</v>
+      </c>
+      <c r="H4" t="n">
         <v>4</v>
       </c>
-      <c r="G4" t="n">
-        <v>0.02360148039191767</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3</v>
-      </c>
       <c r="I4" t="n">
-        <v>0.6822701612908508</v>
+        <v>0.6215641572957189</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
@@ -608,35 +608,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.05523915390276699</v>
+        <v>0.09496593287494429</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1472118822135189</v>
+        <v>0.01642505265108248</v>
       </c>
       <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.02365507463254061</v>
+      </c>
+      <c r="H5" t="n">
         <v>3</v>
       </c>
-      <c r="G5" t="n">
-        <v>0.008552106770008071</v>
-      </c>
-      <c r="H5" t="n">
-        <v>6</v>
-      </c>
       <c r="I5" t="n">
-        <v>0.6178166855264426</v>
+        <v>0.4605703166301494</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
@@ -649,31 +649,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.007332764951427079</v>
+        <v>0.01421334901113243</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05099292444392457</v>
+        <v>0.06926788527600564</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0014827288783222</v>
+        <v>0.00332199820672759</v>
       </c>
       <c r="H6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>1.236279030419674</v>
+        <v>1.445085822558013</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>6.25</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="7">
@@ -682,35 +682,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01437921541051098</v>
+        <v>0.008659263575318672</v>
       </c>
       <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.01190476707562985</v>
+      </c>
+      <c r="F7" t="n">
+        <v>11</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.004252076778319102</v>
+      </c>
+      <c r="H7" t="n">
         <v>6</v>
       </c>
-      <c r="E7" t="n">
-        <v>0.0396324080579542</v>
-      </c>
-      <c r="F7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.01139062738611738</v>
-      </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
+        <v>0.66269244681932</v>
+      </c>
+      <c r="J7" t="n">
         <v>4</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.28650978335402</v>
-      </c>
-      <c r="J7" t="n">
-        <v>10</v>
-      </c>
       <c r="K7" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -719,35 +719,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.05936462511312079</v>
+        <v>0.008619581204237481</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008049120596560178</v>
+        <v>0.01496345785060761</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01033062653383406</v>
+        <v>0.003952990711925663</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4739090618199784</v>
+        <v>0.1873592230830228</v>
       </c>
       <c r="J8" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="9">
@@ -756,35 +756,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.005865493220224619</v>
+        <v>0.005805417654146275</v>
       </c>
       <c r="D9" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01353967665917896</v>
+      </c>
+      <c r="F9" t="n">
         <v>9</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.01171508403166955</v>
-      </c>
-      <c r="F9" t="n">
-        <v>7</v>
-      </c>
       <c r="G9" t="n">
-        <v>0.002352385369849608</v>
+        <v>0.0009534297387564616</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I9" t="n">
-        <v>0.229810539278942</v>
+        <v>0.2422781661061482</v>
       </c>
       <c r="J9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>9.25</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="10">
@@ -797,31 +797,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.003680338482789539</v>
+        <v>0.004171390416423985</v>
       </c>
       <c r="D10" t="n">
         <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003549982278399404</v>
+        <v>0.00481808450208358</v>
       </c>
       <c r="F10" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002523136450429486</v>
+        <v>0.003468478794544239</v>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3677464095429919</v>
+        <v>0.361662266454982</v>
       </c>
       <c r="J10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K10" t="n">
-        <v>11.5</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="11">
@@ -830,35 +830,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.005951551135848279</v>
+        <v>0.00380271714631139</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01139603876227962</v>
+        <v>0.0128559873647453</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002136458895167481</v>
+        <v>0.002653734574104982</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1407178423155786</v>
+        <v>0.5026811508925402</v>
       </c>
       <c r="J11" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>12.25</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="12">
@@ -867,35 +867,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.003182975224781823</v>
+        <v>0.007872805879607678</v>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>0.004671017670986557</v>
+        <v>0.0159312519072255</v>
       </c>
       <c r="F12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001005090769901151</v>
+        <v>0.002740628099216091</v>
       </c>
       <c r="H12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6640910913673306</v>
+        <v>0.1371412425332703</v>
       </c>
       <c r="J12" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="K12" t="n">
-        <v>12.25</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="13">
@@ -904,32 +904,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.002450678522644812</v>
+        <v>0.004913497195705433</v>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>0.004791652244209006</v>
+        <v>0.002582528428023573</v>
       </c>
       <c r="F13" t="n">
+        <v>17</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.001082700563551575</v>
+      </c>
+      <c r="H13" t="n">
         <v>13</v>
       </c>
-      <c r="G13" t="n">
-        <v>0.0009216647418518575</v>
-      </c>
-      <c r="H13" t="n">
-        <v>15</v>
-      </c>
       <c r="I13" t="n">
-        <v>0.4961148960923709</v>
+        <v>0.1959490560392148</v>
       </c>
       <c r="J13" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K13" t="n">
         <v>13.25</v>
@@ -941,35 +941,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.005568558762841301</v>
+        <v>0.01047054099489799</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01166209065597926</v>
+        <v>0.002172313056935274</v>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001733866369081005</v>
+        <v>0.005746459978263685</v>
       </c>
       <c r="H14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1198625489822751</v>
+        <v>0.1205109958479595</v>
       </c>
       <c r="J14" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K14" t="n">
-        <v>14.5</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="15">
@@ -978,35 +978,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.003786938594379947</v>
+        <v>0.007350305572308778</v>
       </c>
       <c r="D15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002111454812359339</v>
+        <v>0.002353100713898803</v>
       </c>
       <c r="F15" t="n">
         <v>19</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001664456317987884</v>
+        <v>0.0003445281492521657</v>
       </c>
       <c r="H15" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1416256039247572</v>
+        <v>0.1944292539484866</v>
       </c>
       <c r="J15" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>16.25</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="16">
@@ -1015,35 +1015,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.001909589683063649</v>
+        <v>0.003977406121844788</v>
       </c>
       <c r="D16" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
-        <v>0.007637278622181098</v>
+        <v>0.002914915260674493</v>
       </c>
       <c r="F16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>0.000387969342948602</v>
+        <v>0.0007612504259516872</v>
       </c>
       <c r="H16" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2387552123432464</v>
+        <v>0.1037297377208199</v>
       </c>
       <c r="J16" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K16" t="n">
-        <v>18.5</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="17">
@@ -1052,35 +1052,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.00542538573678234</v>
+        <v>0.002228427751615875</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001843656198317041</v>
+        <v>0.008556315930821014</v>
       </c>
       <c r="F17" t="n">
+        <v>12</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0004787536452435015</v>
+      </c>
+      <c r="H17" t="n">
         <v>21</v>
       </c>
-      <c r="G17" t="n">
-        <v>0.00129758752940613</v>
-      </c>
-      <c r="H17" t="n">
-        <v>13</v>
-      </c>
       <c r="I17" t="n">
-        <v>0.1150710484016844</v>
+        <v>0.1829621589958523</v>
       </c>
       <c r="J17" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>19</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="18">
@@ -1089,35 +1089,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.002072288043532046</v>
+        <v>0.003035328153665141</v>
       </c>
       <c r="D18" t="n">
+        <v>18</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.002527577588815142</v>
+      </c>
+      <c r="F18" t="n">
+        <v>18</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.0003386623738867222</v>
+      </c>
+      <c r="H18" t="n">
+        <v>29</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.1296686657626984</v>
+      </c>
+      <c r="J18" t="n">
         <v>24</v>
       </c>
-      <c r="E18" t="n">
-        <v>0.004507777600072711</v>
-      </c>
-      <c r="F18" t="n">
-        <v>15</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.000125652302639645</v>
-      </c>
-      <c r="H18" t="n">
-        <v>32</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.2398858944846856</v>
-      </c>
-      <c r="J18" t="n">
-        <v>11</v>
-      </c>
       <c r="K18" t="n">
-        <v>20.5</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="19">
@@ -1126,35 +1126,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.00225115840821352</v>
+        <v>0.00281412303182168</v>
       </c>
       <c r="D19" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E19" t="n">
-        <v>0.001357061971355008</v>
+        <v>0.00118466042658106</v>
       </c>
       <c r="F19" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0004163616826270977</v>
+        <v>0.0004494361343189812</v>
       </c>
       <c r="H19" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1598125154675447</v>
+        <v>0.1609745217265175</v>
       </c>
       <c r="J19" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K19" t="n">
-        <v>22.25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -1163,35 +1163,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.002423001199226675</v>
+        <v>0.002933469357508301</v>
       </c>
       <c r="D20" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E20" t="n">
-        <v>0.002412386175043696</v>
+        <v>0.0008546693811585762</v>
       </c>
       <c r="F20" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0008939545123207493</v>
+        <v>0.001920355074727909</v>
       </c>
       <c r="H20" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1038346518305531</v>
+        <v>0.1340082756701844</v>
       </c>
       <c r="J20" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="K20" t="n">
-        <v>22.5</v>
+        <v>23.25</v>
       </c>
     </row>
     <row r="21">
@@ -1200,35 +1200,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.001615536306275759</v>
+        <v>0.003017239130651168</v>
       </c>
       <c r="D21" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E21" t="n">
-        <v>0.002557803826870271</v>
+        <v>0.002613929821600999</v>
       </c>
       <c r="F21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0003160224410929891</v>
+        <v>-8.627531463611948e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2062187982627752</v>
+        <v>0.1300982458321855</v>
       </c>
       <c r="J21" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K21" t="n">
-        <v>22.5</v>
+        <v>24.25</v>
       </c>
     </row>
     <row r="22">
@@ -1237,35 +1237,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.003116999146508176</v>
+        <v>0.001237943634158155</v>
       </c>
       <c r="D22" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="E22" t="n">
-        <v>0.001237897278353882</v>
+        <v>0.01781167675747098</v>
       </c>
       <c r="F22" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0001045709538454731</v>
+        <v>0.0006414853561366396</v>
       </c>
       <c r="H22" t="n">
+        <v>18</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.08913391913071145</v>
+      </c>
+      <c r="J22" t="n">
         <v>33</v>
       </c>
-      <c r="I22" t="n">
-        <v>0.1601129381638917</v>
-      </c>
-      <c r="J22" t="n">
-        <v>19</v>
-      </c>
       <c r="K22" t="n">
-        <v>24.5</v>
+        <v>24.25</v>
       </c>
     </row>
     <row r="23">
@@ -1274,35 +1274,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.002266012182974288</v>
+        <v>0.001506392619819774</v>
       </c>
       <c r="D23" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="E23" t="n">
-        <v>0.001231804086661222</v>
+        <v>0.001231253241034245</v>
       </c>
       <c r="F23" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G23" t="n">
-        <v>0.00047072720512219</v>
+        <v>0.0004079862201908813</v>
       </c>
       <c r="H23" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1148730857526199</v>
+        <v>0.1979102120027658</v>
       </c>
       <c r="J23" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="K23" t="n">
-        <v>25.25</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="24">
@@ -1315,31 +1315,31 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.00220460670377708</v>
+        <v>0.002950072652216257</v>
       </c>
       <c r="D24" t="n">
+        <v>20</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.002774350947291762</v>
+      </c>
+      <c r="F24" t="n">
+        <v>15</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.0001643881675597592</v>
+      </c>
+      <c r="H24" t="n">
+        <v>42</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.1327844524658035</v>
+      </c>
+      <c r="J24" t="n">
         <v>22</v>
       </c>
-      <c r="E24" t="n">
-        <v>0.0013480432808974</v>
-      </c>
-      <c r="F24" t="n">
-        <v>28</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.0002265491737181713</v>
-      </c>
-      <c r="H24" t="n">
-        <v>30</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.1374923718309686</v>
-      </c>
-      <c r="J24" t="n">
-        <v>25</v>
-      </c>
       <c r="K24" t="n">
-        <v>26.25</v>
+        <v>24.75</v>
       </c>
     </row>
     <row r="25">
@@ -1348,35 +1348,35 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.004053578774404341</v>
+        <v>0.003639393511303549</v>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E25" t="n">
-        <v>0.001829738778094041</v>
+        <v>0.001199729026705398</v>
       </c>
       <c r="F25" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.0006547469196776956</v>
+        <v>0.0001435333525940385</v>
       </c>
       <c r="H25" t="n">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1925807873599821</v>
+        <v>0.1247615231682322</v>
       </c>
       <c r="J25" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K25" t="n">
-        <v>26.25</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
@@ -1385,35 +1385,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.001523763742701117</v>
+        <v>0.002907683011589532</v>
       </c>
       <c r="D26" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E26" t="n">
-        <v>0.001058699724778284</v>
+        <v>0.002102191164414161</v>
       </c>
       <c r="F26" t="n">
+        <v>21</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-5.205685512910119e-06</v>
+      </c>
+      <c r="H26" t="n">
         <v>37</v>
       </c>
-      <c r="G26" t="n">
-        <v>0.0004086844772112186</v>
-      </c>
-      <c r="H26" t="n">
-        <v>22</v>
-      </c>
       <c r="I26" t="n">
-        <v>0.2162787103716499</v>
+        <v>0.1333401570501227</v>
       </c>
       <c r="J26" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K26" t="n">
-        <v>26.5</v>
+        <v>25.25</v>
       </c>
     </row>
     <row r="27">
@@ -1422,35 +1422,35 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.001952816557958622</v>
+        <v>0.002206623688330278</v>
       </c>
       <c r="D27" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E27" t="n">
-        <v>0.001721754149235873</v>
+        <v>0.001839449130005477</v>
       </c>
       <c r="F27" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0002886776865377749</v>
+        <v>6.518018794301472e-05</v>
       </c>
       <c r="H27" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1215714553125802</v>
+        <v>0.1429028751153396</v>
       </c>
       <c r="J27" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="K27" t="n">
-        <v>26.75</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="28">
@@ -1459,35 +1459,35 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.001925401250557361</v>
+        <v>0.002536620423087952</v>
       </c>
       <c r="D28" t="n">
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0009511806763082975</v>
+        <v>0.001265914054842857</v>
       </c>
       <c r="F28" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0006425803427979271</v>
+        <v>0.0008744190762375537</v>
       </c>
       <c r="H28" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1314372965756354</v>
+        <v>0.06281291121510701</v>
       </c>
       <c r="J28" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="K28" t="n">
-        <v>28</v>
+        <v>25.75</v>
       </c>
     </row>
     <row r="29">
@@ -1496,35 +1496,35 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.00168310873626361</v>
+        <v>0.002613759898075903</v>
       </c>
       <c r="D29" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E29" t="n">
-        <v>0.001207563170348514</v>
+        <v>0.001211296857974932</v>
       </c>
       <c r="F29" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0001433223145790419</v>
+        <v>1.044119178074121e-05</v>
       </c>
       <c r="H29" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1533962047699582</v>
+        <v>0.1570288853233155</v>
       </c>
       <c r="J29" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K29" t="n">
-        <v>28.25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30">
@@ -1533,35 +1533,35 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.001422216227604319</v>
+        <v>0.001898504610182973</v>
       </c>
       <c r="D30" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E30" t="n">
-        <v>0.008973586438909669</v>
+        <v>0.001163182844239249</v>
       </c>
       <c r="F30" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0003281996298877377</v>
+        <v>0.000501418140758847</v>
       </c>
       <c r="H30" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I30" t="n">
-        <v>0.08537318741232736</v>
+        <v>0.1127553931185408</v>
       </c>
       <c r="J30" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="K30" t="n">
-        <v>28.25</v>
+        <v>27.25</v>
       </c>
     </row>
     <row r="31">
@@ -1570,35 +1570,35 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.001876100480860019</v>
+        <v>0.001488815140054277</v>
       </c>
       <c r="D31" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E31" t="n">
-        <v>0.001807229545069563</v>
+        <v>0.001112629681782611</v>
       </c>
       <c r="F31" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.0001195851064772269</v>
+        <v>0.0003700175390899507</v>
       </c>
       <c r="H31" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1975684889068154</v>
+        <v>0.1956021692664685</v>
       </c>
       <c r="J31" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K31" t="n">
-        <v>29.75</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32">
@@ -1607,35 +1607,35 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.001546442873848397</v>
+        <v>0.002703183944969406</v>
       </c>
       <c r="D32" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E32" t="n">
-        <v>0.001813175004032185</v>
+        <v>0.0009908512039546642</v>
       </c>
       <c r="F32" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="G32" t="n">
-        <v>2.762245849663447e-06</v>
+        <v>0.0008421070769518146</v>
       </c>
       <c r="H32" t="n">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1399203475237156</v>
+        <v>0.06526898211343335</v>
       </c>
       <c r="J32" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K32" t="n">
-        <v>30</v>
+        <v>28.25</v>
       </c>
     </row>
     <row r="33">
@@ -1644,35 +1644,35 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.001467879364589689</v>
+        <v>0.002188873242683482</v>
       </c>
       <c r="D33" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0009266225191322128</v>
+        <v>0.001370530624470443</v>
       </c>
       <c r="F33" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0002731873965256759</v>
+        <v>0.0004009693875428822</v>
       </c>
       <c r="H33" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2045485718760616</v>
+        <v>0.05812931149084299</v>
       </c>
       <c r="J33" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="K33" t="n">
-        <v>31</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="34">
@@ -1681,35 +1681,35 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.001405256658231053</v>
+        <v>0.002208798431234469</v>
       </c>
       <c r="D34" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E34" t="n">
-        <v>0.001101450565593942</v>
+        <v>0.001198887999553266</v>
       </c>
       <c r="F34" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0004939475910281765</v>
+        <v>0.000212479767682694</v>
       </c>
       <c r="H34" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="I34" t="n">
-        <v>0.106171265677435</v>
+        <v>0.08590775237564729</v>
       </c>
       <c r="J34" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K34" t="n">
-        <v>31.25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35">
@@ -1718,35 +1718,35 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.001880153310329902</v>
+        <v>0.001814753712862562</v>
       </c>
       <c r="D35" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E35" t="n">
-        <v>0.001934360536190422</v>
+        <v>0.001100329891203608</v>
       </c>
       <c r="F35" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.0003126019529183788</v>
+        <v>0.000462372387614507</v>
       </c>
       <c r="H35" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1294575803156772</v>
+        <v>0.09229532984918176</v>
       </c>
       <c r="J35" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K35" t="n">
-        <v>31.5</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="36">
@@ -1755,35 +1755,35 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.002181944414213</v>
+        <v>0.001795922268633566</v>
       </c>
       <c r="D36" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E36" t="n">
-        <v>0.001475508310899919</v>
+        <v>0.001140085161598094</v>
       </c>
       <c r="F36" t="n">
+        <v>32</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.0003992164384769903</v>
+      </c>
+      <c r="H36" t="n">
         <v>26</v>
       </c>
-      <c r="G36" t="n">
-        <v>-0.000338981420510287</v>
-      </c>
-      <c r="H36" t="n">
-        <v>52</v>
-      </c>
       <c r="I36" t="n">
-        <v>0.1282316679533264</v>
+        <v>0.1034487711885506</v>
       </c>
       <c r="J36" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K36" t="n">
-        <v>32.25</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37">
@@ -1792,35 +1792,35 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.001324181788718726</v>
+        <v>0.002114945787401633</v>
       </c>
       <c r="D37" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E37" t="n">
-        <v>0.001075282134623642</v>
+        <v>0.001057381532781222</v>
       </c>
       <c r="F37" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0004189207118883931</v>
+        <v>0.0001307880198220035</v>
       </c>
       <c r="H37" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I37" t="n">
-        <v>0.11158529414972</v>
+        <v>0.105556233734625</v>
       </c>
       <c r="J37" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="K37" t="n">
-        <v>32.5</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="38">
@@ -1833,31 +1833,31 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.00358843655999448</v>
+        <v>0.004511930585227162</v>
       </c>
       <c r="D38" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E38" t="n">
-        <v>0.00109379240620066</v>
+        <v>0.0009661410966560955</v>
       </c>
       <c r="F38" t="n">
+        <v>39</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-0.0002423586497693808</v>
+      </c>
+      <c r="H38" t="n">
+        <v>43</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.06628200146933505</v>
+      </c>
+      <c r="J38" t="n">
         <v>35</v>
       </c>
-      <c r="G38" t="n">
-        <v>-5.223207071622937e-05</v>
-      </c>
-      <c r="H38" t="n">
-        <v>47</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.07325591331459158</v>
-      </c>
-      <c r="J38" t="n">
-        <v>42</v>
-      </c>
       <c r="K38" t="n">
-        <v>34.75</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="39">
@@ -1866,35 +1866,35 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.0013199485006502</v>
+        <v>0.001882208831225212</v>
       </c>
       <c r="D39" t="n">
+        <v>33</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.0006994352667825254</v>
+      </c>
+      <c r="F39" t="n">
         <v>41</v>
       </c>
-      <c r="E39" t="n">
-        <v>0.001154547130382378</v>
-      </c>
-      <c r="F39" t="n">
-        <v>32</v>
-      </c>
       <c r="G39" t="n">
-        <v>0.0003298602118368188</v>
+        <v>0.0004897220609223152</v>
       </c>
       <c r="H39" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0524700468327115</v>
+        <v>0.05452235026964969</v>
       </c>
       <c r="J39" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="K39" t="n">
-        <v>36.25</v>
+        <v>33.75</v>
       </c>
     </row>
     <row r="40">
@@ -1903,35 +1903,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.001278372169820007</v>
+        <v>0.001812279178860347</v>
       </c>
       <c r="D40" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E40" t="n">
-        <v>0.001002967469465903</v>
+        <v>0.001027086686044412</v>
       </c>
       <c r="F40" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0003681251614669811</v>
+        <v>-0.0007954739357298624</v>
       </c>
       <c r="H40" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="I40" t="n">
-        <v>0.08786926996012312</v>
+        <v>0.09590600730350829</v>
       </c>
       <c r="J40" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="K40" t="n">
-        <v>36.5</v>
+        <v>36.75</v>
       </c>
     </row>
     <row r="41">
@@ -1940,35 +1940,35 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.001489522975204905</v>
+        <v>0.0016069423763632</v>
       </c>
       <c r="D41" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E41" t="n">
-        <v>0.0009939507152283882</v>
+        <v>0.001192275866598129</v>
       </c>
       <c r="F41" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="G41" t="n">
-        <v>4.357300668266229e-05</v>
+        <v>-0.0002699360974856791</v>
       </c>
       <c r="H41" t="n">
+        <v>44</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.06330130239914888</v>
+      </c>
+      <c r="J41" t="n">
         <v>37</v>
       </c>
-      <c r="I41" t="n">
-        <v>0.07201304738427394</v>
-      </c>
-      <c r="J41" t="n">
-        <v>43</v>
-      </c>
       <c r="K41" t="n">
-        <v>39</v>
+        <v>36.75</v>
       </c>
     </row>
     <row r="42">
@@ -1977,35 +1977,35 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.001170717320282009</v>
+        <v>0.001590591978543202</v>
       </c>
       <c r="D42" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E42" t="n">
-        <v>0.001014908604712684</v>
+        <v>0.0009889208037062104</v>
       </c>
       <c r="F42" t="n">
+        <v>38</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-0.0001037090056165812</v>
+      </c>
+      <c r="H42" t="n">
         <v>40</v>
       </c>
-      <c r="G42" t="n">
-        <v>0.0001004520136867804</v>
-      </c>
-      <c r="H42" t="n">
-        <v>34</v>
-      </c>
       <c r="I42" t="n">
-        <v>0.09691135010235818</v>
+        <v>0.05831871248340992</v>
       </c>
       <c r="J42" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K42" t="n">
-        <v>39</v>
+        <v>38.75</v>
       </c>
     </row>
     <row r="43">
@@ -2014,35 +2014,35 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.001259483624557032</v>
+        <v>0.0001823049081357287</v>
       </c>
       <c r="D43" t="n">
         <v>43</v>
       </c>
       <c r="E43" t="n">
-        <v>0.001095079940739656</v>
+        <v>0.0002214324671219349</v>
       </c>
       <c r="F43" t="n">
+        <v>43</v>
+      </c>
+      <c r="G43" t="n">
+        <v>6.302967083727795e-05</v>
+      </c>
+      <c r="H43" t="n">
         <v>34</v>
       </c>
-      <c r="G43" t="n">
-        <v>4.210899185663752e-05</v>
-      </c>
-      <c r="H43" t="n">
-        <v>38</v>
-      </c>
       <c r="I43" t="n">
-        <v>0.06522008278876879</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K43" t="n">
-        <v>39.75</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="44">
@@ -2051,35 +2051,35 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.001377660164585235</v>
+        <v>0.0001955000532993873</v>
       </c>
       <c r="D44" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E44" t="n">
-        <v>0.0008008771383007751</v>
+        <v>0.0005157339857014848</v>
       </c>
       <c r="F44" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G44" t="n">
-        <v>-9.861126962218414e-07</v>
+        <v>-5.264588066035136e-05</v>
       </c>
       <c r="H44" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1134854836112336</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="K44" t="n">
-        <v>40.25</v>
+        <v>41.25</v>
       </c>
     </row>
     <row r="45">
@@ -2088,35 +2088,35 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.001459353406819576</v>
+        <v>1.675992323848266e-05</v>
       </c>
       <c r="D45" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E45" t="n">
-        <v>0.001045676264699847</v>
+        <v>0.0001036190779050449</v>
       </c>
       <c r="F45" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="G45" t="n">
-        <v>-7.407733931898974e-05</v>
+        <v>2.0592047542356e-05</v>
       </c>
       <c r="H45" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="I45" t="n">
-        <v>0.05844033263516879</v>
+        <v>0.0235346423412075</v>
       </c>
       <c r="J45" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="K45" t="n">
-        <v>42</v>
+        <v>41.75</v>
       </c>
     </row>
     <row r="46">
@@ -2125,331 +2125,35 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.001159971095830336</v>
+        <v>0.00012232478004381</v>
       </c>
       <c r="D46" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E46" t="n">
-        <v>0.0009263130496737242</v>
+        <v>0.0001851066041741383</v>
       </c>
       <c r="F46" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G46" t="n">
-        <v>-3.494969673079051e-05</v>
+        <v>-0.0001089199559701659</v>
       </c>
       <c r="H46" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1062600742559612</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K46" t="n">
-        <v>42.5</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_1</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.0005306475056556192</v>
-      </c>
-      <c r="D47" t="n">
-        <v>49</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0.000767815827354959</v>
-      </c>
-      <c r="F47" t="n">
-        <v>49</v>
-      </c>
-      <c r="G47" t="n">
-        <v>4.996488354246376e-05</v>
-      </c>
-      <c r="H47" t="n">
-        <v>35</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0.07723852475526449</v>
-      </c>
-      <c r="J47" t="n">
-        <v>41</v>
-      </c>
-      <c r="K47" t="n">
-        <v>43.5</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_2</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0.0006485909228951996</v>
-      </c>
-      <c r="D48" t="n">
-        <v>48</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0.0008914295508628588</v>
-      </c>
-      <c r="F48" t="n">
-        <v>46</v>
-      </c>
-      <c r="G48" t="n">
-        <v>4.448725532436581e-05</v>
-      </c>
-      <c r="H48" t="n">
-        <v>36</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0.005638754778659383</v>
-      </c>
-      <c r="J48" t="n">
-        <v>50</v>
-      </c>
-      <c r="K48" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>wastewater_r2_pol</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.001105095374194287</v>
-      </c>
-      <c r="D49" t="n">
-        <v>47</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0.00104881979376202</v>
-      </c>
-      <c r="F49" t="n">
-        <v>38</v>
-      </c>
-      <c r="G49" t="n">
-        <v>-0.0003023502629998176</v>
-      </c>
-      <c r="H49" t="n">
-        <v>50</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.05784603239742125</v>
-      </c>
-      <c r="J49" t="n">
-        <v>46</v>
-      </c>
-      <c r="K49" t="n">
-        <v>45.25</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>boiling_r3_pol</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0.00111841178422654</v>
-      </c>
-      <c r="D50" t="n">
-        <v>46</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0.0007946482086225369</v>
-      </c>
-      <c r="F50" t="n">
-        <v>48</v>
-      </c>
-      <c r="G50" t="n">
-        <v>-1.721897560961194e-05</v>
-      </c>
-      <c r="H50" t="n">
-        <v>44</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0.04452011846688331</v>
-      </c>
-      <c r="J50" t="n">
-        <v>48</v>
-      </c>
-      <c r="K50" t="n">
-        <v>46.5</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.0001249375002640287</v>
-      </c>
-      <c r="D51" t="n">
-        <v>50</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0.0002812180453595566</v>
-      </c>
-      <c r="F51" t="n">
-        <v>52</v>
-      </c>
-      <c r="G51" t="n">
-        <v>2.258744967038595e-05</v>
-      </c>
-      <c r="H51" t="n">
-        <v>39</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.0007857841193852355</v>
-      </c>
-      <c r="J51" t="n">
-        <v>51</v>
-      </c>
-      <c r="K51" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>boiler_hardness</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>6.737916972965479e-05</v>
-      </c>
-      <c r="D52" t="n">
-        <v>52</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0.0005170322901136405</v>
-      </c>
-      <c r="F52" t="n">
-        <v>50</v>
-      </c>
-      <c r="G52" t="n">
-        <v>6.820480638736192e-06</v>
-      </c>
-      <c r="H52" t="n">
-        <v>40</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
-        <v>52</v>
-      </c>
-      <c r="K52" t="n">
-        <v>48.5</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>carbonated_alkalinity</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>2.532199209291146e-05</v>
-      </c>
-      <c r="D53" t="n">
-        <v>53</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0.0001221167458791846</v>
-      </c>
-      <c r="F53" t="n">
-        <v>53</v>
-      </c>
-      <c r="G53" t="n">
-        <v>-9.206848448517491e-06</v>
-      </c>
-      <c r="H53" t="n">
         <v>43</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0.02298624135869165</v>
-      </c>
-      <c r="J53" t="n">
-        <v>49</v>
-      </c>
-      <c r="K53" t="n">
-        <v>49.5</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>shift_name</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>7.577446736926195e-05</v>
-      </c>
-      <c r="D54" t="n">
-        <v>51</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0.0003402447111151486</v>
-      </c>
-      <c r="F54" t="n">
-        <v>51</v>
-      </c>
-      <c r="G54" t="n">
-        <v>-5.125645230293907e-05</v>
-      </c>
-      <c r="H54" t="n">
-        <v>46</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>52</v>
-      </c>
-      <c r="K54" t="n">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2533,25 +2237,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4165063630280615</v>
+        <v>0.5920742209544035</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3306041230813141</v>
+        <v>0.4679226951658499</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4761045525333641</v>
+        <v>1.031908169033023</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.198349616808716</v>
+        <v>1.208046827087069</v>
       </c>
       <c r="J2" t="n">
         <v>2</v>
@@ -2566,35 +2270,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2808911641104241</v>
+        <v>0.08967119999287057</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2390766078490786</v>
+        <v>0.08670767180741892</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2791487904168629</v>
+        <v>0.02395540046258777</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1.072530669500765</v>
+        <v>0.6762138378539095</v>
       </c>
       <c r="J3" t="n">
         <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -2603,35 +2307,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0704731334153732</v>
+        <v>0.08167065478904427</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07063431481632378</v>
+        <v>0.2154339671576504</v>
       </c>
       <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01782556110928256</v>
+      </c>
+      <c r="H4" t="n">
         <v>4</v>
       </c>
-      <c r="G4" t="n">
-        <v>0.02360148039191767</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3</v>
-      </c>
       <c r="I4" t="n">
-        <v>0.6822701612908508</v>
+        <v>0.6215641572957189</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="5">
@@ -2640,35 +2344,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.05523915390276699</v>
+        <v>0.09496593287494429</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1472118822135189</v>
+        <v>0.01642505265108248</v>
       </c>
       <c r="F5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.02365507463254061</v>
+      </c>
+      <c r="H5" t="n">
         <v>3</v>
       </c>
-      <c r="G5" t="n">
-        <v>0.008552106770008071</v>
-      </c>
-      <c r="H5" t="n">
-        <v>6</v>
-      </c>
       <c r="I5" t="n">
-        <v>0.6178166855264426</v>
+        <v>0.4605703166301494</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
@@ -2681,31 +2385,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.007332764951427079</v>
+        <v>0.01421334901113243</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05099292444392457</v>
+        <v>0.06926788527600564</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0014827288783222</v>
+        <v>0.00332199820672759</v>
       </c>
       <c r="H6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>1.236279030419674</v>
+        <v>1.445085822558013</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>6.25</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="7">
@@ -2714,35 +2418,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01437921541051098</v>
+        <v>0.008659263575318672</v>
       </c>
       <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.01190476707562985</v>
+      </c>
+      <c r="F7" t="n">
+        <v>11</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.004252076778319102</v>
+      </c>
+      <c r="H7" t="n">
         <v>6</v>
       </c>
-      <c r="E7" t="n">
-        <v>0.0396324080579542</v>
-      </c>
-      <c r="F7" t="n">
-        <v>6</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.01139062738611738</v>
-      </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
+        <v>0.66269244681932</v>
+      </c>
+      <c r="J7" t="n">
         <v>4</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.28650978335402</v>
-      </c>
-      <c r="J7" t="n">
-        <v>10</v>
-      </c>
       <c r="K7" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -2751,35 +2455,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.05936462511312079</v>
+        <v>0.008619581204237481</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008049120596560178</v>
+        <v>0.01496345785060761</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01033062653383406</v>
+        <v>0.003952990711925663</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4739090618199784</v>
+        <v>0.1873592230830228</v>
       </c>
       <c r="J8" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="9">
@@ -2788,35 +2492,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.005865493220224619</v>
+        <v>0.005805417654146275</v>
       </c>
       <c r="D9" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01353967665917896</v>
+      </c>
+      <c r="F9" t="n">
         <v>9</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.01171508403166955</v>
-      </c>
-      <c r="F9" t="n">
-        <v>7</v>
-      </c>
       <c r="G9" t="n">
-        <v>0.002352385369849608</v>
+        <v>0.0009534297387564616</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I9" t="n">
-        <v>0.229810539278942</v>
+        <v>0.2422781661061482</v>
       </c>
       <c r="J9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>9.25</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="10">
@@ -2829,31 +2533,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.003680338482789539</v>
+        <v>0.004171390416423985</v>
       </c>
       <c r="D10" t="n">
         <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003549982278399404</v>
+        <v>0.00481808450208358</v>
       </c>
       <c r="F10" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002523136450429486</v>
+        <v>0.003468478794544239</v>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3677464095429919</v>
+        <v>0.361662266454982</v>
       </c>
       <c r="J10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K10" t="n">
-        <v>11.5</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="11">
@@ -2862,35 +2566,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.005951551135848279</v>
+        <v>0.00380271714631139</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01139603876227962</v>
+        <v>0.0128559873647453</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002136458895167481</v>
+        <v>0.002653734574104982</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1407178423155786</v>
+        <v>0.5026811508925402</v>
       </c>
       <c r="J11" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>12.25</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="12">
@@ -2899,35 +2603,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.003182975224781823</v>
+        <v>0.007872805879607678</v>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>0.004671017670986557</v>
+        <v>0.0159312519072255</v>
       </c>
       <c r="F12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001005090769901151</v>
+        <v>0.002740628099216091</v>
       </c>
       <c r="H12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6640910913673306</v>
+        <v>0.1371412425332703</v>
       </c>
       <c r="J12" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="K12" t="n">
-        <v>12.25</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="13">
@@ -2936,32 +2640,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.002450678522644812</v>
+        <v>0.004913497195705433</v>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>0.004791652244209006</v>
+        <v>0.002582528428023573</v>
       </c>
       <c r="F13" t="n">
+        <v>17</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.001082700563551575</v>
+      </c>
+      <c r="H13" t="n">
         <v>13</v>
       </c>
-      <c r="G13" t="n">
-        <v>0.0009216647418518575</v>
-      </c>
-      <c r="H13" t="n">
-        <v>15</v>
-      </c>
       <c r="I13" t="n">
-        <v>0.4961148960923709</v>
+        <v>0.1959490560392148</v>
       </c>
       <c r="J13" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K13" t="n">
         <v>13.25</v>
@@ -2973,35 +2677,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.005568558762841301</v>
+        <v>0.01047054099489799</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01166209065597926</v>
+        <v>0.002172313056935274</v>
       </c>
       <c r="F14" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001733866369081005</v>
+        <v>0.005746459978263685</v>
       </c>
       <c r="H14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1198625489822751</v>
+        <v>0.1205109958479595</v>
       </c>
       <c r="J14" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K14" t="n">
-        <v>14.5</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="15">
@@ -3010,35 +2714,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.003786938594379947</v>
+        <v>0.007350305572308778</v>
       </c>
       <c r="D15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002111454812359339</v>
+        <v>0.002353100713898803</v>
       </c>
       <c r="F15" t="n">
         <v>19</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001664456317987884</v>
+        <v>0.0003445281492521657</v>
       </c>
       <c r="H15" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1416256039247572</v>
+        <v>0.1944292539484866</v>
       </c>
       <c r="J15" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>16.25</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="16">
@@ -3047,35 +2751,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.001909589683063649</v>
+        <v>0.003977406121844788</v>
       </c>
       <c r="D16" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E16" t="n">
-        <v>0.007637278622181098</v>
+        <v>0.002914915260674493</v>
       </c>
       <c r="F16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>0.000387969342948602</v>
+        <v>0.0007612504259516872</v>
       </c>
       <c r="H16" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2387552123432464</v>
+        <v>0.1037297377208199</v>
       </c>
       <c r="J16" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K16" t="n">
-        <v>18.5</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="17">
@@ -3084,35 +2788,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.00542538573678234</v>
+        <v>0.002228427751615875</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E17" t="n">
-        <v>0.001843656198317041</v>
+        <v>0.008556315930821014</v>
       </c>
       <c r="F17" t="n">
+        <v>12</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0004787536452435015</v>
+      </c>
+      <c r="H17" t="n">
         <v>21</v>
       </c>
-      <c r="G17" t="n">
-        <v>0.00129758752940613</v>
-      </c>
-      <c r="H17" t="n">
-        <v>13</v>
-      </c>
       <c r="I17" t="n">
-        <v>0.1150710484016844</v>
+        <v>0.1829621589958523</v>
       </c>
       <c r="J17" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="K17" t="n">
-        <v>19</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="18">
@@ -3121,35 +2825,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.002072288043532046</v>
+        <v>0.003035328153665141</v>
       </c>
       <c r="D18" t="n">
+        <v>18</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.002527577588815142</v>
+      </c>
+      <c r="F18" t="n">
+        <v>18</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.0003386623738867222</v>
+      </c>
+      <c r="H18" t="n">
+        <v>29</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.1296686657626984</v>
+      </c>
+      <c r="J18" t="n">
         <v>24</v>
       </c>
-      <c r="E18" t="n">
-        <v>0.004507777600072711</v>
-      </c>
-      <c r="F18" t="n">
-        <v>15</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.000125652302639645</v>
-      </c>
-      <c r="H18" t="n">
-        <v>32</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.2398858944846856</v>
-      </c>
-      <c r="J18" t="n">
-        <v>11</v>
-      </c>
       <c r="K18" t="n">
-        <v>20.5</v>
+        <v>22.25</v>
       </c>
     </row>
     <row r="19">
@@ -3158,35 +2862,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.00225115840821352</v>
+        <v>0.00281412303182168</v>
       </c>
       <c r="D19" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E19" t="n">
-        <v>0.001357061971355008</v>
+        <v>0.00118466042658106</v>
       </c>
       <c r="F19" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0004163616826270977</v>
+        <v>0.0004494361343189812</v>
       </c>
       <c r="H19" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1598125154675447</v>
+        <v>0.1609745217265175</v>
       </c>
       <c r="J19" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K19" t="n">
-        <v>22.25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -3195,35 +2899,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.002423001199226675</v>
+        <v>0.002933469357508301</v>
       </c>
       <c r="D20" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E20" t="n">
-        <v>0.002412386175043696</v>
+        <v>0.0008546693811585762</v>
       </c>
       <c r="F20" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0008939545123207493</v>
+        <v>0.001920355074727909</v>
       </c>
       <c r="H20" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1038346518305531</v>
+        <v>0.1340082756701844</v>
       </c>
       <c r="J20" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="K20" t="n">
-        <v>22.5</v>
+        <v>23.25</v>
       </c>
     </row>
     <row r="21">
@@ -3232,35 +2936,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.001615536306275759</v>
+        <v>0.003017239130651168</v>
       </c>
       <c r="D21" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E21" t="n">
-        <v>0.002557803826870271</v>
+        <v>0.002613929821600999</v>
       </c>
       <c r="F21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0003160224410929891</v>
+        <v>-8.627531463611948e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2062187982627752</v>
+        <v>0.1300982458321855</v>
       </c>
       <c r="J21" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K21" t="n">
-        <v>22.5</v>
+        <v>24.25</v>
       </c>
     </row>
   </sheetData>
@@ -3274,7 +2978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3304,7 +3008,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4165063630280615</v>
+        <v>0.5920742209544035</v>
       </c>
     </row>
     <row r="3">
@@ -3313,11 +3017,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2808911641104241</v>
+        <v>0.09496593287494429</v>
       </c>
     </row>
     <row r="4">
@@ -3330,7 +3034,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.0704731334153732</v>
+        <v>0.08967119999287057</v>
       </c>
     </row>
     <row r="5">
@@ -3339,11 +3043,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.05936462511312079</v>
+        <v>0.08167065478904427</v>
       </c>
     </row>
     <row r="6">
@@ -3352,11 +3056,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.05523915390276699</v>
+        <v>0.01421334901113243</v>
       </c>
     </row>
     <row r="7">
@@ -3365,11 +3069,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.01437921541051098</v>
+        <v>0.01047054099489799</v>
       </c>
     </row>
     <row r="8">
@@ -3378,11 +3082,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.007332764951427079</v>
+        <v>0.008659263575318672</v>
       </c>
     </row>
     <row r="9">
@@ -3395,7 +3099,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.005951551135848279</v>
+        <v>0.008619581204237481</v>
       </c>
     </row>
     <row r="10">
@@ -3404,11 +3108,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.005865493220224619</v>
+        <v>0.007872805879607678</v>
       </c>
     </row>
     <row r="11">
@@ -3417,11 +3121,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.005568558762841301</v>
+        <v>0.007350305572308778</v>
       </c>
     </row>
     <row r="12">
@@ -3430,11 +3134,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.00542538573678234</v>
+        <v>0.005805417654146275</v>
       </c>
     </row>
     <row r="13">
@@ -3443,11 +3147,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.004053578774404341</v>
+        <v>0.004913497195705433</v>
       </c>
     </row>
     <row r="14">
@@ -3456,11 +3160,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.003786938594379947</v>
+        <v>0.004511930585227162</v>
       </c>
     </row>
     <row r="15">
@@ -3473,7 +3177,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.003680338482789539</v>
+        <v>0.004171390416423985</v>
       </c>
     </row>
     <row r="16">
@@ -3482,11 +3186,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.00358843655999448</v>
+        <v>0.003977406121844788</v>
       </c>
     </row>
     <row r="17">
@@ -3495,11 +3199,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.003182975224781823</v>
+        <v>0.00380271714631139</v>
       </c>
     </row>
     <row r="18">
@@ -3508,11 +3212,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.003116999146508176</v>
+        <v>0.003639393511303549</v>
       </c>
     </row>
     <row r="19">
@@ -3521,11 +3225,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.002450678522644812</v>
+        <v>0.003035328153665141</v>
       </c>
     </row>
     <row r="20">
@@ -3534,11 +3238,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.002423001199226675</v>
+        <v>0.003017239130651168</v>
       </c>
     </row>
     <row r="21">
@@ -3547,11 +3251,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.002266012182974288</v>
+        <v>0.002950072652216257</v>
       </c>
     </row>
     <row r="22">
@@ -3560,11 +3264,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.00225115840821352</v>
+        <v>0.002933469357508301</v>
       </c>
     </row>
     <row r="23">
@@ -3573,11 +3277,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.00220460670377708</v>
+        <v>0.002907683011589532</v>
       </c>
     </row>
     <row r="24">
@@ -3586,11 +3290,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.002181944414213</v>
+        <v>0.00281412303182168</v>
       </c>
     </row>
     <row r="25">
@@ -3599,11 +3303,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.002072288043532046</v>
+        <v>0.002703183944969406</v>
       </c>
     </row>
     <row r="26">
@@ -3612,11 +3316,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.001952816557958622</v>
+        <v>0.002613759898075903</v>
       </c>
     </row>
     <row r="27">
@@ -3625,11 +3329,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.001925401250557361</v>
+        <v>0.002536620423087952</v>
       </c>
     </row>
     <row r="28">
@@ -3638,11 +3342,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.001909589683063649</v>
+        <v>0.002228427751615875</v>
       </c>
     </row>
     <row r="29">
@@ -3651,11 +3355,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.001880153310329902</v>
+        <v>0.002208798431234469</v>
       </c>
     </row>
     <row r="30">
@@ -3664,11 +3368,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.001876100480860019</v>
+        <v>0.002206623688330278</v>
       </c>
     </row>
     <row r="31">
@@ -3677,11 +3381,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.00168310873626361</v>
+        <v>0.002188873242683482</v>
       </c>
     </row>
     <row r="32">
@@ -3690,11 +3394,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.001615536306275759</v>
+        <v>0.002114945787401633</v>
       </c>
     </row>
     <row r="33">
@@ -3703,11 +3407,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.001546442873848397</v>
+        <v>0.001898504610182973</v>
       </c>
     </row>
     <row r="34">
@@ -3716,11 +3420,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.001523763742701117</v>
+        <v>0.001882208831225212</v>
       </c>
     </row>
     <row r="35">
@@ -3729,11 +3433,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.001489522975204905</v>
+        <v>0.001814753712862562</v>
       </c>
     </row>
     <row r="36">
@@ -3742,11 +3446,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.001467879364589689</v>
+        <v>0.001812279178860347</v>
       </c>
     </row>
     <row r="37">
@@ -3755,11 +3459,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.001459353406819576</v>
+        <v>0.001795922268633566</v>
       </c>
     </row>
     <row r="38">
@@ -3768,11 +3472,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.001422216227604319</v>
+        <v>0.0016069423763632</v>
       </c>
     </row>
     <row r="39">
@@ -3781,11 +3485,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.001405256658231053</v>
+        <v>0.001590591978543202</v>
       </c>
     </row>
     <row r="40">
@@ -3794,11 +3498,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.001377660164585235</v>
+        <v>0.001506392619819774</v>
       </c>
     </row>
     <row r="41">
@@ -3807,11 +3511,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.001324181788718726</v>
+        <v>0.001488815140054277</v>
       </c>
     </row>
     <row r="42">
@@ -3820,11 +3524,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0013199485006502</v>
+        <v>0.001237943634158155</v>
       </c>
     </row>
     <row r="43">
@@ -3833,11 +3537,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.001278372169820007</v>
+        <v>0.0001955000532993873</v>
       </c>
     </row>
     <row r="44">
@@ -3846,11 +3550,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.001259483624557032</v>
+        <v>0.0001823049081357287</v>
       </c>
     </row>
     <row r="45">
@@ -3859,11 +3563,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.001170717320282009</v>
+        <v>0.00012232478004381</v>
       </c>
     </row>
     <row r="46">
@@ -3872,115 +3576,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.001159971095830336</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>boiling_r3_pol</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.00111841178422654</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>wastewater_r2_pol</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0.001105095374194287</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_2</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.0006485909228951996</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_1</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0.0005306475056556192</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.0001249375002640287</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>shift_name</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>7.577446736926195e-05</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>boiler_hardness</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>6.737916972965479e-05</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>carbonated_alkalinity</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>2.532199209291146e-05</v>
+        <v>1.675992323848266e-05</v>
       </c>
     </row>
   </sheetData>
@@ -3994,7 +3594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4024,7 +3624,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3306041230813141</v>
+        <v>0.4679226951658499</v>
       </c>
     </row>
     <row r="3">
@@ -4033,11 +3633,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2390766078490786</v>
+        <v>0.2154339671576504</v>
       </c>
     </row>
     <row r="4">
@@ -4046,11 +3646,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1472118822135189</v>
+        <v>0.08670767180741892</v>
       </c>
     </row>
     <row r="5">
@@ -4059,11 +3659,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.07063431481632378</v>
+        <v>0.06926788527600564</v>
       </c>
     </row>
     <row r="6">
@@ -4072,11 +3672,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.05099292444392457</v>
+        <v>0.01781167675747098</v>
       </c>
     </row>
     <row r="7">
@@ -4085,11 +3685,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0396324080579542</v>
+        <v>0.01642505265108248</v>
       </c>
     </row>
     <row r="8">
@@ -4098,11 +3698,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.01171508403166955</v>
+        <v>0.0159312519072255</v>
       </c>
     </row>
     <row r="9">
@@ -4111,11 +3711,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.01166209065597926</v>
+        <v>0.01496345785060761</v>
       </c>
     </row>
     <row r="10">
@@ -4124,11 +3724,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.01139603876227962</v>
+        <v>0.01353967665917896</v>
       </c>
     </row>
     <row r="11">
@@ -4137,11 +3737,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.008973586438909669</v>
+        <v>0.0128559873647453</v>
       </c>
     </row>
     <row r="12">
@@ -4150,11 +3750,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.008049120596560178</v>
+        <v>0.01190476707562985</v>
       </c>
     </row>
     <row r="13">
@@ -4163,11 +3763,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.007637278622181098</v>
+        <v>0.008556315930821014</v>
       </c>
     </row>
     <row r="14">
@@ -4176,11 +3776,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.004791652244209006</v>
+        <v>0.00481808450208358</v>
       </c>
     </row>
     <row r="15">
@@ -4189,11 +3789,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.004671017670986557</v>
+        <v>0.002914915260674493</v>
       </c>
     </row>
     <row r="16">
@@ -4202,11 +3802,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.004507777600072711</v>
+        <v>0.002774350947291762</v>
       </c>
     </row>
     <row r="17">
@@ -4215,11 +3815,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.003549982278399404</v>
+        <v>0.002613929821600999</v>
       </c>
     </row>
     <row r="18">
@@ -4228,11 +3828,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.002557803826870271</v>
+        <v>0.002582528428023573</v>
       </c>
     </row>
     <row r="19">
@@ -4241,11 +3841,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.002412386175043696</v>
+        <v>0.002527577588815142</v>
       </c>
     </row>
     <row r="20">
@@ -4254,11 +3854,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.002111454812359339</v>
+        <v>0.002353100713898803</v>
       </c>
     </row>
     <row r="21">
@@ -4267,11 +3867,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.001934360536190422</v>
+        <v>0.002172313056935274</v>
       </c>
     </row>
     <row r="22">
@@ -4280,11 +3880,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.001843656198317041</v>
+        <v>0.002102191164414161</v>
       </c>
     </row>
     <row r="23">
@@ -4293,11 +3893,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.001829738778094041</v>
+        <v>0.001839449130005477</v>
       </c>
     </row>
     <row r="24">
@@ -4306,11 +3906,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.001813175004032185</v>
+        <v>0.001370530624470443</v>
       </c>
     </row>
     <row r="25">
@@ -4319,11 +3919,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.001807229545069563</v>
+        <v>0.001265914054842857</v>
       </c>
     </row>
     <row r="26">
@@ -4332,11 +3932,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.001721754149235873</v>
+        <v>0.001231253241034245</v>
       </c>
     </row>
     <row r="27">
@@ -4345,11 +3945,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.001475508310899919</v>
+        <v>0.001211296857974932</v>
       </c>
     </row>
     <row r="28">
@@ -4358,11 +3958,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.001357061971355008</v>
+        <v>0.001199729026705398</v>
       </c>
     </row>
     <row r="29">
@@ -4371,11 +3971,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0013480432808974</v>
+        <v>0.001198887999553266</v>
       </c>
     </row>
     <row r="30">
@@ -4384,11 +3984,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.001237897278353882</v>
+        <v>0.001192275866598129</v>
       </c>
     </row>
     <row r="31">
@@ -4397,11 +3997,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.001231804086661222</v>
+        <v>0.00118466042658106</v>
       </c>
     </row>
     <row r="32">
@@ -4410,11 +4010,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.001207563170348514</v>
+        <v>0.001163182844239249</v>
       </c>
     </row>
     <row r="33">
@@ -4423,11 +4023,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.001154547130382378</v>
+        <v>0.001140085161598094</v>
       </c>
     </row>
     <row r="34">
@@ -4436,11 +4036,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.001101450565593942</v>
+        <v>0.001112629681782611</v>
       </c>
     </row>
     <row r="35">
@@ -4449,11 +4049,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.001095079940739656</v>
+        <v>0.001100329891203608</v>
       </c>
     </row>
     <row r="36">
@@ -4462,11 +4062,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.00109379240620066</v>
+        <v>0.001057381532781222</v>
       </c>
     </row>
     <row r="37">
@@ -4475,11 +4075,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.001075282134623642</v>
+        <v>0.001027086686044412</v>
       </c>
     </row>
     <row r="38">
@@ -4488,11 +4088,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.001058699724778284</v>
+        <v>0.0009908512039546642</v>
       </c>
     </row>
     <row r="39">
@@ -4501,11 +4101,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.00104881979376202</v>
+        <v>0.0009889208037062104</v>
       </c>
     </row>
     <row r="40">
@@ -4514,11 +4114,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.001045676264699847</v>
+        <v>0.0009661410966560955</v>
       </c>
     </row>
     <row r="41">
@@ -4527,11 +4127,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.001014908604712684</v>
+        <v>0.0008546693811585762</v>
       </c>
     </row>
     <row r="42">
@@ -4540,11 +4140,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.001002967469465903</v>
+        <v>0.0006994352667825254</v>
       </c>
     </row>
     <row r="43">
@@ -4553,11 +4153,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.0009939507152283882</v>
+        <v>0.0005157339857014848</v>
       </c>
     </row>
     <row r="44">
@@ -4566,11 +4166,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.0009511806763082975</v>
+        <v>0.0002214324671219349</v>
       </c>
     </row>
     <row r="45">
@@ -4579,11 +4179,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.0009266225191322128</v>
+        <v>0.0001851066041741383</v>
       </c>
     </row>
     <row r="46">
@@ -4592,115 +4192,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0009263130496737242</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_2</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.0008914295508628588</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>boiling_r3_q</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0.0008008771383007751</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>boiling_r3_pol</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.0007946482086225369</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_1</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0.000767815827354959</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>boiler_hardness</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.0005170322901136405</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>shift_name</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0.0003402447111151486</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>0.0002812180453595566</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>carbonated_alkalinity</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>0.0001221167458791846</v>
+        <v>0.0001036190779050449</v>
       </c>
     </row>
   </sheetData>
@@ -4714,7 +4210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4749,10 +4245,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4761045525333641</v>
+        <v>1.031908169033023</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03515390124805571</v>
+        <v>0.06483460901878255</v>
       </c>
     </row>
     <row r="3">
@@ -4761,14 +4257,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2791487904168629</v>
+        <v>0.02395540046258777</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02224560841029052</v>
+        <v>0.004148256530987549</v>
       </c>
     </row>
     <row r="4">
@@ -4777,14 +4273,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.02360148039191767</v>
+        <v>0.02365507463254061</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003959301992855883</v>
+        <v>0.004529487375333506</v>
       </c>
     </row>
     <row r="5">
@@ -4793,14 +4289,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.01139062738611738</v>
+        <v>0.01782556110928256</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003265662775843141</v>
+        <v>0.003800625711887561</v>
       </c>
     </row>
     <row r="6">
@@ -4809,14 +4305,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01033062653383406</v>
+        <v>0.005746459978263685</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002037440960858786</v>
+        <v>0.002049372547728696</v>
       </c>
     </row>
     <row r="7">
@@ -4825,14 +4321,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.008552106770008071</v>
+        <v>0.004252076778319102</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002068625637215081</v>
+        <v>0.0006413031319941207</v>
       </c>
     </row>
     <row r="8">
@@ -4841,14 +4337,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.002523136450429486</v>
+        <v>0.003952990711925663</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0005373922822073943</v>
+        <v>0.002320657529912883</v>
       </c>
     </row>
     <row r="9">
@@ -4857,14 +4353,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.002352385369849608</v>
+        <v>0.003468478794544239</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001171440340158609</v>
+        <v>0.0005071331507324282</v>
       </c>
     </row>
     <row r="10">
@@ -4873,14 +4369,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>sheet_name</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.002136458895167481</v>
+        <v>0.00332199820672759</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001249642493012473</v>
+        <v>0.0002886049665169193</v>
       </c>
     </row>
     <row r="11">
@@ -4893,10 +4389,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001733866369081005</v>
+        <v>0.002740628099216091</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001280745624214428</v>
+        <v>0.001932407804346836</v>
       </c>
     </row>
     <row r="12">
@@ -4905,14 +4401,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001664456317987884</v>
+        <v>0.002653734574104982</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0006350417102082824</v>
+        <v>0.0007640228709403788</v>
       </c>
     </row>
     <row r="13">
@@ -4921,14 +4417,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sheet_name</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.0014827288783222</v>
+        <v>0.001920355074727909</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0001794409693926725</v>
+        <v>0.0008099875507001177</v>
       </c>
     </row>
     <row r="14">
@@ -4937,14 +4433,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.00129758752940613</v>
+        <v>0.001082700563551575</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0006847882641749602</v>
+        <v>0.0004245562138236915</v>
       </c>
     </row>
     <row r="15">
@@ -4953,14 +4449,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.001005090769901151</v>
+        <v>0.0009534297387564616</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0002328475787992394</v>
+        <v>0.0006004919467179716</v>
       </c>
     </row>
     <row r="16">
@@ -4969,14 +4465,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0009216647418518575</v>
+        <v>0.0008744190762375537</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0002641336677146671</v>
+        <v>0.0001470382160563812</v>
       </c>
     </row>
     <row r="17">
@@ -4985,14 +4481,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0008939545123207493</v>
+        <v>0.0008421070769518146</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0004956754370202931</v>
+        <v>0.0002660159538487669</v>
       </c>
     </row>
     <row r="18">
@@ -5001,14 +4497,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0006425803427979271</v>
+        <v>0.0007612504259516872</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0004416961751193849</v>
+        <v>0.0004563029984586963</v>
       </c>
     </row>
     <row r="19">
@@ -5017,14 +4513,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0004939475910281765</v>
+        <v>0.0006414853561366396</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0002284868843701428</v>
+        <v>0.0003642809832461546</v>
       </c>
     </row>
     <row r="20">
@@ -5033,14 +4529,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.00047072720512219</v>
+        <v>0.000501418140758847</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0002011924938086137</v>
+        <v>0.00029015617009795</v>
       </c>
     </row>
     <row r="21">
@@ -5049,14 +4545,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0004189207118883931</v>
+        <v>0.0004897220609223152</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0002205058215989761</v>
+        <v>0.0001841017615487794</v>
       </c>
     </row>
     <row r="22">
@@ -5065,14 +4561,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0004163616826270977</v>
+        <v>0.0004787536452435015</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0004101029283148488</v>
+        <v>0.0002588665096283554</v>
       </c>
     </row>
     <row r="23">
@@ -5081,14 +4577,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0004086844772112186</v>
+        <v>0.000462372387614507</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0002584483202664728</v>
+        <v>0.0003076794031763569</v>
       </c>
     </row>
     <row r="24">
@@ -5097,14 +4593,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.000387969342948602</v>
+        <v>0.0004494361343189812</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0004842629602930608</v>
+        <v>0.0004424233595838965</v>
       </c>
     </row>
     <row r="25">
@@ -5113,14 +4609,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0003681251614669811</v>
+        <v>0.0004079862201908813</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0001901413595004068</v>
+        <v>0.0002649739726124574</v>
       </c>
     </row>
     <row r="26">
@@ -5129,14 +4625,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0003298602118368188</v>
+        <v>0.0004009693875428822</v>
       </c>
       <c r="D26" t="n">
-        <v>7.42025610728648e-05</v>
+        <v>0.0003004140324106993</v>
       </c>
     </row>
     <row r="27">
@@ -5145,14 +4641,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0003281996298877377</v>
+        <v>0.0003992164384769903</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0001265747425788562</v>
+        <v>0.0001887227518379333</v>
       </c>
     </row>
     <row r="28">
@@ -5161,14 +4657,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0003160224410929891</v>
+        <v>0.0003700175390899507</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0001936066576622069</v>
+        <v>0.0002503622416564516</v>
       </c>
     </row>
     <row r="29">
@@ -5177,14 +4673,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0002886776865377749</v>
+        <v>0.0003445281492521657</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0002998485437186469</v>
+        <v>0.0008558601442587333</v>
       </c>
     </row>
     <row r="30">
@@ -5193,14 +4689,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0002731873965256759</v>
+        <v>0.0003386623738867222</v>
       </c>
       <c r="D30" t="n">
-        <v>0.000278062110645897</v>
+        <v>0.0008694353663974934</v>
       </c>
     </row>
     <row r="31">
@@ -5209,14 +4705,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0002265491737181713</v>
+        <v>0.000212479767682694</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0004667151962868532</v>
+        <v>0.000297356347470635</v>
       </c>
     </row>
     <row r="32">
@@ -5225,14 +4721,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0001433223145790419</v>
+        <v>0.0001435333525940385</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0001606887678236195</v>
+        <v>0.0004886335786264656</v>
       </c>
     </row>
     <row r="33">
@@ -5241,14 +4737,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.000125652302639645</v>
+        <v>0.0001307880198220035</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0002027547360125282</v>
+        <v>0.000211848864335124</v>
       </c>
     </row>
     <row r="34">
@@ -5257,14 +4753,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0001045709538454731</v>
+        <v>6.518018794301472e-05</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0005433195132755317</v>
+        <v>0.0003202677272923181</v>
       </c>
     </row>
     <row r="35">
@@ -5273,14 +4769,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0001004520136867804</v>
+        <v>6.302967083727795e-05</v>
       </c>
       <c r="D35" t="n">
-        <v>7.699375576561304e-05</v>
+        <v>4.939716127416846e-05</v>
       </c>
     </row>
     <row r="36">
@@ -5289,14 +4785,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4.996488354246376e-05</v>
+        <v>2.0592047542356e-05</v>
       </c>
       <c r="D36" t="n">
-        <v>9.530251591256675e-05</v>
+        <v>7.98906797493988e-06</v>
       </c>
     </row>
     <row r="37">
@@ -5305,14 +4801,14 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>white_quality_moisture_2</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4.448725532436581e-05</v>
+        <v>1.044119178074121e-05</v>
       </c>
       <c r="D37" t="n">
-        <v>8.10229410632983e-05</v>
+        <v>0.0003873844645454328</v>
       </c>
     </row>
     <row r="38">
@@ -5321,14 +4817,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4.357300668266229e-05</v>
+        <v>-5.205685512910119e-06</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0002140827525696152</v>
+        <v>0.0005181812916777388</v>
       </c>
     </row>
     <row r="39">
@@ -5337,14 +4833,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4.210899185663752e-05</v>
+        <v>-5.264588066035136e-05</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0001591835438267418</v>
+        <v>0.0001005926659898474</v>
       </c>
     </row>
     <row r="40">
@@ -5353,14 +4849,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2.258744967038595e-05</v>
+        <v>-8.627531463611948e-05</v>
       </c>
       <c r="D40" t="n">
-        <v>2.36203310726899e-05</v>
+        <v>0.0005851475196628253</v>
       </c>
     </row>
     <row r="41">
@@ -5369,14 +4865,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6.820480638736192e-06</v>
+        <v>-0.0001037090056165812</v>
       </c>
       <c r="D41" t="n">
-        <v>4.485582365178197e-05</v>
+        <v>0.0002515606320212552</v>
       </c>
     </row>
     <row r="42">
@@ -5385,14 +4881,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2.762245849663447e-06</v>
+        <v>-0.0001089199559701659</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0001595544517068001</v>
+        <v>4.571503364579956e-05</v>
       </c>
     </row>
     <row r="43">
@@ -5401,14 +4897,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-9.861126962218414e-07</v>
+        <v>-0.0001643881675597592</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0001482059553467903</v>
+        <v>0.0003015750209263514</v>
       </c>
     </row>
     <row r="44">
@@ -5417,14 +4913,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-9.206848448517491e-06</v>
+        <v>-0.0002423586497693808</v>
       </c>
       <c r="D44" t="n">
-        <v>7.775929036744435e-06</v>
+        <v>0.0007249012455583655</v>
       </c>
     </row>
     <row r="45">
@@ -5433,14 +4929,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-1.721897560961194e-05</v>
+        <v>-0.0002699360974856791</v>
       </c>
       <c r="D45" t="n">
-        <v>9.490379946940288e-05</v>
+        <v>0.0002667323064682876</v>
       </c>
     </row>
     <row r="46">
@@ -5453,138 +4949,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-3.494969673079051e-05</v>
+        <v>-0.0007954739357298624</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0001287288212643273</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>shift_name</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>-5.125645230293907e-05</v>
-      </c>
-      <c r="D47" t="n">
-        <v>1.941419715886425e-05</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>sulphited_pH</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>-5.223207071622937e-05</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0.0005565570931598128</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>standard_liquor_pH</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>-7.407733931898974e-05</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0.0002236628811538142</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>co2_percent</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>-0.0001195851064772269</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0.0001561249239193307</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>wastewater_r2_pol</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>-0.0003023502629998176</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0.0002050707450227234</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>wastewater_r1_pol</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>-0.0003126019529183788</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0.000262627523622785</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>boiling_r1_pol</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>-0.000338981420510287</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0.0002626940205436014</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>sweetwater_brix</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>-0.0006547469196776956</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0.0003377717366934631</v>
+        <v>0.0003342289718296256</v>
       </c>
     </row>
   </sheetData>
@@ -5598,7 +4966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5628,7 +4996,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.236279030419674</v>
+        <v>1.445085822558013</v>
       </c>
     </row>
     <row r="3">
@@ -5641,7 +5009,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.198349616808716</v>
+        <v>1.208046827087069</v>
       </c>
     </row>
     <row r="4">
@@ -5650,11 +5018,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>white_ash</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.072530669500765</v>
+        <v>0.6762138378539095</v>
       </c>
     </row>
     <row r="5">
@@ -5663,11 +5031,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>white_ash</t>
+          <t>work_day</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6822701612908508</v>
+        <v>0.66269244681932</v>
       </c>
     </row>
     <row r="6">
@@ -5676,11 +5044,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>work_day</t>
+          <t>white_moisture</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.6640910913673306</v>
+        <v>0.6215641572957189</v>
       </c>
     </row>
     <row r="7">
@@ -5689,11 +5057,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>white_moisture</t>
+          <t>report_date_month</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6178166855264426</v>
+        <v>0.5026811508925402</v>
       </c>
     </row>
     <row r="8">
@@ -5702,11 +5070,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>report_date_month</t>
+          <t>white_invert</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.4961148960923709</v>
+        <v>0.4605703166301494</v>
       </c>
     </row>
     <row r="9">
@@ -5715,11 +5083,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>white_invert</t>
+          <t>report_date_day</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.4739090618199784</v>
+        <v>0.361662266454982</v>
       </c>
     </row>
     <row r="10">
@@ -5728,11 +5096,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>report_date_day</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.3677464095429919</v>
+        <v>0.2422781661061482</v>
       </c>
     </row>
     <row r="11">
@@ -5741,11 +5109,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_1</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.28650978335402</v>
+        <v>0.1979102120027658</v>
       </c>
     </row>
     <row r="12">
@@ -5754,11 +5122,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.2398858944846856</v>
+        <v>0.1959490560392148</v>
       </c>
     </row>
     <row r="13">
@@ -5767,11 +5135,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_1</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.2387552123432464</v>
+        <v>0.1956021692664685</v>
       </c>
     </row>
     <row r="14">
@@ -5780,11 +5148,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>white_quality_apparent_color_2</t>
+          <t>sweetwater_brix</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.229810539278942</v>
+        <v>0.1944292539484866</v>
       </c>
     </row>
     <row r="15">
@@ -5793,11 +5161,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>report_date_year</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.2162787103716499</v>
+        <v>0.1873592230830228</v>
       </c>
     </row>
     <row r="16">
@@ -5810,7 +5178,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.2062187982627752</v>
+        <v>0.1829621589958523</v>
       </c>
     </row>
     <row r="17">
@@ -5819,11 +5187,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.2045485718760616</v>
+        <v>0.1609745217265175</v>
       </c>
     </row>
     <row r="18">
@@ -5832,11 +5200,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.1975684889068154</v>
+        <v>0.1570288853233155</v>
       </c>
     </row>
     <row r="19">
@@ -5845,11 +5213,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>sulphited_color</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.1925807873599821</v>
+        <v>0.1429028751153396</v>
       </c>
     </row>
     <row r="20">
@@ -5858,11 +5226,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>report_year</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.1601129381638917</v>
+        <v>0.1371412425332703</v>
       </c>
     </row>
     <row r="21">
@@ -5871,11 +5239,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.1598125154675447</v>
+        <v>0.1340082756701844</v>
       </c>
     </row>
     <row r="22">
@@ -5884,11 +5252,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.1533962047699582</v>
+        <v>0.1333401570501227</v>
       </c>
     </row>
     <row r="23">
@@ -5897,11 +5265,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>white_quality_ash_1</t>
+          <t>standard_liquor_color</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.1416256039247572</v>
+        <v>0.1327844524658035</v>
       </c>
     </row>
     <row r="24">
@@ -5910,11 +5278,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>report_date_year</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.1407178423155786</v>
+        <v>0.1300982458321855</v>
       </c>
     </row>
     <row r="25">
@@ -5923,11 +5291,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>white_quality_solution_color_2</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.1399203475237156</v>
+        <v>0.1296686657626984</v>
       </c>
     </row>
     <row r="26">
@@ -5936,11 +5304,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.1374923718309686</v>
+        <v>0.1247615231682322</v>
       </c>
     </row>
     <row r="27">
@@ -5949,11 +5317,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.1314372965756354</v>
+        <v>0.1205109958479595</v>
       </c>
     </row>
     <row r="28">
@@ -5962,11 +5330,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.1294575803156772</v>
+        <v>0.1127553931185408</v>
       </c>
     </row>
     <row r="29">
@@ -5975,11 +5343,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.1282316679533264</v>
+        <v>0.105556233734625</v>
       </c>
     </row>
     <row r="30">
@@ -5988,11 +5356,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.1215714553125802</v>
+        <v>0.1037297377208199</v>
       </c>
     </row>
     <row r="31">
@@ -6001,11 +5369,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>report_year</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.1198625489822751</v>
+        <v>0.1034487711885506</v>
       </c>
     </row>
     <row r="32">
@@ -6014,11 +5382,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>filtercake_sugar</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.1150710484016844</v>
+        <v>0.09590600730350829</v>
       </c>
     </row>
     <row r="33">
@@ -6027,11 +5395,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.1148730857526199</v>
+        <v>0.09229532984918176</v>
       </c>
     </row>
     <row r="34">
@@ -6040,11 +5408,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.1134854836112336</v>
+        <v>0.08913391913071145</v>
       </c>
     </row>
     <row r="35">
@@ -6053,11 +5421,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.11158529414972</v>
+        <v>0.08590775237564729</v>
       </c>
     </row>
     <row r="36">
@@ -6066,11 +5434,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.1062600742559612</v>
+        <v>0.06628200146933505</v>
       </c>
     </row>
     <row r="37">
@@ -6079,11 +5447,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>filtercake_moisture</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.106171265677435</v>
+        <v>0.06526898211343335</v>
       </c>
     </row>
     <row r="38">
@@ -6092,11 +5460,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.1038346518305531</v>
+        <v>0.06330130239914888</v>
       </c>
     </row>
     <row r="39">
@@ -6105,11 +5473,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.09691135010235818</v>
+        <v>0.06281291121510701</v>
       </c>
     </row>
     <row r="40">
@@ -6118,11 +5486,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.08786926996012312</v>
+        <v>0.05831871248340992</v>
       </c>
     </row>
     <row r="41">
@@ -6131,11 +5499,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.08537318741232736</v>
+        <v>0.05812931149084299</v>
       </c>
     </row>
     <row r="42">
@@ -6144,11 +5512,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>white_quality_moisture_1</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.07723852475526449</v>
+        <v>0.05452235026964969</v>
       </c>
     </row>
     <row r="43">
@@ -6157,11 +5525,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.07325591331459158</v>
+        <v>0.0235346423412075</v>
       </c>
     </row>
     <row r="44">
@@ -6170,140 +5538,36 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>shift_name</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.07201304738427394</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.06522008278876879</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.05844033263516879</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>wastewater_r2_pol</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>0.05784603239742125</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>standard_liquor_brix</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>0.0524700468327115</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>boiling_r3_pol</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>0.04452011846688331</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>carbonated_alkalinity</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>0.02298624135869165</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>white_quality_moisture_2</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>0.005638754778659383</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0.0007857841193852355</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>shift_name</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>52</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>boiler_hardness</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6379,10 +5643,10 @@
         <v>197</v>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F2" t="n">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -6391,7 +5655,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-15 07:20:55 UTC</t>
+          <t>2026-06-16 11:48:17 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_apparent_color.xlsx
+++ b/NN/reports/feature_importance_white_apparent_color.xlsx
@@ -587,7 +587,7 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01782556110928256</v>
+        <v>0.01782556110928258</v>
       </c>
       <c r="H4" t="n">
         <v>4</v>
@@ -624,7 +624,7 @@
         <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02365507463254061</v>
+        <v>0.02365507463254059</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -661,7 +661,7 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00332199820672759</v>
+        <v>0.003321998206727679</v>
       </c>
       <c r="H6" t="n">
         <v>9</v>
@@ -698,7 +698,7 @@
         <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004252076778319102</v>
+        <v>0.004252076778319069</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -735,7 +735,7 @@
         <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003952990711925663</v>
+        <v>0.003952990711925642</v>
       </c>
       <c r="H8" t="n">
         <v>7</v>
@@ -772,7 +772,7 @@
         <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0009534297387564616</v>
+        <v>0.0009534297387564505</v>
       </c>
       <c r="H9" t="n">
         <v>14</v>
@@ -809,7 +809,7 @@
         <v>13</v>
       </c>
       <c r="G10" t="n">
-        <v>0.003468478794544239</v>
+        <v>0.00346847879454425</v>
       </c>
       <c r="H10" t="n">
         <v>8</v>
@@ -957,7 +957,7 @@
         <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>0.005746459978263685</v>
+        <v>0.005746459978263696</v>
       </c>
       <c r="H14" t="n">
         <v>5</v>
@@ -994,7 +994,7 @@
         <v>19</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0003445281492521657</v>
+        <v>0.0003445281492521768</v>
       </c>
       <c r="H15" t="n">
         <v>28</v>
@@ -1031,7 +1031,7 @@
         <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0007612504259516872</v>
+        <v>0.0007612504259516762</v>
       </c>
       <c r="H16" t="n">
         <v>17</v>
@@ -1068,7 +1068,7 @@
         <v>12</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004787536452435015</v>
+        <v>0.0004787536452434793</v>
       </c>
       <c r="H17" t="n">
         <v>21</v>
@@ -1105,7 +1105,7 @@
         <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0003386623738867222</v>
+        <v>0.0003386623738867445</v>
       </c>
       <c r="H18" t="n">
         <v>29</v>
@@ -1142,7 +1142,7 @@
         <v>30</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0004494361343189812</v>
+        <v>0.0004494361343189701</v>
       </c>
       <c r="H19" t="n">
         <v>23</v>
@@ -1179,7 +1179,7 @@
         <v>40</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001920355074727909</v>
+        <v>0.00192035507472792</v>
       </c>
       <c r="H20" t="n">
         <v>12</v>
@@ -1216,7 +1216,7 @@
         <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>-8.627531463611948e-05</v>
+        <v>-8.627531463610838e-05</v>
       </c>
       <c r="H21" t="n">
         <v>39</v>
@@ -1253,7 +1253,7 @@
         <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0006414853561366396</v>
+        <v>0.0006414853561366618</v>
       </c>
       <c r="H22" t="n">
         <v>18</v>
@@ -1290,7 +1290,7 @@
         <v>25</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0004079862201908813</v>
+        <v>0.0004079862201908701</v>
       </c>
       <c r="H23" t="n">
         <v>24</v>
@@ -1327,7 +1327,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0001643881675597592</v>
+        <v>-0.0001643881675598147</v>
       </c>
       <c r="H24" t="n">
         <v>42</v>
@@ -1364,7 +1364,7 @@
         <v>27</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0001435333525940385</v>
+        <v>0.0001435333525940274</v>
       </c>
       <c r="H25" t="n">
         <v>31</v>
@@ -1401,7 +1401,7 @@
         <v>21</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.205685512910119e-06</v>
+        <v>-5.205685512887914e-06</v>
       </c>
       <c r="H26" t="n">
         <v>37</v>
@@ -1512,7 +1512,7 @@
         <v>26</v>
       </c>
       <c r="G29" t="n">
-        <v>1.044119178074121e-05</v>
+        <v>1.044119178073011e-05</v>
       </c>
       <c r="H29" t="n">
         <v>36</v>
@@ -1586,7 +1586,7 @@
         <v>33</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0003700175390899507</v>
+        <v>0.0003700175390899396</v>
       </c>
       <c r="H31" t="n">
         <v>27</v>
@@ -1623,7 +1623,7 @@
         <v>37</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0008421070769518146</v>
+        <v>0.0008421070769518257</v>
       </c>
       <c r="H32" t="n">
         <v>16</v>
@@ -1660,7 +1660,7 @@
         <v>23</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0004009693875428822</v>
+        <v>0.000400969387542871</v>
       </c>
       <c r="H33" t="n">
         <v>25</v>
@@ -1697,7 +1697,7 @@
         <v>28</v>
       </c>
       <c r="G34" t="n">
-        <v>0.000212479767682694</v>
+        <v>0.0002124797676826717</v>
       </c>
       <c r="H34" t="n">
         <v>30</v>
@@ -1734,7 +1734,7 @@
         <v>34</v>
       </c>
       <c r="G35" t="n">
-        <v>0.000462372387614507</v>
+        <v>0.000462372387614518</v>
       </c>
       <c r="H35" t="n">
         <v>22</v>
@@ -1771,7 +1771,7 @@
         <v>32</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0003992164384769903</v>
+        <v>0.0003992164384770125</v>
       </c>
       <c r="H36" t="n">
         <v>26</v>
@@ -1808,7 +1808,7 @@
         <v>35</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0001307880198220035</v>
+        <v>0.0001307880198219924</v>
       </c>
       <c r="H37" t="n">
         <v>32</v>
@@ -1845,7 +1845,7 @@
         <v>39</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.0002423586497693808</v>
+        <v>-0.0002423586497693475</v>
       </c>
       <c r="H38" t="n">
         <v>43</v>
@@ -1919,7 +1919,7 @@
         <v>36</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0007954739357298624</v>
+        <v>-0.0007954739357298735</v>
       </c>
       <c r="H40" t="n">
         <v>45</v>
@@ -1993,7 +1993,7 @@
         <v>38</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.0001037090056165812</v>
+        <v>-0.0001037090056165701</v>
       </c>
       <c r="H42" t="n">
         <v>40</v>
@@ -2030,7 +2030,7 @@
         <v>43</v>
       </c>
       <c r="G43" t="n">
-        <v>6.302967083727795e-05</v>
+        <v>6.302967083728905e-05</v>
       </c>
       <c r="H43" t="n">
         <v>34</v>
@@ -2141,7 +2141,7 @@
         <v>44</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.0001089199559701659</v>
+        <v>-0.0001089199559701548</v>
       </c>
       <c r="H46" t="n">
         <v>41</v>
@@ -2323,7 +2323,7 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01782556110928256</v>
+        <v>0.01782556110928258</v>
       </c>
       <c r="H4" t="n">
         <v>4</v>
@@ -2360,7 +2360,7 @@
         <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02365507463254061</v>
+        <v>0.02365507463254059</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -2397,7 +2397,7 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00332199820672759</v>
+        <v>0.003321998206727679</v>
       </c>
       <c r="H6" t="n">
         <v>9</v>
@@ -2434,7 +2434,7 @@
         <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004252076778319102</v>
+        <v>0.004252076778319069</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -2471,7 +2471,7 @@
         <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003952990711925663</v>
+        <v>0.003952990711925642</v>
       </c>
       <c r="H8" t="n">
         <v>7</v>
@@ -2508,7 +2508,7 @@
         <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0009534297387564616</v>
+        <v>0.0009534297387564505</v>
       </c>
       <c r="H9" t="n">
         <v>14</v>
@@ -2545,7 +2545,7 @@
         <v>13</v>
       </c>
       <c r="G10" t="n">
-        <v>0.003468478794544239</v>
+        <v>0.00346847879454425</v>
       </c>
       <c r="H10" t="n">
         <v>8</v>
@@ -2693,7 +2693,7 @@
         <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>0.005746459978263685</v>
+        <v>0.005746459978263696</v>
       </c>
       <c r="H14" t="n">
         <v>5</v>
@@ -2730,7 +2730,7 @@
         <v>19</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0003445281492521657</v>
+        <v>0.0003445281492521768</v>
       </c>
       <c r="H15" t="n">
         <v>28</v>
@@ -2767,7 +2767,7 @@
         <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0007612504259516872</v>
+        <v>0.0007612504259516762</v>
       </c>
       <c r="H16" t="n">
         <v>17</v>
@@ -2804,7 +2804,7 @@
         <v>12</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004787536452435015</v>
+        <v>0.0004787536452434793</v>
       </c>
       <c r="H17" t="n">
         <v>21</v>
@@ -2841,7 +2841,7 @@
         <v>18</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0003386623738867222</v>
+        <v>0.0003386623738867445</v>
       </c>
       <c r="H18" t="n">
         <v>29</v>
@@ -2878,7 +2878,7 @@
         <v>30</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0004494361343189812</v>
+        <v>0.0004494361343189701</v>
       </c>
       <c r="H19" t="n">
         <v>23</v>
@@ -2915,7 +2915,7 @@
         <v>40</v>
       </c>
       <c r="G20" t="n">
-        <v>0.001920355074727909</v>
+        <v>0.00192035507472792</v>
       </c>
       <c r="H20" t="n">
         <v>12</v>
@@ -2952,7 +2952,7 @@
         <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>-8.627531463611948e-05</v>
+        <v>-8.627531463610838e-05</v>
       </c>
       <c r="H21" t="n">
         <v>39</v>
@@ -4248,7 +4248,7 @@
         <v>1.031908169033023</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06483460901878255</v>
+        <v>0.06483460901878252</v>
       </c>
     </row>
     <row r="3">
@@ -4264,7 +4264,7 @@
         <v>0.02395540046258777</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004148256530987549</v>
+        <v>0.004148256530987567</v>
       </c>
     </row>
     <row r="4">
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.02365507463254061</v>
+        <v>0.02365507463254059</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004529487375333506</v>
+        <v>0.004529487375333501</v>
       </c>
     </row>
     <row r="5">
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.01782556110928256</v>
+        <v>0.01782556110928258</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003800625711887561</v>
+        <v>0.003800625711887562</v>
       </c>
     </row>
     <row r="6">
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.005746459978263685</v>
+        <v>0.005746459978263696</v>
       </c>
       <c r="D6" t="n">
         <v>0.002049372547728696</v>
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.004252076778319102</v>
+        <v>0.004252076778319069</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0006413031319941207</v>
+        <v>0.0006413031319941232</v>
       </c>
     </row>
     <row r="8">
@@ -4341,10 +4341,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.003952990711925663</v>
+        <v>0.003952990711925642</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002320657529912883</v>
+        <v>0.002320657529912905</v>
       </c>
     </row>
     <row r="9">
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.003468478794544239</v>
+        <v>0.00346847879454425</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0005071331507324282</v>
+        <v>0.0005071331507324145</v>
       </c>
     </row>
     <row r="10">
@@ -4373,10 +4373,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.00332199820672759</v>
+        <v>0.003321998206727679</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0002886049665169193</v>
+        <v>0.0002886049665165974</v>
       </c>
     </row>
     <row r="11">
@@ -4392,7 +4392,7 @@
         <v>0.002740628099216091</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001932407804346836</v>
+        <v>0.001932407804346833</v>
       </c>
     </row>
     <row r="12">
@@ -4421,10 +4421,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001920355074727909</v>
+        <v>0.00192035507472792</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0008099875507001177</v>
+        <v>0.0008099875507001267</v>
       </c>
     </row>
     <row r="14">
@@ -4440,7 +4440,7 @@
         <v>0.001082700563551575</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0004245562138236915</v>
+        <v>0.0004245562138236739</v>
       </c>
     </row>
     <row r="15">
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0009534297387564616</v>
+        <v>0.0009534297387564505</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0006004919467179716</v>
+        <v>0.0006004919467179795</v>
       </c>
     </row>
     <row r="16">
@@ -4472,7 +4472,7 @@
         <v>0.0008744190762375537</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0001470382160563812</v>
+        <v>0.0001470382160563793</v>
       </c>
     </row>
     <row r="17">
@@ -4485,10 +4485,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0008421070769518146</v>
+        <v>0.0008421070769518257</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0002660159538487669</v>
+        <v>0.0002660159538487716</v>
       </c>
     </row>
     <row r="18">
@@ -4501,10 +4501,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0007612504259516872</v>
+        <v>0.0007612504259516762</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0004563029984586963</v>
+        <v>0.0004563029984587029</v>
       </c>
     </row>
     <row r="19">
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0006414853561366396</v>
+        <v>0.0006414853561366618</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0003642809832461546</v>
+        <v>0.0003642809832461261</v>
       </c>
     </row>
     <row r="20">
@@ -4536,7 +4536,7 @@
         <v>0.000501418140758847</v>
       </c>
       <c r="D20" t="n">
-        <v>0.00029015617009795</v>
+        <v>0.0002901561700979256</v>
       </c>
     </row>
     <row r="21">
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0004787536452435015</v>
+        <v>0.0004787536452434793</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0002588665096283554</v>
+        <v>0.0002588665096283787</v>
       </c>
     </row>
     <row r="23">
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.000462372387614507</v>
+        <v>0.000462372387614518</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0003076794031763569</v>
+        <v>0.0003076794031763396</v>
       </c>
     </row>
     <row r="24">
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0004494361343189812</v>
+        <v>0.0004494361343189701</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0004424233595838965</v>
+        <v>0.0004424233595838924</v>
       </c>
     </row>
     <row r="25">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0004079862201908813</v>
+        <v>0.0004079862201908701</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0002649739726124574</v>
+        <v>0.0002649739726124862</v>
       </c>
     </row>
     <row r="26">
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0004009693875428822</v>
+        <v>0.000400969387542871</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0003004140324106993</v>
+        <v>0.0003004140324106724</v>
       </c>
     </row>
     <row r="27">
@@ -4645,10 +4645,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0003992164384769903</v>
+        <v>0.0003992164384770125</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0001887227518379333</v>
+        <v>0.0001887227518379503</v>
       </c>
     </row>
     <row r="28">
@@ -4661,10 +4661,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0003700175390899507</v>
+        <v>0.0003700175390899396</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0002503622416564516</v>
+        <v>0.0002503622416564283</v>
       </c>
     </row>
     <row r="29">
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0003445281492521657</v>
+        <v>0.0003445281492521768</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0008558601442587333</v>
+        <v>0.0008558601442587256</v>
       </c>
     </row>
     <row r="30">
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.0003386623738867222</v>
+        <v>0.0003386623738867445</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0008694353663974934</v>
+        <v>0.0008694353663974839</v>
       </c>
     </row>
     <row r="31">
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.000212479767682694</v>
+        <v>0.0002124797676826717</v>
       </c>
       <c r="D31" t="n">
-        <v>0.000297356347470635</v>
+        <v>0.0002973563474706347</v>
       </c>
     </row>
     <row r="32">
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0001435333525940385</v>
+        <v>0.0001435333525940274</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0004886335786264656</v>
+        <v>0.0004886335786264794</v>
       </c>
     </row>
     <row r="33">
@@ -4741,10 +4741,10 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.0001307880198220035</v>
+        <v>0.0001307880198219924</v>
       </c>
       <c r="D33" t="n">
-        <v>0.000211848864335124</v>
+        <v>0.0002118488643351195</v>
       </c>
     </row>
     <row r="34">
@@ -4760,7 +4760,7 @@
         <v>6.518018794301472e-05</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0003202677272923181</v>
+        <v>0.0003202677272923424</v>
       </c>
     </row>
     <row r="35">
@@ -4773,10 +4773,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6.302967083727795e-05</v>
+        <v>6.302967083728905e-05</v>
       </c>
       <c r="D35" t="n">
-        <v>4.939716127416846e-05</v>
+        <v>4.939716127420135e-05</v>
       </c>
     </row>
     <row r="36">
@@ -4792,7 +4792,7 @@
         <v>2.0592047542356e-05</v>
       </c>
       <c r="D36" t="n">
-        <v>7.98906797493988e-06</v>
+        <v>7.989067974940258e-06</v>
       </c>
     </row>
     <row r="37">
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.044119178074121e-05</v>
+        <v>1.044119178073011e-05</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0003873844645454328</v>
+        <v>0.0003873844645454435</v>
       </c>
     </row>
     <row r="38">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-5.205685512910119e-06</v>
+        <v>-5.205685512887914e-06</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0005181812916777388</v>
+        <v>0.0005181812916777306</v>
       </c>
     </row>
     <row r="39">
@@ -4840,7 +4840,7 @@
         <v>-5.264588066035136e-05</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0001005926659898474</v>
+        <v>0.0001005926659898859</v>
       </c>
     </row>
     <row r="40">
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-8.627531463611948e-05</v>
+        <v>-8.627531463610838e-05</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0005851475196628253</v>
+        <v>0.0005851475196628157</v>
       </c>
     </row>
     <row r="41">
@@ -4869,10 +4869,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-0.0001037090056165812</v>
+        <v>-0.0001037090056165701</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0002515606320212552</v>
+        <v>0.0002515606320212703</v>
       </c>
     </row>
     <row r="42">
@@ -4885,10 +4885,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-0.0001089199559701659</v>
+        <v>-0.0001089199559701548</v>
       </c>
       <c r="D42" t="n">
-        <v>4.571503364579956e-05</v>
+        <v>4.571503364580398e-05</v>
       </c>
     </row>
     <row r="43">
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-0.0001643881675597592</v>
+        <v>-0.0001643881675598147</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0003015750209263514</v>
+        <v>0.000301575020926359</v>
       </c>
     </row>
     <row r="44">
@@ -4917,10 +4917,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-0.0002423586497693808</v>
+        <v>-0.0002423586497693475</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0007249012455583655</v>
+        <v>0.0007249012455583587</v>
       </c>
     </row>
     <row r="45">
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-0.0007954739357298624</v>
+        <v>-0.0007954739357298735</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0003342289718296256</v>
+        <v>0.0003342289718296362</v>
       </c>
     </row>
   </sheetData>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-16 11:48:17 UTC</t>
+          <t>2026-06-16 14:06:28 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_apparent_color.xlsx
+++ b/NN/reports/feature_importance_white_apparent_color.xlsx
@@ -550,7 +550,7 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02395540046258777</v>
+        <v>0.02395540046258778</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -587,7 +587,7 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01782556110928258</v>
+        <v>0.01782556110928256</v>
       </c>
       <c r="H4" t="n">
         <v>4</v>
@@ -624,7 +624,7 @@
         <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02365507463254059</v>
+        <v>0.02365507463254058</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -661,7 +661,7 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003321998206727679</v>
+        <v>0.00332199820672749</v>
       </c>
       <c r="H6" t="n">
         <v>9</v>
@@ -698,7 +698,7 @@
         <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004252076778319069</v>
+        <v>0.004252076778319081</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -735,7 +735,7 @@
         <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003952990711925642</v>
+        <v>0.003952990711925652</v>
       </c>
       <c r="H8" t="n">
         <v>7</v>
@@ -772,7 +772,7 @@
         <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0009534297387564505</v>
+        <v>0.0009534297387564283</v>
       </c>
       <c r="H9" t="n">
         <v>14</v>
@@ -883,7 +883,7 @@
         <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>0.002740628099216091</v>
+        <v>0.002740628099216103</v>
       </c>
       <c r="H12" t="n">
         <v>10</v>
@@ -920,7 +920,7 @@
         <v>17</v>
       </c>
       <c r="G13" t="n">
-        <v>0.001082700563551575</v>
+        <v>0.001082700563551553</v>
       </c>
       <c r="H13" t="n">
         <v>13</v>
@@ -1031,7 +1031,7 @@
         <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0007612504259516762</v>
+        <v>0.000761250425951665</v>
       </c>
       <c r="H16" t="n">
         <v>17</v>
@@ -1068,7 +1068,7 @@
         <v>12</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004787536452434793</v>
+        <v>0.0004787536452435015</v>
       </c>
       <c r="H17" t="n">
         <v>21</v>
@@ -1142,7 +1142,7 @@
         <v>30</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0004494361343189701</v>
+        <v>0.0004494361343189812</v>
       </c>
       <c r="H19" t="n">
         <v>23</v>
@@ -1179,7 +1179,7 @@
         <v>40</v>
       </c>
       <c r="G20" t="n">
-        <v>0.00192035507472792</v>
+        <v>0.001920355074727886</v>
       </c>
       <c r="H20" t="n">
         <v>12</v>
@@ -1216,7 +1216,7 @@
         <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>-8.627531463610838e-05</v>
+        <v>-8.627531463609728e-05</v>
       </c>
       <c r="H21" t="n">
         <v>39</v>
@@ -1253,7 +1253,7 @@
         <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0006414853561366618</v>
+        <v>0.0006414853561366284</v>
       </c>
       <c r="H22" t="n">
         <v>18</v>
@@ -1290,7 +1290,7 @@
         <v>25</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0004079862201908701</v>
+        <v>0.0004079862201908813</v>
       </c>
       <c r="H23" t="n">
         <v>24</v>
@@ -1327,7 +1327,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0001643881675598147</v>
+        <v>-0.0001643881675597814</v>
       </c>
       <c r="H24" t="n">
         <v>42</v>
@@ -1364,7 +1364,7 @@
         <v>27</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0001435333525940274</v>
+        <v>0.0001435333525940385</v>
       </c>
       <c r="H25" t="n">
         <v>31</v>
@@ -1401,7 +1401,7 @@
         <v>21</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.205685512887914e-06</v>
+        <v>-5.205685512910119e-06</v>
       </c>
       <c r="H26" t="n">
         <v>37</v>
@@ -1438,7 +1438,7 @@
         <v>22</v>
       </c>
       <c r="G27" t="n">
-        <v>6.518018794301472e-05</v>
+        <v>6.518018794300362e-05</v>
       </c>
       <c r="H27" t="n">
         <v>33</v>
@@ -1475,7 +1475,7 @@
         <v>24</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0008744190762375537</v>
+        <v>0.0008744190762375315</v>
       </c>
       <c r="H28" t="n">
         <v>15</v>
@@ -1512,7 +1512,7 @@
         <v>26</v>
       </c>
       <c r="G29" t="n">
-        <v>1.044119178073011e-05</v>
+        <v>1.044119178074121e-05</v>
       </c>
       <c r="H29" t="n">
         <v>36</v>
@@ -1549,7 +1549,7 @@
         <v>31</v>
       </c>
       <c r="G30" t="n">
-        <v>0.000501418140758847</v>
+        <v>0.0005014181407588247</v>
       </c>
       <c r="H30" t="n">
         <v>19</v>
@@ -1660,7 +1660,7 @@
         <v>23</v>
       </c>
       <c r="G33" t="n">
-        <v>0.000400969387542871</v>
+        <v>0.0004009693875429043</v>
       </c>
       <c r="H33" t="n">
         <v>25</v>
@@ -1697,7 +1697,7 @@
         <v>28</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0002124797676826717</v>
+        <v>0.0002124797676826828</v>
       </c>
       <c r="H34" t="n">
         <v>30</v>
@@ -1734,7 +1734,7 @@
         <v>34</v>
       </c>
       <c r="G35" t="n">
-        <v>0.000462372387614518</v>
+        <v>0.0004623723876145291</v>
       </c>
       <c r="H35" t="n">
         <v>22</v>
@@ -1771,7 +1771,7 @@
         <v>32</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0003992164384770125</v>
+        <v>0.0003992164384770014</v>
       </c>
       <c r="H36" t="n">
         <v>26</v>
@@ -1845,7 +1845,7 @@
         <v>39</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.0002423586497693475</v>
+        <v>-0.0002423586497693586</v>
       </c>
       <c r="H38" t="n">
         <v>43</v>
@@ -1882,7 +1882,7 @@
         <v>41</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0004897220609223152</v>
+        <v>0.0004897220609223263</v>
       </c>
       <c r="H39" t="n">
         <v>20</v>
@@ -1919,7 +1919,7 @@
         <v>36</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0007954739357298735</v>
+        <v>-0.0007954739357298624</v>
       </c>
       <c r="H40" t="n">
         <v>45</v>
@@ -1956,7 +1956,7 @@
         <v>29</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.0002699360974856791</v>
+        <v>-0.0002699360974856901</v>
       </c>
       <c r="H41" t="n">
         <v>44</v>
@@ -1993,7 +1993,7 @@
         <v>38</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.0001037090056165701</v>
+        <v>-0.000103709005616559</v>
       </c>
       <c r="H42" t="n">
         <v>40</v>
@@ -2030,7 +2030,7 @@
         <v>43</v>
       </c>
       <c r="G43" t="n">
-        <v>6.302967083728905e-05</v>
+        <v>6.302967083726685e-05</v>
       </c>
       <c r="H43" t="n">
         <v>34</v>
@@ -2067,7 +2067,7 @@
         <v>42</v>
       </c>
       <c r="G44" t="n">
-        <v>-5.264588066035136e-05</v>
+        <v>-5.264588066036247e-05</v>
       </c>
       <c r="H44" t="n">
         <v>38</v>
@@ -2104,7 +2104,7 @@
         <v>45</v>
       </c>
       <c r="G45" t="n">
-        <v>2.0592047542356e-05</v>
+        <v>2.05920475423893e-05</v>
       </c>
       <c r="H45" t="n">
         <v>35</v>
@@ -2141,7 +2141,7 @@
         <v>44</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.0001089199559701548</v>
+        <v>-0.0001089199559701659</v>
       </c>
       <c r="H46" t="n">
         <v>41</v>
@@ -2286,7 +2286,7 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02395540046258777</v>
+        <v>0.02395540046258778</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -2323,7 +2323,7 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01782556110928258</v>
+        <v>0.01782556110928256</v>
       </c>
       <c r="H4" t="n">
         <v>4</v>
@@ -2360,7 +2360,7 @@
         <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02365507463254059</v>
+        <v>0.02365507463254058</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -2397,7 +2397,7 @@
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003321998206727679</v>
+        <v>0.00332199820672749</v>
       </c>
       <c r="H6" t="n">
         <v>9</v>
@@ -2434,7 +2434,7 @@
         <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004252076778319069</v>
+        <v>0.004252076778319081</v>
       </c>
       <c r="H7" t="n">
         <v>6</v>
@@ -2471,7 +2471,7 @@
         <v>8</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003952990711925642</v>
+        <v>0.003952990711925652</v>
       </c>
       <c r="H8" t="n">
         <v>7</v>
@@ -2508,7 +2508,7 @@
         <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0009534297387564505</v>
+        <v>0.0009534297387564283</v>
       </c>
       <c r="H9" t="n">
         <v>14</v>
@@ -2619,7 +2619,7 @@
         <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>0.002740628099216091</v>
+        <v>0.002740628099216103</v>
       </c>
       <c r="H12" t="n">
         <v>10</v>
@@ -2656,7 +2656,7 @@
         <v>17</v>
       </c>
       <c r="G13" t="n">
-        <v>0.001082700563551575</v>
+        <v>0.001082700563551553</v>
       </c>
       <c r="H13" t="n">
         <v>13</v>
@@ -2767,7 +2767,7 @@
         <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0007612504259516762</v>
+        <v>0.000761250425951665</v>
       </c>
       <c r="H16" t="n">
         <v>17</v>
@@ -2804,7 +2804,7 @@
         <v>12</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0004787536452434793</v>
+        <v>0.0004787536452435015</v>
       </c>
       <c r="H17" t="n">
         <v>21</v>
@@ -2878,7 +2878,7 @@
         <v>30</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0004494361343189701</v>
+        <v>0.0004494361343189812</v>
       </c>
       <c r="H19" t="n">
         <v>23</v>
@@ -2915,7 +2915,7 @@
         <v>40</v>
       </c>
       <c r="G20" t="n">
-        <v>0.00192035507472792</v>
+        <v>0.001920355074727886</v>
       </c>
       <c r="H20" t="n">
         <v>12</v>
@@ -2952,7 +2952,7 @@
         <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>-8.627531463610838e-05</v>
+        <v>-8.627531463609728e-05</v>
       </c>
       <c r="H21" t="n">
         <v>39</v>
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.02395540046258777</v>
+        <v>0.02395540046258778</v>
       </c>
       <c r="D3" t="n">
-        <v>0.004148256530987567</v>
+        <v>0.004148256530987549</v>
       </c>
     </row>
     <row r="4">
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.02365507463254059</v>
+        <v>0.02365507463254058</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004529487375333501</v>
+        <v>0.004529487375333487</v>
       </c>
     </row>
     <row r="5">
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.01782556110928258</v>
+        <v>0.01782556110928256</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003800625711887562</v>
+        <v>0.003800625711887582</v>
       </c>
     </row>
     <row r="6">
@@ -4312,7 +4312,7 @@
         <v>0.005746459978263696</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002049372547728696</v>
+        <v>0.002049372547728709</v>
       </c>
     </row>
     <row r="7">
@@ -4325,10 +4325,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.004252076778319069</v>
+        <v>0.004252076778319081</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0006413031319941232</v>
+        <v>0.0006413031319941168</v>
       </c>
     </row>
     <row r="8">
@@ -4341,10 +4341,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.003952990711925642</v>
+        <v>0.003952990711925652</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002320657529912905</v>
+        <v>0.002320657529912886</v>
       </c>
     </row>
     <row r="9">
@@ -4373,10 +4373,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.003321998206727679</v>
+        <v>0.00332199820672749</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0002886049665165974</v>
+        <v>0.0002886049665166643</v>
       </c>
     </row>
     <row r="11">
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.002740628099216091</v>
+        <v>0.002740628099216103</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001932407804346833</v>
+        <v>0.001932407804346844</v>
       </c>
     </row>
     <row r="12">
@@ -4421,10 +4421,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.00192035507472792</v>
+        <v>0.001920355074727886</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0008099875507001267</v>
+        <v>0.0008099875507001553</v>
       </c>
     </row>
     <row r="14">
@@ -4437,10 +4437,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.001082700563551575</v>
+        <v>0.001082700563551553</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0004245562138236739</v>
+        <v>0.0004245562138236652</v>
       </c>
     </row>
     <row r="15">
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.0009534297387564505</v>
+        <v>0.0009534297387564283</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0006004919467179795</v>
+        <v>0.0006004919467179518</v>
       </c>
     </row>
     <row r="16">
@@ -4469,10 +4469,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0008744190762375537</v>
+        <v>0.0008744190762375315</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0001470382160563793</v>
+        <v>0.0001470382160563735</v>
       </c>
     </row>
     <row r="17">
@@ -4501,10 +4501,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0007612504259516762</v>
+        <v>0.000761250425951665</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0004563029984587029</v>
+        <v>0.0004563029984586919</v>
       </c>
     </row>
     <row r="19">
@@ -4517,10 +4517,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0006414853561366618</v>
+        <v>0.0006414853561366284</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0003642809832461261</v>
+        <v>0.0003642809832461361</v>
       </c>
     </row>
     <row r="20">
@@ -4533,10 +4533,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.000501418140758847</v>
+        <v>0.0005014181407588247</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0002901561700979256</v>
+        <v>0.0002901561700979167</v>
       </c>
     </row>
     <row r="21">
@@ -4549,10 +4549,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.0004897220609223152</v>
+        <v>0.0004897220609223263</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0001841017615487794</v>
+        <v>0.0001841017615487763</v>
       </c>
     </row>
     <row r="22">
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0004787536452434793</v>
+        <v>0.0004787536452435015</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0002588665096283787</v>
+        <v>0.0002588665096283406</v>
       </c>
     </row>
     <row r="23">
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.000462372387614518</v>
+        <v>0.0004623723876145291</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0003076794031763396</v>
+        <v>0.0003076794031763406</v>
       </c>
     </row>
     <row r="24">
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0004494361343189701</v>
+        <v>0.0004494361343189812</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0004424233595838924</v>
+        <v>0.0004424233595838965</v>
       </c>
     </row>
     <row r="25">
@@ -4613,10 +4613,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.0004079862201908701</v>
+        <v>0.0004079862201908813</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0002649739726124862</v>
+        <v>0.0002649739726124465</v>
       </c>
     </row>
     <row r="26">
@@ -4629,10 +4629,10 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.000400969387542871</v>
+        <v>0.0004009693875429043</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0003004140324106724</v>
+        <v>0.0003004140324106915</v>
       </c>
     </row>
     <row r="27">
@@ -4645,10 +4645,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0003992164384770125</v>
+        <v>0.0003992164384770014</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0001887227518379503</v>
+        <v>0.0001887227518379191</v>
       </c>
     </row>
     <row r="28">
@@ -4664,7 +4664,7 @@
         <v>0.0003700175390899396</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0002503622416564283</v>
+        <v>0.0002503622416564183</v>
       </c>
     </row>
     <row r="29">
@@ -4680,7 +4680,7 @@
         <v>0.0003445281492521768</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0008558601442587256</v>
+        <v>0.0008558601442587281</v>
       </c>
     </row>
     <row r="30">
@@ -4696,7 +4696,7 @@
         <v>0.0003386623738867445</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0008694353663974839</v>
+        <v>0.0008694353663974704</v>
       </c>
     </row>
     <row r="31">
@@ -4709,10 +4709,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0002124797676826717</v>
+        <v>0.0002124797676826828</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0002973563474706347</v>
+        <v>0.0002973563474706339</v>
       </c>
     </row>
     <row r="32">
@@ -4725,10 +4725,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.0001435333525940274</v>
+        <v>0.0001435333525940385</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0004886335786264794</v>
+        <v>0.0004886335786264628</v>
       </c>
     </row>
     <row r="33">
@@ -4744,7 +4744,7 @@
         <v>0.0001307880198219924</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0002118488643351195</v>
+        <v>0.0002118488643351314</v>
       </c>
     </row>
     <row r="34">
@@ -4757,10 +4757,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6.518018794301472e-05</v>
+        <v>6.518018794300362e-05</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0003202677272923424</v>
+        <v>0.0003202677272923095</v>
       </c>
     </row>
     <row r="35">
@@ -4773,10 +4773,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6.302967083728905e-05</v>
+        <v>6.302967083726685e-05</v>
       </c>
       <c r="D35" t="n">
-        <v>4.939716127420135e-05</v>
+        <v>4.9397161274178e-05</v>
       </c>
     </row>
     <row r="36">
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2.0592047542356e-05</v>
+        <v>2.05920475423893e-05</v>
       </c>
       <c r="D36" t="n">
-        <v>7.989067974940258e-06</v>
+        <v>7.989067974929929e-06</v>
       </c>
     </row>
     <row r="37">
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.044119178073011e-05</v>
+        <v>1.044119178074121e-05</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0003873844645454435</v>
+        <v>0.0003873844645454328</v>
       </c>
     </row>
     <row r="38">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-5.205685512887914e-06</v>
+        <v>-5.205685512910119e-06</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0005181812916777306</v>
+        <v>0.0005181812916777388</v>
       </c>
     </row>
     <row r="39">
@@ -4837,10 +4837,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-5.264588066035136e-05</v>
+        <v>-5.264588066036247e-05</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0001005926659898859</v>
+        <v>0.0001005926659898828</v>
       </c>
     </row>
     <row r="40">
@@ -4853,10 +4853,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-8.627531463610838e-05</v>
+        <v>-8.627531463609728e-05</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0005851475196628157</v>
+        <v>0.0005851475196628058</v>
       </c>
     </row>
     <row r="41">
@@ -4869,10 +4869,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-0.0001037090056165701</v>
+        <v>-0.000103709005616559</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0002515606320212703</v>
+        <v>0.0002515606320212818</v>
       </c>
     </row>
     <row r="42">
@@ -4885,10 +4885,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-0.0001089199559701548</v>
+        <v>-0.0001089199559701659</v>
       </c>
       <c r="D42" t="n">
-        <v>4.571503364580398e-05</v>
+        <v>4.571503364579956e-05</v>
       </c>
     </row>
     <row r="43">
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-0.0001643881675598147</v>
+        <v>-0.0001643881675597814</v>
       </c>
       <c r="D43" t="n">
-        <v>0.000301575020926359</v>
+        <v>0.0003015750209263384</v>
       </c>
     </row>
     <row r="44">
@@ -4917,10 +4917,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-0.0002423586497693475</v>
+        <v>-0.0002423586497693586</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0007249012455583587</v>
+        <v>0.0007249012455583409</v>
       </c>
     </row>
     <row r="45">
@@ -4933,10 +4933,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-0.0002699360974856791</v>
+        <v>-0.0002699360974856901</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0002667323064682876</v>
+        <v>0.0002667323064682776</v>
       </c>
     </row>
     <row r="46">
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-0.0007954739357298735</v>
+        <v>-0.0007954739357298624</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0003342289718296362</v>
+        <v>0.0003342289718296381</v>
       </c>
     </row>
   </sheetData>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-16 14:06:28 UTC</t>
+          <t>2026-06-16 15:18:20 UTC</t>
         </is>
       </c>
     </row>

--- a/NN/reports/feature_importance_white_apparent_color.xlsx
+++ b/NN/reports/feature_importance_white_apparent_color.xlsx
@@ -550,7 +550,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2791487904168628</v>
+        <v>0.2791487904168629</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -587,7 +587,7 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02360148039191765</v>
+        <v>0.02360148039191764</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -624,7 +624,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008552106770008039</v>
+        <v>0.008552106770008051</v>
       </c>
       <c r="H5" t="n">
         <v>6</v>
@@ -661,7 +661,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001482728878322677</v>
+        <v>0.001482728878323179</v>
       </c>
       <c r="H6" t="n">
         <v>12</v>
@@ -698,7 +698,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01139062738611735</v>
+        <v>0.01139062738611738</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
@@ -772,7 +772,7 @@
         <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002352385369849619</v>
+        <v>0.00235238536984963</v>
       </c>
       <c r="H9" t="n">
         <v>8</v>
@@ -809,7 +809,7 @@
         <v>16</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002523136450429464</v>
+        <v>0.002523136450429475</v>
       </c>
       <c r="H10" t="n">
         <v>7</v>
@@ -846,7 +846,7 @@
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002136458895167448</v>
+        <v>0.002136458895167492</v>
       </c>
       <c r="H11" t="n">
         <v>9</v>
@@ -883,7 +883,7 @@
         <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001005090769901163</v>
+        <v>0.001005090769901174</v>
       </c>
       <c r="H12" t="n">
         <v>14</v>
@@ -920,7 +920,7 @@
         <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0009216647418518575</v>
+        <v>0.0009216647418518464</v>
       </c>
       <c r="H13" t="n">
         <v>15</v>
@@ -957,7 +957,7 @@
         <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001733866369081016</v>
+        <v>0.001733866369081005</v>
       </c>
       <c r="H14" t="n">
         <v>10</v>
@@ -994,7 +994,7 @@
         <v>19</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001664456317987884</v>
+        <v>0.001664456317987873</v>
       </c>
       <c r="H15" t="n">
         <v>11</v>
@@ -1031,7 +1031,7 @@
         <v>12</v>
       </c>
       <c r="G16" t="n">
-        <v>0.000387969342948602</v>
+        <v>0.0003879693429486131</v>
       </c>
       <c r="H16" t="n">
         <v>23</v>
@@ -1068,7 +1068,7 @@
         <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>0.001297587529406119</v>
+        <v>0.001297587529406141</v>
       </c>
       <c r="H17" t="n">
         <v>13</v>
@@ -1142,7 +1142,7 @@
         <v>27</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0004163616826270977</v>
+        <v>0.0004163616826271421</v>
       </c>
       <c r="H19" t="n">
         <v>21</v>
@@ -1253,7 +1253,7 @@
         <v>29</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0001045709538454842</v>
+        <v>0.0001045709538454953</v>
       </c>
       <c r="H22" t="n">
         <v>33</v>
@@ -1290,7 +1290,7 @@
         <v>30</v>
       </c>
       <c r="G23" t="n">
-        <v>0.00047072720512219</v>
+        <v>0.0004707272051221678</v>
       </c>
       <c r="H23" t="n">
         <v>19</v>
@@ -1327,7 +1327,7 @@
         <v>28</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0002265491737181602</v>
+        <v>0.0002265491737181713</v>
       </c>
       <c r="H24" t="n">
         <v>30</v>
@@ -1364,7 +1364,7 @@
         <v>22</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.0006547469196777067</v>
+        <v>-0.0006547469196776956</v>
       </c>
       <c r="H25" t="n">
         <v>53</v>
@@ -1401,7 +1401,7 @@
         <v>37</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0004086844772112186</v>
+        <v>0.0004086844772112075</v>
       </c>
       <c r="H26" t="n">
         <v>22</v>
@@ -1475,7 +1475,7 @@
         <v>43</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0006425803427979049</v>
+        <v>0.0006425803427979382</v>
       </c>
       <c r="H28" t="n">
         <v>17</v>
@@ -1512,7 +1512,7 @@
         <v>31</v>
       </c>
       <c r="G29" t="n">
-        <v>0.000143322314579053</v>
+        <v>0.0001433223145790641</v>
       </c>
       <c r="H29" t="n">
         <v>31</v>
@@ -1549,7 +1549,7 @@
         <v>10</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0003281996298877377</v>
+        <v>0.0003281996298877488</v>
       </c>
       <c r="H30" t="n">
         <v>26</v>
@@ -1697,7 +1697,7 @@
         <v>33</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0004939475910281877</v>
+        <v>0.0004939475910281765</v>
       </c>
       <c r="H34" t="n">
         <v>18</v>
@@ -1734,7 +1734,7 @@
         <v>20</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.0003126019529183899</v>
+        <v>-0.0003126019529183677</v>
       </c>
       <c r="H35" t="n">
         <v>51</v>
@@ -1771,7 +1771,7 @@
         <v>26</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.0003389814205102981</v>
+        <v>-0.0003389814205102648</v>
       </c>
       <c r="H36" t="n">
         <v>52</v>
@@ -1956,7 +1956,7 @@
         <v>42</v>
       </c>
       <c r="G41" t="n">
-        <v>4.357300668264008e-05</v>
+        <v>4.357300668265118e-05</v>
       </c>
       <c r="H41" t="n">
         <v>37</v>
@@ -1993,7 +1993,7 @@
         <v>40</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0001004520136867915</v>
+        <v>0.0001004520136867693</v>
       </c>
       <c r="H42" t="n">
         <v>34</v>
@@ -2030,7 +2030,7 @@
         <v>34</v>
       </c>
       <c r="G43" t="n">
-        <v>4.210899185662642e-05</v>
+        <v>4.210899185661532e-05</v>
       </c>
       <c r="H43" t="n">
         <v>38</v>
@@ -2067,7 +2067,7 @@
         <v>47</v>
       </c>
       <c r="G44" t="n">
-        <v>-9.861126962218414e-07</v>
+        <v>-9.861126962107391e-07</v>
       </c>
       <c r="H44" t="n">
         <v>42</v>
@@ -2141,7 +2141,7 @@
         <v>45</v>
       </c>
       <c r="G46" t="n">
-        <v>-3.494969673081272e-05</v>
+        <v>-3.494969673080161e-05</v>
       </c>
       <c r="H46" t="n">
         <v>45</v>
@@ -2178,7 +2178,7 @@
         <v>49</v>
       </c>
       <c r="G47" t="n">
-        <v>4.996488354248596e-05</v>
+        <v>4.996488354246376e-05</v>
       </c>
       <c r="H47" t="n">
         <v>35</v>
@@ -2326,7 +2326,7 @@
         <v>52</v>
       </c>
       <c r="G51" t="n">
-        <v>2.258744967039705e-05</v>
+        <v>2.258744967036375e-05</v>
       </c>
       <c r="H51" t="n">
         <v>39</v>
@@ -2363,7 +2363,7 @@
         <v>50</v>
       </c>
       <c r="G52" t="n">
-        <v>6.82048063872509e-06</v>
+        <v>6.820480638736192e-06</v>
       </c>
       <c r="H52" t="n">
         <v>40</v>
@@ -2400,7 +2400,7 @@
         <v>53</v>
       </c>
       <c r="G53" t="n">
-        <v>-9.206848448506388e-06</v>
+        <v>-9.206848448517491e-06</v>
       </c>
       <c r="H53" t="n">
         <v>43</v>
@@ -2582,7 +2582,7 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2791487904168628</v>
+        <v>0.2791487904168629</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -2619,7 +2619,7 @@
         <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02360148039191765</v>
+        <v>0.02360148039191764</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -2656,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0.008552106770008039</v>
+        <v>0.008552106770008051</v>
       </c>
       <c r="H5" t="n">
         <v>6</v>
@@ -2693,7 +2693,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001482728878322677</v>
+        <v>0.001482728878323179</v>
       </c>
       <c r="H6" t="n">
         <v>12</v>
@@ -2730,7 +2730,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01139062738611735</v>
+        <v>0.01139062738611738</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
@@ -2804,7 +2804,7 @@
         <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002352385369849619</v>
+        <v>0.00235238536984963</v>
       </c>
       <c r="H9" t="n">
         <v>8</v>
@@ -2841,7 +2841,7 @@
         <v>16</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002523136450429464</v>
+        <v>0.002523136450429475</v>
       </c>
       <c r="H10" t="n">
         <v>7</v>
@@ -2878,7 +2878,7 @@
         <v>9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002136458895167448</v>
+        <v>0.002136458895167492</v>
       </c>
       <c r="H11" t="n">
         <v>9</v>
@@ -2915,7 +2915,7 @@
         <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001005090769901163</v>
+        <v>0.001005090769901174</v>
       </c>
       <c r="H12" t="n">
         <v>14</v>
@@ -2952,7 +2952,7 @@
         <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0009216647418518575</v>
+        <v>0.0009216647418518464</v>
       </c>
       <c r="H13" t="n">
         <v>15</v>
@@ -2989,7 +2989,7 @@
         <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.001733866369081016</v>
+        <v>0.001733866369081005</v>
       </c>
       <c r="H14" t="n">
         <v>10</v>
@@ -3026,7 +3026,7 @@
         <v>19</v>
       </c>
       <c r="G15" t="n">
-        <v>0.001664456317987884</v>
+        <v>0.001664456317987873</v>
       </c>
       <c r="H15" t="n">
         <v>11</v>
@@ -3063,7 +3063,7 @@
         <v>12</v>
       </c>
       <c r="G16" t="n">
-        <v>0.000387969342948602</v>
+        <v>0.0003879693429486131</v>
       </c>
       <c r="H16" t="n">
         <v>23</v>
@@ -3100,7 +3100,7 @@
         <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>0.001297587529406119</v>
+        <v>0.001297587529406141</v>
       </c>
       <c r="H17" t="n">
         <v>13</v>
@@ -3174,7 +3174,7 @@
         <v>27</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0004163616826270977</v>
+        <v>0.0004163616826271421</v>
       </c>
       <c r="H19" t="n">
         <v>21</v>
@@ -4752,7 +4752,7 @@
         <v>0.4761045525333641</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03515390124805566</v>
+        <v>0.03515390124805567</v>
       </c>
     </row>
     <row r="3">
@@ -4765,10 +4765,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.2791487904168628</v>
+        <v>0.2791487904168629</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02224560841029055</v>
+        <v>0.02224560841029056</v>
       </c>
     </row>
     <row r="4">
@@ -4781,10 +4781,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.02360148039191765</v>
+        <v>0.02360148039191764</v>
       </c>
       <c r="D4" t="n">
-        <v>0.003959301992855861</v>
+        <v>0.003959301992855852</v>
       </c>
     </row>
     <row r="5">
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.01139062738611735</v>
+        <v>0.01139062738611738</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003265662775843139</v>
+        <v>0.00326566277584314</v>
       </c>
     </row>
     <row r="6">
@@ -4816,7 +4816,7 @@
         <v>0.01033062653383405</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002037440960858772</v>
+        <v>0.002037440960858784</v>
       </c>
     </row>
     <row r="7">
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.008552106770008039</v>
+        <v>0.008552106770008051</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002068625637215055</v>
+        <v>0.002068625637215083</v>
       </c>
     </row>
     <row r="8">
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.002523136450429464</v>
+        <v>0.002523136450429475</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0005373922822073779</v>
+        <v>0.0005373922822073615</v>
       </c>
     </row>
     <row r="9">
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.002352385369849619</v>
+        <v>0.00235238536984963</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001171440340158616</v>
+        <v>0.001171440340158625</v>
       </c>
     </row>
     <row r="10">
@@ -4877,10 +4877,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.002136458895167448</v>
+        <v>0.002136458895167492</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001249642493012471</v>
+        <v>0.001249642493012464</v>
       </c>
     </row>
     <row r="11">
@@ -4893,10 +4893,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.001733866369081016</v>
+        <v>0.001733866369081005</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001280745624214429</v>
+        <v>0.001280745624214428</v>
       </c>
     </row>
     <row r="12">
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.001664456317987884</v>
+        <v>0.001664456317987873</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0006350417102082709</v>
+        <v>0.0006350417102082852</v>
       </c>
     </row>
     <row r="13">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.001482728878322677</v>
+        <v>0.001482728878323179</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0001794409693939473</v>
+        <v>0.0001794409693939698</v>
       </c>
     </row>
     <row r="14">
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.001297587529406119</v>
+        <v>0.001297587529406141</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0006847882641749693</v>
+        <v>0.0006847882641749607</v>
       </c>
     </row>
     <row r="15">
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.001005090769901163</v>
+        <v>0.001005090769901174</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0002328475787992315</v>
+        <v>0.0002328475787992229</v>
       </c>
     </row>
     <row r="16">
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0009216647418518575</v>
+        <v>0.0009216647418518464</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0002641336677146884</v>
+        <v>0.0002641336677146894</v>
       </c>
     </row>
     <row r="17">
@@ -4992,7 +4992,7 @@
         <v>0.0008939545123207493</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0004956754370202703</v>
+        <v>0.0004956754370202776</v>
       </c>
     </row>
     <row r="18">
@@ -5005,10 +5005,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0006425803427979049</v>
+        <v>0.0006425803427979382</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0004416961751193929</v>
+        <v>0.0004416961751193755</v>
       </c>
     </row>
     <row r="19">
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0004939475910281877</v>
+        <v>0.0004939475910281765</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0002284868843701049</v>
+        <v>0.0002284868843701323</v>
       </c>
     </row>
     <row r="20">
@@ -5037,10 +5037,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.00047072720512219</v>
+        <v>0.0004707272051221678</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0002011924938085931</v>
+        <v>0.0002011924938086056</v>
       </c>
     </row>
     <row r="21">
@@ -5056,7 +5056,7 @@
         <v>0.0004189207118883931</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0002205058215989641</v>
+        <v>0.0002205058215989713</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0004163616826270977</v>
+        <v>0.0004163616826271421</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0004101029283148259</v>
+        <v>0.0004101029283148243</v>
       </c>
     </row>
     <row r="23">
@@ -5085,10 +5085,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0004086844772112186</v>
+        <v>0.0004086844772112075</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0002584483202664285</v>
+        <v>0.000258448320266476</v>
       </c>
     </row>
     <row r="24">
@@ -5101,10 +5101,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.000387969342948602</v>
+        <v>0.0003879693429486131</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0004842629602930905</v>
+        <v>0.000484262960293087</v>
       </c>
     </row>
     <row r="25">
@@ -5120,7 +5120,7 @@
         <v>0.0003681251614669922</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0001901413595004222</v>
+        <v>0.0001901413595004276</v>
       </c>
     </row>
     <row r="26">
@@ -5136,7 +5136,7 @@
         <v>0.0003298602118368299</v>
       </c>
       <c r="D26" t="n">
-        <v>7.420256107290811e-05</v>
+        <v>7.420256107286672e-05</v>
       </c>
     </row>
     <row r="27">
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0003281996298877377</v>
+        <v>0.0003281996298877488</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0001265747425788584</v>
+        <v>0.0001265747425788487</v>
       </c>
     </row>
     <row r="28">
@@ -5168,7 +5168,7 @@
         <v>0.0003160224410930001</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0001936066576621885</v>
+        <v>0.0001936066576622181</v>
       </c>
     </row>
     <row r="29">
@@ -5184,7 +5184,7 @@
         <v>0.0002886776865377749</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0002998485437186236</v>
+        <v>0.0002998485437186585</v>
       </c>
     </row>
     <row r="30">
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0002265491737181602</v>
+        <v>0.0002265491737181713</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0004667151962868474</v>
+        <v>0.0004667151962868256</v>
       </c>
     </row>
     <row r="32">
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.000143322314579053</v>
+        <v>0.0001433223145790641</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0001606887678236269</v>
+        <v>0.0001606887678236217</v>
       </c>
     </row>
     <row r="33">
@@ -5248,7 +5248,7 @@
         <v>0.000125652302639645</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0002027547360125371</v>
+        <v>0.0002027547360125282</v>
       </c>
     </row>
     <row r="34">
@@ -5261,10 +5261,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.0001045709538454842</v>
+        <v>0.0001045709538454953</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0005433195132755192</v>
+        <v>0.000543319513275529</v>
       </c>
     </row>
     <row r="35">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.0001004520136867915</v>
+        <v>0.0001004520136867693</v>
       </c>
       <c r="D35" t="n">
-        <v>7.699375576561803e-05</v>
+        <v>7.699375576559575e-05</v>
       </c>
     </row>
     <row r="36">
@@ -5293,10 +5293,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4.996488354248596e-05</v>
+        <v>4.996488354246376e-05</v>
       </c>
       <c r="D36" t="n">
-        <v>9.530251591256622e-05</v>
+        <v>9.530251591256675e-05</v>
       </c>
     </row>
     <row r="37">
@@ -5312,7 +5312,7 @@
         <v>4.448725532437692e-05</v>
       </c>
       <c r="D37" t="n">
-        <v>8.102294106327235e-05</v>
+        <v>8.1022941063288e-05</v>
       </c>
     </row>
     <row r="38">
@@ -5325,10 +5325,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4.357300668264008e-05</v>
+        <v>4.357300668265118e-05</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0002140827525695976</v>
+        <v>0.0002140827525695816</v>
       </c>
     </row>
     <row r="39">
@@ -5341,10 +5341,10 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4.210899185662642e-05</v>
+        <v>4.210899185661532e-05</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0001591835438267494</v>
+        <v>0.000159183543826726</v>
       </c>
     </row>
     <row r="40">
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2.258744967039705e-05</v>
+        <v>2.258744967036375e-05</v>
       </c>
       <c r="D40" t="n">
-        <v>2.362033107267677e-05</v>
+        <v>2.362033107270174e-05</v>
       </c>
     </row>
     <row r="41">
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>6.82048063872509e-06</v>
+        <v>6.820480638736192e-06</v>
       </c>
       <c r="D41" t="n">
-        <v>4.485582365181625e-05</v>
+        <v>4.485582365178413e-05</v>
       </c>
     </row>
     <row r="42">
@@ -5392,7 +5392,7 @@
         <v>2.762245849674549e-06</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0001595544517067935</v>
+        <v>0.0001595544517068051</v>
       </c>
     </row>
     <row r="43">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-9.861126962218414e-07</v>
+        <v>-9.861126962107391e-07</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0001482059553467903</v>
+        <v>0.0001482059553467739</v>
       </c>
     </row>
     <row r="44">
@@ -5421,10 +5421,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-9.206848448506388e-06</v>
+        <v>-9.206848448517491e-06</v>
       </c>
       <c r="D44" t="n">
-        <v>7.775929036751156e-06</v>
+        <v>7.775929036758813e-06</v>
       </c>
     </row>
     <row r="45">
@@ -5453,10 +5453,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-3.494969673081272e-05</v>
+        <v>-3.494969673080161e-05</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0001287288212643009</v>
+        <v>0.0001287288212643306</v>
       </c>
     </row>
     <row r="47">
@@ -5472,7 +5472,7 @@
         <v>-5.125645230295017e-05</v>
       </c>
       <c r="D47" t="n">
-        <v>1.941419715885385e-05</v>
+        <v>1.941419715885076e-05</v>
       </c>
     </row>
     <row r="48">
@@ -5536,7 +5536,7 @@
         <v>-0.0003023502629998176</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0002050707450226975</v>
+        <v>0.0002050707450227105</v>
       </c>
     </row>
     <row r="52">
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-0.0003126019529183899</v>
+        <v>-0.0003126019529183677</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0002626275236228015</v>
+        <v>0.0002626275236227876</v>
       </c>
     </row>
     <row r="53">
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.0003389814205102981</v>
+        <v>-0.0003389814205102648</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0002626940205436082</v>
+        <v>0.0002626940205435897</v>
       </c>
     </row>
     <row r="54">
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.0006547469196777067</v>
+        <v>-0.0006547469196776956</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0003377717366934673</v>
+        <v>0.0003377717366934631</v>
       </c>
     </row>
   </sheetData>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-06-14 21:58:10 UTC</t>
+          <t>2026-06-16 19:25:09 UTC</t>
         </is>
       </c>
     </row>
